--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY141"/>
+  <dimension ref="A1:AY142"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -12953,32 +12953,32 @@
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128314411</v>
+        <v>135358856</v>
       </c>
       <c r="B118" t="n">
-        <v>92348</v>
+        <v>91459</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5420</v>
+        <v>2051</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I118" t="inlineStr">
@@ -12986,11 +12986,7 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
@@ -12999,10 +12995,10 @@
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>688088</v>
+        <v>688004</v>
       </c>
       <c r="R118" t="n">
-        <v>6562722</v>
+        <v>6562799</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13029,12 +13025,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13062,36 +13058,44 @@
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128314833</v>
+        <v>128314411</v>
       </c>
       <c r="B119" t="n">
-        <v>93235</v>
+        <v>92348</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
-      <c r="J119" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J119" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
       <c r="P119" t="inlineStr">
@@ -13100,10 +13104,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>688073</v>
+        <v>688088</v>
       </c>
       <c r="R119" t="n">
-        <v>6562768</v>
+        <v>6562722</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13163,7 +13167,7 @@
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128317789</v>
+        <v>128314833</v>
       </c>
       <c r="B120" t="n">
         <v>93235</v>
@@ -13201,10 +13205,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>688094</v>
+        <v>688073</v>
       </c>
       <c r="R120" t="n">
-        <v>6562777</v>
+        <v>6562768</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13264,7 +13268,7 @@
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128526064</v>
+        <v>128317789</v>
       </c>
       <c r="B121" t="n">
         <v>93235</v>
@@ -13302,10 +13306,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>687952</v>
+        <v>688094</v>
       </c>
       <c r="R121" t="n">
-        <v>6562790</v>
+        <v>6562777</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13332,12 +13336,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13365,7 +13369,7 @@
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128646583</v>
+        <v>128526064</v>
       </c>
       <c r="B122" t="n">
         <v>93235</v>
@@ -13403,10 +13407,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>688067</v>
+        <v>687952</v>
       </c>
       <c r="R122" t="n">
-        <v>6562731</v>
+        <v>6562790</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -13433,12 +13437,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -13466,10 +13470,10 @@
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>17285491</v>
+        <v>128646583</v>
       </c>
       <c r="B123" t="n">
-        <v>80432</v>
+        <v>93235</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -13477,36 +13481,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Norrby torp, 480 m Ö, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>688111</v>
+        <v>688067</v>
       </c>
       <c r="R123" t="n">
-        <v>6562706</v>
+        <v>6562731</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -13533,17 +13538,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -13552,30 +13552,26 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>Yngre gallrad blandskog</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>79273786</v>
+        <v>17285491</v>
       </c>
       <c r="B124" t="n">
         <v>80432</v>
@@ -13604,16 +13600,18 @@
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Åvadal, Srm</t>
+          <t>Norrby torp, 480 m Ö, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>688109</v>
+        <v>688111</v>
       </c>
       <c r="R124" t="n">
-        <v>6562704</v>
+        <v>6562706</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -13640,12 +13638,17 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2015-04-02</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2015-04-02</t>
+        </is>
+      </c>
+      <c r="AC124" t="inlineStr">
+        <is>
+          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -13657,37 +13660,27 @@
       <c r="AG124" t="b">
         <v>0</v>
       </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+      <c r="AI124" t="inlineStr">
+        <is>
+          <t>Yngre gallrad blandskog</t>
         </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>89840770</v>
+        <v>79273786</v>
       </c>
       <c r="B125" t="n">
         <v>80432</v>
@@ -13716,19 +13709,16 @@
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
-      <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Ö Norrby Torp, Srm</t>
+          <t>Åvadal, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>688146</v>
+        <v>688109</v>
       </c>
       <c r="R125" t="n">
-        <v>6562738</v>
+        <v>6562704</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -13755,17 +13745,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
-        </is>
-      </c>
-      <c r="AC125" t="inlineStr">
-        <is>
-          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -13774,26 +13759,40 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ125" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK125" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO125" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>112384453</v>
+        <v>89840770</v>
       </c>
       <c r="B126" t="n">
         <v>80432</v>
@@ -13827,14 +13826,14 @@
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Norrby torp Ö om, Srm</t>
+          <t>Ö Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>688145</v>
+        <v>688146</v>
       </c>
       <c r="R126" t="n">
-        <v>6562737</v>
+        <v>6562738</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -13861,17 +13860,17 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AC126" t="inlineStr">
         <is>
-          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
+          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -13887,19 +13886,19 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122779297</v>
+        <v>112384453</v>
       </c>
       <c r="B127" t="n">
         <v>80432</v>
@@ -13933,14 +13932,14 @@
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Lunglav, Srm</t>
+          <t>Norrby torp Ö om, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>688116</v>
+        <v>688145</v>
       </c>
       <c r="R127" t="n">
-        <v>6562703</v>
+        <v>6562737</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -13967,17 +13966,17 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Lunglav på gammal ek</t>
+          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -13993,76 +13992,63 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125923864</v>
+        <v>122779297</v>
       </c>
       <c r="B128" t="n">
-        <v>57754</v>
+        <v>80432</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>102118</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Lunglav, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>687916</v>
+        <v>688116</v>
       </c>
       <c r="R128" t="n">
-        <v>6562815</v>
+        <v>6562703</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14086,17 +14072,17 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
+          <t>Lunglav på gammal ek</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14105,58 +14091,67 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128317861</v>
+        <v>125923864</v>
       </c>
       <c r="B129" t="n">
-        <v>58114</v>
+        <v>57754</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
+      <c r="L129" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M129" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N129" t="inlineStr"/>
@@ -14166,10 +14161,10 @@
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>688058</v>
+        <v>687916</v>
       </c>
       <c r="R129" t="n">
-        <v>6562805</v>
+        <v>6562815</v>
       </c>
       <c r="S129" t="n">
         <v>25</v>
@@ -14196,12 +14191,17 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14228,65 +14228,56 @@
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122692266</v>
+        <v>128317861</v>
       </c>
       <c r="B130" t="n">
-        <v>58826</v>
+        <v>58114</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>208242</v>
+        <v>103021</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="M130" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>687868</v>
+        <v>688058</v>
       </c>
       <c r="R130" t="n">
-        <v>6562755</v>
+        <v>6562805</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14310,17 +14301,12 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC130" t="inlineStr">
-        <is>
-          <t>Mindre vattensalamander</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14329,29 +14315,28 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>101544040</v>
+        <v>122692266</v>
       </c>
       <c r="B131" t="n">
-        <v>99035</v>
+        <v>58826</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
@@ -14359,41 +14344,54 @@
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219790</v>
+        <v>208242</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I131" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
-      <c r="N131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N131" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P131" t="inlineStr">
         <is>
-          <t>NO Norrby Torp, Srm</t>
+          <t>Mindre vattensalamander, Srm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>687896</v>
+        <v>687868</v>
       </c>
       <c r="R131" t="n">
-        <v>6562764</v>
+        <v>6562755</v>
       </c>
       <c r="S131" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T131" t="inlineStr">
         <is>
@@ -14417,12 +14415,17 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -14438,22 +14441,22 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122930166</v>
+        <v>101544040</v>
       </c>
       <c r="B132" t="n">
-        <v>96554</v>
+        <v>99035</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -14461,21 +14464,21 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>210</v>
+        <v>219790</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I132" t="inlineStr"/>
@@ -14485,17 +14488,17 @@
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>NO Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>686762</v>
+        <v>687896</v>
       </c>
       <c r="R132" t="n">
-        <v>6562715</v>
+        <v>6562764</v>
       </c>
       <c r="S132" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -14519,22 +14522,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -14543,28 +14536,29 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122929535</v>
+        <v>122930166</v>
       </c>
       <c r="B133" t="n">
-        <v>8455</v>
+        <v>96554</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -14572,32 +14566,27 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>210</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
@@ -14605,13 +14594,13 @@
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>686612</v>
+        <v>686762</v>
       </c>
       <c r="R133" t="n">
-        <v>6562882</v>
+        <v>6562715</v>
       </c>
       <c r="S133" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -14640,7 +14629,7 @@
       </c>
       <c r="Z133" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
@@ -14650,7 +14639,7 @@
       </c>
       <c r="AB133" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -14677,10 +14666,10 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>122928987</v>
+        <v>122929535</v>
       </c>
       <c r="B134" t="n">
-        <v>97983</v>
+        <v>8455</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -14688,27 +14677,32 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
+      <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
@@ -14716,13 +14710,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>686389</v>
+        <v>686612</v>
       </c>
       <c r="R134" t="n">
-        <v>6562967</v>
+        <v>6562882</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14751,7 +14745,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -14761,7 +14755,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14788,45 +14782,49 @@
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126061106</v>
+        <v>122928987</v>
       </c>
       <c r="B135" t="n">
-        <v>91333</v>
+        <v>97983</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2008</v>
+        <v>221945</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>686883</v>
+        <v>686389</v>
       </c>
       <c r="R135" t="n">
-        <v>6562742</v>
+        <v>6562967</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -14853,22 +14851,22 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14883,44 +14881,44 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126061107</v>
+        <v>126061106</v>
       </c>
       <c r="B136" t="n">
-        <v>96458</v>
+        <v>91333</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2818</v>
+        <v>2008</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
@@ -14930,10 +14928,10 @@
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>686880</v>
+        <v>686883</v>
       </c>
       <c r="R136" t="n">
-        <v>6562745</v>
+        <v>6562742</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14965,7 +14963,7 @@
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
@@ -14975,7 +14973,7 @@
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15002,10 +15000,10 @@
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129215187</v>
+        <v>126061107</v>
       </c>
       <c r="B137" t="n">
-        <v>91872</v>
+        <v>96458</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15013,37 +15011,34 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
-      <c r="J137" t="inlineStr"/>
-      <c r="K137" t="inlineStr"/>
-      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>686977</v>
+        <v>686880</v>
       </c>
       <c r="R137" t="n">
-        <v>6562706</v>
+        <v>6562745</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15070,12 +15065,22 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15084,29 +15089,28 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126061104</v>
+        <v>129215187</v>
       </c>
       <c r="B138" t="n">
-        <v>4775</v>
+        <v>91872</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15114,34 +15118,37 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
+      <c r="K138" t="inlineStr"/>
+      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>686868</v>
+        <v>686977</v>
       </c>
       <c r="R138" t="n">
-        <v>6562739</v>
+        <v>6562706</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15168,22 +15175,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z138" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB138" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15192,48 +15189,29 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
+      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL138" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126061116</v>
+        <v>126061104</v>
       </c>
       <c r="B139" t="n">
-        <v>44177</v>
+        <v>4775</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15241,21 +15219,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>101735</v>
+        <v>100299</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15265,10 +15243,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>686928</v>
+        <v>686868</v>
       </c>
       <c r="R139" t="n">
-        <v>6562716</v>
+        <v>6562739</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15300,7 +15278,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -15310,7 +15288,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15324,22 +15302,22 @@
       </c>
       <c r="AJ139" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK139" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL139" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk.</t>
+          <t>Stående död gran.</t>
         </is>
       </c>
       <c r="AO139" t="inlineStr">
         <is>
-          <t>Fomes fomentarius # Fnöskticka på björk.</t>
+          <t>Picea abies # Stående död gran.</t>
         </is>
       </c>
       <c r="AT139" t="inlineStr"/>
@@ -15357,10 +15335,10 @@
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125974903</v>
+        <v>126061116</v>
       </c>
       <c r="B140" t="n">
-        <v>8444</v>
+        <v>44177</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15368,50 +15346,37 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J140" t="inlineStr"/>
-      <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N140" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>686838</v>
+        <v>686928</v>
       </c>
       <c r="R140" t="n">
-        <v>6562733</v>
+        <v>6562716</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -15438,14 +15403,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z140" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA140" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+      <c r="AB140" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15454,46 +15424,45 @@
       <c r="AE140" t="b">
         <v>0</v>
       </c>
-      <c r="AF140" t="inlineStr"/>
       <c r="AG140" t="b">
         <v>0</v>
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>vårtbjörk</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AL140" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
+          <t>Fomes fomentarius # Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126061105</v>
+        <v>125974903</v>
       </c>
       <c r="B141" t="n">
         <v>8444</v>
@@ -15521,20 +15490,33 @@
           <t>Janson, 1856</t>
         </is>
       </c>
-      <c r="I141" t="inlineStr"/>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J141" t="inlineStr"/>
+      <c r="K141" t="inlineStr"/>
+      <c r="L141" t="inlineStr"/>
+      <c r="M141" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>söder om Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>686860</v>
+        <v>686838</v>
       </c>
       <c r="R141" t="n">
-        <v>6562743</v>
+        <v>6562733</v>
       </c>
       <c r="S141" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15561,19 +15543,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z141" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB141" t="inlineStr">
-        <is>
-          <t>13:36</t>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15582,36 +15559,164 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
+      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM141" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Wood surface of dead wood # Betula pendula</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
+          <t>Nette Bygren</t>
+        </is>
+      </c>
+      <c r="AX141" t="inlineStr">
+        <is>
+          <t>Nette Bygren</t>
+        </is>
+      </c>
+      <c r="AY141" t="inlineStr"/>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>126061105</v>
+      </c>
+      <c r="B142" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>686860</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6562743</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
           <t>Klas Magnusson</t>
         </is>
       </c>
-      <c r="AX141" t="inlineStr">
+      <c r="AX142" t="inlineStr">
         <is>
           <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
-      <c r="AY141" t="inlineStr"/>
+      <c r="AY142" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY142"/>
+  <dimension ref="A1:AY143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14666,57 +14666,51 @@
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>122929535</v>
+        <v>119061006</v>
       </c>
       <c r="B134" t="n">
-        <v>8455</v>
+        <v>91459</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>106545</v>
+        <v>2051</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
       <c r="K134" t="inlineStr"/>
-      <c r="L134" t="inlineStr"/>
-      <c r="M134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>S Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>686612</v>
+        <v>686477</v>
       </c>
       <c r="R134" t="n">
-        <v>6562882</v>
+        <v>6562857</v>
       </c>
       <c r="S134" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -14740,22 +14734,17 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z134" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB134" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>Brukad skog nära kant mot gammal.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -14764,28 +14753,29 @@
       <c r="AE134" t="b">
         <v>0</v>
       </c>
+      <c r="AF134" t="inlineStr"/>
       <c r="AG134" t="b">
         <v>0</v>
       </c>
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>122928987</v>
+        <v>122929535</v>
       </c>
       <c r="B135" t="n">
-        <v>97983</v>
+        <v>8455</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -14793,27 +14783,32 @@
         </is>
       </c>
       <c r="E135" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="L135" t="inlineStr"/>
+      <c r="M135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
@@ -14821,13 +14816,13 @@
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>686389</v>
+        <v>686612</v>
       </c>
       <c r="R135" t="n">
-        <v>6562967</v>
+        <v>6562882</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -14856,7 +14851,7 @@
       </c>
       <c r="Z135" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
@@ -14866,7 +14861,7 @@
       </c>
       <c r="AB135" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -14893,45 +14888,49 @@
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126061106</v>
+        <v>122928987</v>
       </c>
       <c r="B136" t="n">
-        <v>91333</v>
+        <v>97983</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2008</v>
+        <v>221945</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I136" t="inlineStr"/>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>686883</v>
+        <v>686389</v>
       </c>
       <c r="R136" t="n">
-        <v>6562742</v>
+        <v>6562967</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -14958,22 +14957,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -14988,44 +14987,44 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>126061107</v>
+        <v>126061106</v>
       </c>
       <c r="B137" t="n">
-        <v>96458</v>
+        <v>91333</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2818</v>
+        <v>2008</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
@@ -15035,10 +15034,10 @@
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>686880</v>
+        <v>686883</v>
       </c>
       <c r="R137" t="n">
-        <v>6562745</v>
+        <v>6562742</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15070,7 +15069,7 @@
       </c>
       <c r="Z137" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
@@ -15080,7 +15079,7 @@
       </c>
       <c r="AB137" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15107,10 +15106,10 @@
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129215187</v>
+        <v>126061107</v>
       </c>
       <c r="B138" t="n">
-        <v>91872</v>
+        <v>96458</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
@@ -15118,37 +15117,34 @@
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
-      <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
-      <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>686977</v>
+        <v>686880</v>
       </c>
       <c r="R138" t="n">
-        <v>6562706</v>
+        <v>6562745</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15175,12 +15171,22 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z138" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB138" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15189,29 +15195,28 @@
       <c r="AE138" t="b">
         <v>0</v>
       </c>
-      <c r="AF138" t="inlineStr"/>
       <c r="AG138" t="b">
         <v>0</v>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX138" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126061104</v>
+        <v>129215187</v>
       </c>
       <c r="B139" t="n">
-        <v>4775</v>
+        <v>91872</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15219,34 +15224,37 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
+      <c r="J139" t="inlineStr"/>
+      <c r="K139" t="inlineStr"/>
+      <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>686868</v>
+        <v>686977</v>
       </c>
       <c r="R139" t="n">
-        <v>6562739</v>
+        <v>6562706</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15273,22 +15281,12 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z139" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB139" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15297,48 +15295,29 @@
       <c r="AE139" t="b">
         <v>0</v>
       </c>
+      <c r="AF139" t="inlineStr"/>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL139" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>126061116</v>
+        <v>126061104</v>
       </c>
       <c r="B140" t="n">
-        <v>44177</v>
+        <v>4775</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15346,21 +15325,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>101735</v>
+        <v>100299</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -15370,10 +15349,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>686928</v>
+        <v>686868</v>
       </c>
       <c r="R140" t="n">
-        <v>6562716</v>
+        <v>6562739</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -15405,7 +15384,7 @@
       </c>
       <c r="Z140" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
@@ -15415,7 +15394,7 @@
       </c>
       <c r="AB140" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -15429,22 +15408,22 @@
       </c>
       <c r="AJ140" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK140" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL140" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk.</t>
+          <t>Stående död gran.</t>
         </is>
       </c>
       <c r="AO140" t="inlineStr">
         <is>
-          <t>Fomes fomentarius # Fnöskticka på björk.</t>
+          <t>Picea abies # Stående död gran.</t>
         </is>
       </c>
       <c r="AT140" t="inlineStr"/>
@@ -15462,10 +15441,10 @@
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>125974903</v>
+        <v>126061116</v>
       </c>
       <c r="B141" t="n">
-        <v>8444</v>
+        <v>44177</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -15473,50 +15452,37 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J141" t="inlineStr"/>
-      <c r="K141" t="inlineStr"/>
-      <c r="L141" t="inlineStr"/>
-      <c r="M141" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N141" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="P141" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>686838</v>
+        <v>686928</v>
       </c>
       <c r="R141" t="n">
-        <v>6562733</v>
+        <v>6562716</v>
       </c>
       <c r="S141" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T141" t="inlineStr">
         <is>
@@ -15543,14 +15509,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z141" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA141" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC141" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+      <c r="AB141" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -15559,46 +15530,45 @@
       <c r="AE141" t="b">
         <v>0</v>
       </c>
-      <c r="AF141" t="inlineStr"/>
       <c r="AG141" t="b">
         <v>0</v>
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>vårtbjörk</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM141" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AL141" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
+          <t>Fomes fomentarius # Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
       <c r="AW141" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX141" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>126061105</v>
+        <v>125974903</v>
       </c>
       <c r="B142" t="n">
         <v>8444</v>
@@ -15626,20 +15596,33 @@
           <t>Janson, 1856</t>
         </is>
       </c>
-      <c r="I142" t="inlineStr"/>
+      <c r="I142" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J142" t="inlineStr"/>
+      <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
+      <c r="M142" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>söder om Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>686860</v>
+        <v>686838</v>
       </c>
       <c r="R142" t="n">
-        <v>6562743</v>
+        <v>6562733</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -15666,19 +15649,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA142" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>13:36</t>
+      <c r="AC142" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -15687,36 +15665,164 @@
       <c r="AE142" t="b">
         <v>0</v>
       </c>
+      <c r="AF142" t="inlineStr"/>
       <c r="AG142" t="b">
         <v>0</v>
       </c>
       <c r="AJ142" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK142" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM142" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO142" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Wood surface of dead wood # Betula pendula</t>
         </is>
       </c>
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
+          <t>Nette Bygren</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Nette Bygren</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>126061105</v>
+      </c>
+      <c r="B143" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>686860</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6562743</v>
+      </c>
+      <c r="S143" t="n">
+        <v>10</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z143" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB143" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
           <t>Klas Magnusson</t>
         </is>
       </c>
-      <c r="AX142" t="inlineStr">
+      <c r="AX143" t="inlineStr">
         <is>
           <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
-      <c r="AY142" t="inlineStr"/>
+      <c r="AY143" t="inlineStr"/>
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AY143"/>
+  <dimension ref="A1:AZ143"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -672,6 +672,11 @@
           <t>Projektnamn</t>
         </is>
       </c>
+      <c r="AZ1" t="inlineStr">
+        <is>
+          <t>Artportalenlänk</t>
+        </is>
+      </c>
     </row>
     <row r="2">
       <c r="A2" t="n">
@@ -779,6 +784,11 @@
         </is>
       </c>
       <c r="AY2" t="inlineStr"/>
+      <c r="AZ2" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859666</t>
+        </is>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="n">
@@ -885,6 +895,11 @@
         </is>
       </c>
       <c r="AY3" t="inlineStr"/>
+      <c r="AZ3" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968276</t>
+        </is>
+      </c>
     </row>
     <row r="4">
       <c r="A4" t="n">
@@ -991,6 +1006,11 @@
         </is>
       </c>
       <c r="AY4" t="inlineStr"/>
+      <c r="AZ4" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129592411</t>
+        </is>
+      </c>
     </row>
     <row r="5">
       <c r="A5" t="n">
@@ -1097,6 +1117,11 @@
         </is>
       </c>
       <c r="AY5" t="inlineStr"/>
+      <c r="AZ5" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129592461</t>
+        </is>
+      </c>
     </row>
     <row r="6">
       <c r="A6" t="n">
@@ -1198,6 +1223,11 @@
         </is>
       </c>
       <c r="AY6" t="inlineStr"/>
+      <c r="AZ6" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129626491</t>
+        </is>
+      </c>
     </row>
     <row r="7">
       <c r="A7" t="n">
@@ -1299,6 +1329,11 @@
         </is>
       </c>
       <c r="AY7" t="inlineStr"/>
+      <c r="AZ7" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129736828</t>
+        </is>
+      </c>
     </row>
     <row r="8">
       <c r="A8" t="n">
@@ -1400,6 +1435,11 @@
         </is>
       </c>
       <c r="AY8" t="inlineStr"/>
+      <c r="AZ8" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129736849</t>
+        </is>
+      </c>
     </row>
     <row r="9">
       <c r="A9" t="n">
@@ -1501,6 +1541,11 @@
         </is>
       </c>
       <c r="AY9" t="inlineStr"/>
+      <c r="AZ9" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887322</t>
+        </is>
+      </c>
     </row>
     <row r="10">
       <c r="A10" t="n">
@@ -1602,6 +1647,11 @@
         </is>
       </c>
       <c r="AY10" t="inlineStr"/>
+      <c r="AZ10" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887372</t>
+        </is>
+      </c>
     </row>
     <row r="11">
       <c r="A11" t="n">
@@ -1703,6 +1753,11 @@
         </is>
       </c>
       <c r="AY11" t="inlineStr"/>
+      <c r="AZ11" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952311</t>
+        </is>
+      </c>
     </row>
     <row r="12">
       <c r="A12" t="n">
@@ -1804,6 +1859,11 @@
         </is>
       </c>
       <c r="AY12" t="inlineStr"/>
+      <c r="AZ12" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952321</t>
+        </is>
+      </c>
     </row>
     <row r="13">
       <c r="A13" t="n">
@@ -1905,6 +1965,11 @@
         </is>
       </c>
       <c r="AY13" t="inlineStr"/>
+      <c r="AZ13" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887003</t>
+        </is>
+      </c>
     </row>
     <row r="14">
       <c r="A14" t="n">
@@ -2012,6 +2077,11 @@
         </is>
       </c>
       <c r="AY14" t="inlineStr"/>
+      <c r="AZ14" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859662</t>
+        </is>
+      </c>
     </row>
     <row r="15">
       <c r="A15" t="n">
@@ -2113,6 +2183,11 @@
         </is>
       </c>
       <c r="AY15" t="inlineStr"/>
+      <c r="AZ15" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112319692</t>
+        </is>
+      </c>
     </row>
     <row r="16">
       <c r="A16" t="n">
@@ -2214,6 +2289,11 @@
         </is>
       </c>
       <c r="AY16" t="inlineStr"/>
+      <c r="AZ16" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112492249</t>
+        </is>
+      </c>
     </row>
     <row r="17">
       <c r="A17" t="n">
@@ -2315,6 +2395,11 @@
         </is>
       </c>
       <c r="AY17" t="inlineStr"/>
+      <c r="AZ17" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128317394</t>
+        </is>
+      </c>
     </row>
     <row r="18">
       <c r="A18" t="n">
@@ -2416,6 +2501,11 @@
         </is>
       </c>
       <c r="AY18" t="inlineStr"/>
+      <c r="AZ18" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952287</t>
+        </is>
+      </c>
     </row>
     <row r="19">
       <c r="A19" t="n">
@@ -2517,6 +2607,11 @@
         </is>
       </c>
       <c r="AY19" t="inlineStr"/>
+      <c r="AZ19" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128089920</t>
+        </is>
+      </c>
     </row>
     <row r="20">
       <c r="A20" t="n">
@@ -2618,6 +2713,11 @@
         </is>
       </c>
       <c r="AY20" t="inlineStr"/>
+      <c r="AZ20" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128089976</t>
+        </is>
+      </c>
     </row>
     <row r="21">
       <c r="A21" t="n">
@@ -2719,6 +2819,11 @@
         </is>
       </c>
       <c r="AY21" t="inlineStr"/>
+      <c r="AZ21" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887397</t>
+        </is>
+      </c>
     </row>
     <row r="22">
       <c r="A22" t="n">
@@ -2829,6 +2934,11 @@
         </is>
       </c>
       <c r="AY22" t="inlineStr"/>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128090057</t>
+        </is>
+      </c>
     </row>
     <row r="23">
       <c r="A23" t="n">
@@ -2930,6 +3040,11 @@
         </is>
       </c>
       <c r="AY23" t="inlineStr"/>
+      <c r="AZ23" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887356</t>
+        </is>
+      </c>
     </row>
     <row r="24">
       <c r="A24" t="n">
@@ -3031,6 +3146,11 @@
         </is>
       </c>
       <c r="AY24" t="inlineStr"/>
+      <c r="AZ24" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129626405</t>
+        </is>
+      </c>
     </row>
     <row r="25">
       <c r="A25" t="n">
@@ -3132,6 +3252,11 @@
         </is>
       </c>
       <c r="AY25" t="inlineStr"/>
+      <c r="AZ25" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129645852</t>
+        </is>
+      </c>
     </row>
     <row r="26">
       <c r="A26" t="n">
@@ -3233,6 +3358,11 @@
         </is>
       </c>
       <c r="AY26" t="inlineStr"/>
+      <c r="AZ26" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/99519747</t>
+        </is>
+      </c>
     </row>
     <row r="27">
       <c r="A27" t="n">
@@ -3334,6 +3464,11 @@
         </is>
       </c>
       <c r="AY27" t="inlineStr"/>
+      <c r="AZ27" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128359370</t>
+        </is>
+      </c>
     </row>
     <row r="28">
       <c r="A28" t="n">
@@ -3435,6 +3570,11 @@
         </is>
       </c>
       <c r="AY28" t="inlineStr"/>
+      <c r="AZ28" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646833</t>
+        </is>
+      </c>
     </row>
     <row r="29">
       <c r="A29" t="n">
@@ -3541,6 +3681,11 @@
         </is>
       </c>
       <c r="AY29" t="inlineStr"/>
+      <c r="AZ29" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887180</t>
+        </is>
+      </c>
     </row>
     <row r="30">
       <c r="A30" t="n">
@@ -3642,6 +3787,11 @@
         </is>
       </c>
       <c r="AY30" t="inlineStr"/>
+      <c r="AZ30" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128887307</t>
+        </is>
+      </c>
     </row>
     <row r="31">
       <c r="A31" t="n">
@@ -3743,6 +3893,11 @@
         </is>
       </c>
       <c r="AY31" t="inlineStr"/>
+      <c r="AZ31" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128968248</t>
+        </is>
+      </c>
     </row>
     <row r="32">
       <c r="A32" t="n">
@@ -3844,6 +3999,11 @@
         </is>
       </c>
       <c r="AY32" t="inlineStr"/>
+      <c r="AZ32" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128527098</t>
+        </is>
+      </c>
     </row>
     <row r="33">
       <c r="A33" t="n">
@@ -3954,6 +4114,11 @@
         </is>
       </c>
       <c r="AY33" t="inlineStr"/>
+      <c r="AZ33" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129262153</t>
+        </is>
+      </c>
     </row>
     <row r="34">
       <c r="A34" t="n">
@@ -4069,6 +4234,11 @@
         </is>
       </c>
       <c r="AY34" t="inlineStr"/>
+      <c r="AZ34" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129262983</t>
+        </is>
+      </c>
     </row>
     <row r="35">
       <c r="A35" t="n">
@@ -4178,6 +4348,11 @@
         </is>
       </c>
       <c r="AY35" t="inlineStr"/>
+      <c r="AZ35" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128341914</t>
+        </is>
+      </c>
     </row>
     <row r="36">
       <c r="A36" t="n">
@@ -4292,6 +4467,11 @@
         </is>
       </c>
       <c r="AY36" t="inlineStr"/>
+      <c r="AZ36" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779249</t>
+        </is>
+      </c>
     </row>
     <row r="37">
       <c r="A37" t="n">
@@ -4406,6 +4586,11 @@
         </is>
       </c>
       <c r="AY37" t="inlineStr"/>
+      <c r="AZ37" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779251</t>
+        </is>
+      </c>
     </row>
     <row r="38">
       <c r="A38" t="n">
@@ -4511,6 +4696,11 @@
         </is>
       </c>
       <c r="AY38" t="inlineStr"/>
+      <c r="AZ38" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/123014554</t>
+        </is>
+      </c>
     </row>
     <row r="39">
       <c r="A39" t="n">
@@ -4616,6 +4806,11 @@
         </is>
       </c>
       <c r="AY39" t="inlineStr"/>
+      <c r="AZ39" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124593051</t>
+        </is>
+      </c>
     </row>
     <row r="40">
       <c r="A40" t="n">
@@ -4721,6 +4916,11 @@
         </is>
       </c>
       <c r="AY40" t="inlineStr"/>
+      <c r="AZ40" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/127431864</t>
+        </is>
+      </c>
     </row>
     <row r="41">
       <c r="A41" t="n">
@@ -4826,6 +5026,11 @@
         </is>
       </c>
       <c r="AY41" t="inlineStr"/>
+      <c r="AZ41" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128341890</t>
+        </is>
+      </c>
     </row>
     <row r="42">
       <c r="A42" t="n">
@@ -4931,6 +5136,11 @@
         </is>
       </c>
       <c r="AY42" t="inlineStr"/>
+      <c r="AZ42" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128952275</t>
+        </is>
+      </c>
     </row>
     <row r="43">
       <c r="A43" t="n">
@@ -5034,6 +5244,11 @@
         </is>
       </c>
       <c r="AY43" t="inlineStr"/>
+      <c r="AZ43" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129736810</t>
+        </is>
+      </c>
     </row>
     <row r="44">
       <c r="A44" t="n">
@@ -5141,6 +5356,11 @@
         </is>
       </c>
       <c r="AY44" t="inlineStr"/>
+      <c r="AZ44" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/124721625</t>
+        </is>
+      </c>
     </row>
     <row r="45">
       <c r="A45" t="n">
@@ -5243,6 +5463,11 @@
         </is>
       </c>
       <c r="AY45" t="inlineStr"/>
+      <c r="AZ45" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126005083</t>
+        </is>
+      </c>
     </row>
     <row r="46">
       <c r="A46" t="n">
@@ -5345,6 +5570,11 @@
         </is>
       </c>
       <c r="AY46" t="inlineStr"/>
+      <c r="AZ46" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126005099</t>
+        </is>
+      </c>
     </row>
     <row r="47">
       <c r="A47" t="n">
@@ -5456,6 +5686,11 @@
         </is>
       </c>
       <c r="AY47" t="inlineStr"/>
+      <c r="AZ47" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234159</t>
+        </is>
+      </c>
     </row>
     <row r="48">
       <c r="A48" t="n">
@@ -5563,6 +5798,11 @@
         </is>
       </c>
       <c r="AY48" t="inlineStr"/>
+      <c r="AZ48" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859660</t>
+        </is>
+      </c>
     </row>
     <row r="49">
       <c r="A49" t="n">
@@ -5670,6 +5910,11 @@
         </is>
       </c>
       <c r="AY49" t="inlineStr"/>
+      <c r="AZ49" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859669</t>
+        </is>
+      </c>
     </row>
     <row r="50">
       <c r="A50" t="n">
@@ -5785,6 +6030,11 @@
         </is>
       </c>
       <c r="AY50" t="inlineStr"/>
+      <c r="AZ50" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96643468</t>
+        </is>
+      </c>
     </row>
     <row r="51">
       <c r="A51" t="n">
@@ -5887,6 +6137,11 @@
         </is>
       </c>
       <c r="AY51" t="inlineStr"/>
+      <c r="AZ51" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/111689384</t>
+        </is>
+      </c>
     </row>
     <row r="52">
       <c r="A52" t="n">
@@ -5994,6 +6249,11 @@
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
+      <c r="AZ52" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859661</t>
+        </is>
+      </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
@@ -6101,6 +6361,11 @@
         </is>
       </c>
       <c r="AY53" t="inlineStr"/>
+      <c r="AZ53" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859668</t>
+        </is>
+      </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
@@ -6208,6 +6473,11 @@
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
+      <c r="AZ54" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126079502</t>
+        </is>
+      </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
@@ -6310,6 +6580,11 @@
         </is>
       </c>
       <c r="AY55" t="inlineStr"/>
+      <c r="AZ55" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/131694769</t>
+        </is>
+      </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
@@ -6421,6 +6696,11 @@
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
+      <c r="AZ56" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129262166</t>
+        </is>
+      </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
@@ -6535,6 +6815,11 @@
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
+      <c r="AZ57" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234839</t>
+        </is>
+      </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
@@ -6646,6 +6931,11 @@
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
+      <c r="AZ58" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134488457</t>
+        </is>
+      </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
@@ -6753,6 +7043,11 @@
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
+      <c r="AZ59" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859625</t>
+        </is>
+      </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
@@ -6863,6 +7158,11 @@
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
+      <c r="AZ60" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/100252080</t>
+        </is>
+      </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
@@ -6969,6 +7269,11 @@
         </is>
       </c>
       <c r="AY61" t="inlineStr"/>
+      <c r="AZ61" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89470832</t>
+        </is>
+      </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
@@ -7075,6 +7380,11 @@
         </is>
       </c>
       <c r="AY62" t="inlineStr"/>
+      <c r="AZ62" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/113689593</t>
+        </is>
+      </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
@@ -7181,6 +7491,11 @@
         </is>
       </c>
       <c r="AY63" t="inlineStr"/>
+      <c r="AZ63" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563617</t>
+        </is>
+      </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
@@ -7287,6 +7602,11 @@
         </is>
       </c>
       <c r="AY64" t="inlineStr"/>
+      <c r="AZ64" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563797</t>
+        </is>
+      </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
@@ -7393,6 +7713,11 @@
         </is>
       </c>
       <c r="AY65" t="inlineStr"/>
+      <c r="AZ65" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129563832</t>
+        </is>
+      </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
@@ -7499,6 +7824,11 @@
         </is>
       </c>
       <c r="AY66" t="inlineStr"/>
+      <c r="AZ66" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564415</t>
+        </is>
+      </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
@@ -7600,6 +7930,11 @@
         </is>
       </c>
       <c r="AY67" t="inlineStr"/>
+      <c r="AZ67" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129565002</t>
+        </is>
+      </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
@@ -7701,6 +8036,11 @@
         </is>
       </c>
       <c r="AY68" t="inlineStr"/>
+      <c r="AZ68" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129214787</t>
+        </is>
+      </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
@@ -7807,6 +8147,11 @@
         </is>
       </c>
       <c r="AY69" t="inlineStr"/>
+      <c r="AZ69" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129736615</t>
+        </is>
+      </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
@@ -7908,6 +8253,11 @@
         </is>
       </c>
       <c r="AY70" t="inlineStr"/>
+      <c r="AZ70" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128886693</t>
+        </is>
+      </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
@@ -8009,6 +8359,11 @@
         </is>
       </c>
       <c r="AY71" t="inlineStr"/>
+      <c r="AZ71" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122435803</t>
+        </is>
+      </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
@@ -8136,6 +8491,11 @@
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
+      <c r="AZ72" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859626</t>
+        </is>
+      </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
@@ -8237,6 +8597,11 @@
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
+      <c r="AZ73" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457948</t>
+        </is>
+      </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
@@ -8347,6 +8712,11 @@
         </is>
       </c>
       <c r="AY74" t="inlineStr"/>
+      <c r="AZ74" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564462</t>
+        </is>
+      </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
@@ -8448,6 +8818,11 @@
         </is>
       </c>
       <c r="AY75" t="inlineStr"/>
+      <c r="AZ75" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564997</t>
+        </is>
+      </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
@@ -8549,6 +8924,11 @@
         </is>
       </c>
       <c r="AY76" t="inlineStr"/>
+      <c r="AZ76" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129591539</t>
+        </is>
+      </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
@@ -8650,6 +9030,11 @@
         </is>
       </c>
       <c r="AY77" t="inlineStr"/>
+      <c r="AZ77" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129591551</t>
+        </is>
+      </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
@@ -8751,6 +9136,11 @@
         </is>
       </c>
       <c r="AY78" t="inlineStr"/>
+      <c r="AZ78" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230377</t>
+        </is>
+      </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
@@ -8852,6 +9242,11 @@
         </is>
       </c>
       <c r="AY79" t="inlineStr"/>
+      <c r="AZ79" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230409</t>
+        </is>
+      </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
@@ -8953,6 +9348,11 @@
         </is>
       </c>
       <c r="AY80" t="inlineStr"/>
+      <c r="AZ80" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128886665</t>
+        </is>
+      </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
@@ -9054,6 +9454,11 @@
         </is>
       </c>
       <c r="AY81" t="inlineStr"/>
+      <c r="AZ81" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128342127</t>
+        </is>
+      </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
@@ -9155,6 +9560,11 @@
         </is>
       </c>
       <c r="AY82" t="inlineStr"/>
+      <c r="AZ82" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457671</t>
+        </is>
+      </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
@@ -9256,6 +9666,11 @@
         </is>
       </c>
       <c r="AY83" t="inlineStr"/>
+      <c r="AZ83" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457697</t>
+        </is>
+      </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
@@ -9357,6 +9772,11 @@
         </is>
       </c>
       <c r="AY84" t="inlineStr"/>
+      <c r="AZ84" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457855</t>
+        </is>
+      </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
@@ -9458,6 +9878,11 @@
         </is>
       </c>
       <c r="AY85" t="inlineStr"/>
+      <c r="AZ85" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128457938</t>
+        </is>
+      </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
@@ -9559,6 +9984,11 @@
         </is>
       </c>
       <c r="AY86" t="inlineStr"/>
+      <c r="AZ86" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128510579</t>
+        </is>
+      </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
@@ -9660,6 +10090,11 @@
         </is>
       </c>
       <c r="AY87" t="inlineStr"/>
+      <c r="AZ87" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646813</t>
+        </is>
+      </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
@@ -9765,6 +10200,11 @@
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
+      <c r="AZ88" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112337759</t>
+        </is>
+      </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
@@ -9871,6 +10311,11 @@
         </is>
       </c>
       <c r="AY89" t="inlineStr"/>
+      <c r="AZ89" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129591415</t>
+        </is>
+      </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
@@ -9972,6 +10417,11 @@
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
+      <c r="AZ90" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/96643356</t>
+        </is>
+      </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
@@ -10088,6 +10538,11 @@
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
+      <c r="AZ91" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/97239536</t>
+        </is>
+      </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
@@ -10204,6 +10659,11 @@
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
+      <c r="AZ92" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/106813853</t>
+        </is>
+      </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
@@ -10331,6 +10791,11 @@
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
+      <c r="AZ93" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859628</t>
+        </is>
+      </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
@@ -10451,6 +10916,11 @@
         </is>
       </c>
       <c r="AY94" t="inlineStr"/>
+      <c r="AZ94" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859622</t>
+        </is>
+      </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
@@ -10566,6 +11036,11 @@
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
+      <c r="AZ95" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122929399</t>
+        </is>
+      </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
@@ -10673,6 +11148,11 @@
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
+      <c r="AZ96" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126418797</t>
+        </is>
+      </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
@@ -10780,6 +11260,11 @@
         </is>
       </c>
       <c r="AY97" t="inlineStr"/>
+      <c r="AZ97" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134100841</t>
+        </is>
+      </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
@@ -10912,6 +11397,11 @@
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
+      <c r="AZ98" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/121859623</t>
+        </is>
+      </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
@@ -11017,6 +11507,11 @@
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
+      <c r="AZ99" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128510434</t>
+        </is>
+      </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
@@ -11122,6 +11617,11 @@
         </is>
       </c>
       <c r="AY100" t="inlineStr"/>
+      <c r="AZ100" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128886960</t>
+        </is>
+      </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
@@ -11227,6 +11727,11 @@
         </is>
       </c>
       <c r="AY101" t="inlineStr"/>
+      <c r="AZ101" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129230389</t>
+        </is>
+      </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
@@ -11332,6 +11837,11 @@
         </is>
       </c>
       <c r="AY102" t="inlineStr"/>
+      <c r="AZ102" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129591579</t>
+        </is>
+      </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
@@ -11437,6 +11947,11 @@
         </is>
       </c>
       <c r="AY103" t="inlineStr"/>
+      <c r="AZ103" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/133115563</t>
+        </is>
+      </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
@@ -11539,6 +12054,11 @@
         </is>
       </c>
       <c r="AY104" t="inlineStr"/>
+      <c r="AZ104" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/109890506</t>
+        </is>
+      </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
@@ -11646,6 +12166,11 @@
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
+      <c r="AZ105" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122781008</t>
+        </is>
+      </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
@@ -11761,6 +12286,11 @@
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
+      <c r="AZ106" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126418709</t>
+        </is>
+      </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
@@ -11876,6 +12406,11 @@
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
+      <c r="AZ107" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126418756</t>
+        </is>
+      </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
@@ -11978,6 +12513,11 @@
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
+      <c r="AZ108" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129564285</t>
+        </is>
+      </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
@@ -12088,6 +12628,11 @@
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
+      <c r="AZ109" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126234373</t>
+        </is>
+      </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
@@ -12199,6 +12744,11 @@
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
+      <c r="AZ110" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122929342</t>
+        </is>
+      </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
@@ -12310,6 +12860,11 @@
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
+      <c r="AZ111" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/134487656</t>
+        </is>
+      </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
@@ -12420,6 +12975,11 @@
           <t>Fynd med DNA-sekvens - extern</t>
         </is>
       </c>
+      <c r="AZ112" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/118843519</t>
+        </is>
+      </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
@@ -12535,6 +13095,11 @@
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
+      <c r="AZ113" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122203249</t>
+        </is>
+      </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
@@ -12642,6 +13207,11 @@
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
+      <c r="AZ114" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122780924</t>
+        </is>
+      </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
@@ -12743,6 +13313,11 @@
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
+      <c r="AZ115" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624531</t>
+        </is>
+      </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
@@ -12849,6 +13424,11 @@
         </is>
       </c>
       <c r="AY116" t="inlineStr"/>
+      <c r="AZ116" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129624696</t>
+        </is>
+      </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
@@ -12950,6 +13530,11 @@
         </is>
       </c>
       <c r="AY117" t="inlineStr"/>
+      <c r="AZ117" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122203275</t>
+        </is>
+      </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
@@ -13055,6 +13640,11 @@
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
+      <c r="AZ118" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/135358856</t>
+        </is>
+      </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
@@ -13164,6 +13754,11 @@
         </is>
       </c>
       <c r="AY119" t="inlineStr"/>
+      <c r="AZ119" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128314411</t>
+        </is>
+      </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
@@ -13265,6 +13860,11 @@
         </is>
       </c>
       <c r="AY120" t="inlineStr"/>
+      <c r="AZ120" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128314833</t>
+        </is>
+      </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
@@ -13366,6 +13966,11 @@
         </is>
       </c>
       <c r="AY121" t="inlineStr"/>
+      <c r="AZ121" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128317789</t>
+        </is>
+      </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
@@ -13467,6 +14072,11 @@
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
+      <c r="AZ122" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128526064</t>
+        </is>
+      </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
@@ -13568,6 +14178,11 @@
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
+      <c r="AZ123" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128646583</t>
+        </is>
+      </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
@@ -13677,6 +14292,11 @@
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
+      <c r="AZ124" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/17285491</t>
+        </is>
+      </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
@@ -13789,6 +14409,11 @@
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
+      <c r="AZ125" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/79273786</t>
+        </is>
+      </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
@@ -13895,6 +14520,11 @@
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
+      <c r="AZ126" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/89840770</t>
+        </is>
+      </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
@@ -14001,6 +14631,11 @@
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
+      <c r="AZ127" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/112384453</t>
+        </is>
+      </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
@@ -14107,6 +14742,11 @@
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
+      <c r="AZ128" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122779297</t>
+        </is>
+      </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
@@ -14225,6 +14865,11 @@
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
+      <c r="AZ129" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125923864</t>
+        </is>
+      </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
@@ -14330,6 +14975,11 @@
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
+      <c r="AZ130" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/128317861</t>
+        </is>
+      </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
@@ -14450,6 +15100,11 @@
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
+      <c r="AZ131" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122692266</t>
+        </is>
+      </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
@@ -14552,6 +15207,11 @@
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
+      <c r="AZ132" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/101544040</t>
+        </is>
+      </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
@@ -14663,6 +15323,11 @@
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
+      <c r="AZ133" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122930166</t>
+        </is>
+      </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
@@ -14769,6 +15434,11 @@
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
+      <c r="AZ134" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/119061006</t>
+        </is>
+      </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
@@ -14885,6 +15555,11 @@
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
+      <c r="AZ135" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122929535</t>
+        </is>
+      </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
@@ -14996,6 +15671,11 @@
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
+      <c r="AZ136" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/122928987</t>
+        </is>
+      </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
@@ -15103,6 +15783,11 @@
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
+      <c r="AZ137" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061106</t>
+        </is>
+      </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
@@ -15210,6 +15895,11 @@
         </is>
       </c>
       <c r="AY138" t="inlineStr"/>
+      <c r="AZ138" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061107</t>
+        </is>
+      </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
@@ -15311,6 +16001,11 @@
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
+      <c r="AZ139" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215187</t>
+        </is>
+      </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
@@ -15438,6 +16133,11 @@
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
+      <c r="AZ140" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061104</t>
+        </is>
+      </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
@@ -15565,6 +16265,11 @@
         </is>
       </c>
       <c r="AY141" t="inlineStr"/>
+      <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061116</t>
+        </is>
+      </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
@@ -15701,6 +16406,11 @@
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125974903</t>
+        </is>
+      </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
@@ -15823,8 +16533,157 @@
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061105</t>
+        </is>
+      </c>
     </row>
   </sheetData>
+  <hyperlinks>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ2" r:id="rId1"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ3" r:id="rId2"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ4" r:id="rId3"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ5" r:id="rId4"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ6" r:id="rId5"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ7" r:id="rId6"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ8" r:id="rId7"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ9" r:id="rId8"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ10" r:id="rId9"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ11" r:id="rId10"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ12" r:id="rId11"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ13" r:id="rId12"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ14" r:id="rId13"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ15" r:id="rId14"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ16" r:id="rId15"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ17" r:id="rId16"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ18" r:id="rId17"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ19" r:id="rId18"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ20" r:id="rId19"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ21" r:id="rId20"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ22" r:id="rId21"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ23" r:id="rId22"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ24" r:id="rId23"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ25" r:id="rId24"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ26" r:id="rId25"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ27" r:id="rId26"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ28" r:id="rId27"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ29" r:id="rId28"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ30" r:id="rId29"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ31" r:id="rId30"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ32" r:id="rId31"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ33" r:id="rId32"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ34" r:id="rId33"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ35" r:id="rId34"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ36" r:id="rId35"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ37" r:id="rId36"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ38" r:id="rId37"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ39" r:id="rId38"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ40" r:id="rId39"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ41" r:id="rId40"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ42" r:id="rId41"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ43" r:id="rId42"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ44" r:id="rId43"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ45" r:id="rId44"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ46" r:id="rId45"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ47" r:id="rId46"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ48" r:id="rId47"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ49" r:id="rId48"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ50" r:id="rId49"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ51" r:id="rId50"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ52" r:id="rId51"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ53" r:id="rId52"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ54" r:id="rId53"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ55" r:id="rId54"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ56" r:id="rId55"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ57" r:id="rId56"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ58" r:id="rId57"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ59" r:id="rId58"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ60" r:id="rId59"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ61" r:id="rId60"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ62" r:id="rId61"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ63" r:id="rId62"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ64" r:id="rId63"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ65" r:id="rId64"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ66" r:id="rId65"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ67" r:id="rId66"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ68" r:id="rId67"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ69" r:id="rId68"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ70" r:id="rId69"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ71" r:id="rId70"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ72" r:id="rId71"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ73" r:id="rId72"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ74" r:id="rId73"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ75" r:id="rId74"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ76" r:id="rId75"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ77" r:id="rId76"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ78" r:id="rId77"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ79" r:id="rId78"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ80" r:id="rId79"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ81" r:id="rId80"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ82" r:id="rId81"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ83" r:id="rId82"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ84" r:id="rId83"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ85" r:id="rId84"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ86" r:id="rId85"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ87" r:id="rId86"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ88" r:id="rId87"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ89" r:id="rId88"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ90" r:id="rId89"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ91" r:id="rId90"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ92" r:id="rId91"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ93" r:id="rId92"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ94" r:id="rId93"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ95" r:id="rId94"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ96" r:id="rId95"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ97" r:id="rId96"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ98" r:id="rId97"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ99" r:id="rId98"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ100" r:id="rId99"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ101" r:id="rId100"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ102" r:id="rId101"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ103" r:id="rId102"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ104" r:id="rId103"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ105" r:id="rId104"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ106" r:id="rId105"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ107" r:id="rId106"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ108" r:id="rId107"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ109" r:id="rId108"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ110" r:id="rId109"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ111" r:id="rId110"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ112" r:id="rId111"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ113" r:id="rId112"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ114" r:id="rId113"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ115" r:id="rId114"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ116" r:id="rId115"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ117" r:id="rId116"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ118" r:id="rId117"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ119" r:id="rId118"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ120" r:id="rId119"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ121" r:id="rId120"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ122" r:id="rId121"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ123" r:id="rId122"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ124" r:id="rId123"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ125" r:id="rId124"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ126" r:id="rId125"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ127" r:id="rId126"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ128" r:id="rId127"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ129" r:id="rId128"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ130" r:id="rId129"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ131" r:id="rId130"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ132" r:id="rId131"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ133" r:id="rId132"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ134" r:id="rId133"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ135" r:id="rId134"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ136" r:id="rId135"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ137" r:id="rId136"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ138" r:id="rId137"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+  </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
 </file>
--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -13541,7 +13541,7 @@
         <v>135358856</v>
       </c>
       <c r="B118" t="n">
-        <v>91459</v>
+        <v>91501</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>119061006</v>
       </c>
       <c r="B134" t="n">
-        <v>91459</v>
+        <v>91501</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -13541,7 +13541,7 @@
         <v>135358856</v>
       </c>
       <c r="B118" t="n">
-        <v>91501</v>
+        <v>91528</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
@@ -15334,7 +15334,7 @@
         <v>119061006</v>
       </c>
       <c r="B134" t="n">
-        <v>91501</v>
+        <v>91528</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ141"/>
+  <dimension ref="A1:AZ144"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -6145,10 +6145,10 @@
     </row>
     <row r="52">
       <c r="A52" t="n">
-        <v>121859661</v>
+        <v>135827249</v>
       </c>
       <c r="B52" t="n">
-        <v>97983</v>
+        <v>98142</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6156,16 +6156,16 @@
         </is>
       </c>
       <c r="E52" t="n">
-        <v>221945</v>
+        <v>221941</v>
       </c>
       <c r="F52" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Plattlummer</t>
         </is>
       </c>
       <c r="G52" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lycopodium complanatum</t>
         </is>
       </c>
       <c r="H52" t="inlineStr">
@@ -6174,16 +6174,20 @@
         </is>
       </c>
       <c r="I52" t="inlineStr"/>
+      <c r="J52" t="inlineStr"/>
+      <c r="K52" t="inlineStr"/>
+      <c r="L52" t="inlineStr"/>
+      <c r="N52" t="inlineStr"/>
       <c r="P52" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q52" t="n">
-        <v>687335</v>
+        <v>687270</v>
       </c>
       <c r="R52" t="n">
-        <v>6563472</v>
+        <v>6563321</v>
       </c>
       <c r="S52" t="n">
         <v>10</v>
@@ -6210,22 +6214,17 @@
       </c>
       <c r="Y52" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z52" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2026-08-11</t>
         </is>
       </c>
       <c r="AA52" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB52" t="inlineStr">
-        <is>
-          <t>14:29</t>
+          <t>2026-08-11</t>
+        </is>
+      </c>
+      <c r="AC52" t="inlineStr">
+        <is>
+          <t>Återfynd, tidigare rapporterad 2021.</t>
         </is>
       </c>
       <c r="AD52" t="b">
@@ -6234,30 +6233,31 @@
       <c r="AE52" t="b">
         <v>0</v>
       </c>
+      <c r="AF52" t="inlineStr"/>
       <c r="AG52" t="b">
         <v>0</v>
       </c>
       <c r="AT52" t="inlineStr"/>
       <c r="AW52" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX52" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY52" t="inlineStr"/>
       <c r="AZ52" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859661</t>
+          <t>https://artportalen.se/Sighting/135827249</t>
         </is>
       </c>
     </row>
     <row r="53">
       <c r="A53" t="n">
-        <v>121859668</v>
+        <v>121859661</v>
       </c>
       <c r="B53" t="n">
         <v>97983</v>
@@ -6292,10 +6292,10 @@
         </is>
       </c>
       <c r="Q53" t="n">
-        <v>687531</v>
+        <v>687335</v>
       </c>
       <c r="R53" t="n">
-        <v>6563515</v>
+        <v>6563472</v>
       </c>
       <c r="S53" t="n">
         <v>10</v>
@@ -6327,7 +6327,7 @@
       </c>
       <c r="Z53" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AA53" t="inlineStr">
@@ -6337,7 +6337,7 @@
       </c>
       <c r="AB53" t="inlineStr">
         <is>
-          <t>13:34</t>
+          <t>14:29</t>
         </is>
       </c>
       <c r="AD53" t="b">
@@ -6363,13 +6363,13 @@
       <c r="AY53" t="inlineStr"/>
       <c r="AZ53" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859668</t>
+          <t>https://artportalen.se/Sighting/121859661</t>
         </is>
       </c>
     </row>
     <row r="54">
       <c r="A54" t="n">
-        <v>126079502</v>
+        <v>121859668</v>
       </c>
       <c r="B54" t="n">
         <v>97983</v>
@@ -6398,23 +6398,19 @@
         </is>
       </c>
       <c r="I54" t="inlineStr"/>
-      <c r="J54" t="inlineStr"/>
-      <c r="K54" t="inlineStr"/>
-      <c r="L54" t="inlineStr"/>
-      <c r="N54" t="inlineStr"/>
       <c r="P54" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q54" t="n">
-        <v>687453</v>
+        <v>687531</v>
       </c>
       <c r="R54" t="n">
-        <v>6563526</v>
+        <v>6563515</v>
       </c>
       <c r="S54" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T54" t="inlineStr">
         <is>
@@ -6438,17 +6434,22 @@
       </c>
       <c r="Y54" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z54" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AA54" t="inlineStr">
         <is>
-          <t>2025-06-16</t>
-        </is>
-      </c>
-      <c r="AC54" t="inlineStr">
-        <is>
-          <t>Rikligt i kärret.</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB54" t="inlineStr">
+        <is>
+          <t>13:34</t>
         </is>
       </c>
       <c r="AD54" t="b">
@@ -6457,34 +6458,33 @@
       <c r="AE54" t="b">
         <v>0</v>
       </c>
-      <c r="AF54" t="inlineStr"/>
       <c r="AG54" t="b">
         <v>0</v>
       </c>
       <c r="AT54" t="inlineStr"/>
       <c r="AW54" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX54" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY54" t="inlineStr"/>
       <c r="AZ54" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126079502</t>
+          <t>https://artportalen.se/Sighting/121859668</t>
         </is>
       </c>
     </row>
     <row r="55">
       <c r="A55" t="n">
-        <v>131694769</v>
+        <v>126079502</v>
       </c>
       <c r="B55" t="n">
-        <v>98060</v>
+        <v>97983</v>
       </c>
       <c r="D55" t="inlineStr">
         <is>
@@ -6520,13 +6520,13 @@
         </is>
       </c>
       <c r="Q55" t="n">
-        <v>687317</v>
+        <v>687453</v>
       </c>
       <c r="R55" t="n">
-        <v>6563366</v>
+        <v>6563526</v>
       </c>
       <c r="S55" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T55" t="inlineStr">
         <is>
@@ -6550,12 +6550,17 @@
       </c>
       <c r="Y55" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-06-16</t>
         </is>
       </c>
       <c r="AA55" t="inlineStr">
         <is>
-          <t>2026-03-16</t>
+          <t>2025-06-16</t>
+        </is>
+      </c>
+      <c r="AC55" t="inlineStr">
+        <is>
+          <t>Rikligt i kärret.</t>
         </is>
       </c>
       <c r="AD55" t="b">
@@ -6582,16 +6587,16 @@
       <c r="AY55" t="inlineStr"/>
       <c r="AZ55" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/131694769</t>
+          <t>https://artportalen.se/Sighting/126079502</t>
         </is>
       </c>
     </row>
     <row r="56">
       <c r="A56" t="n">
-        <v>129262166</v>
+        <v>131694769</v>
       </c>
       <c r="B56" t="n">
-        <v>97986</v>
+        <v>98060</v>
       </c>
       <c r="D56" t="inlineStr">
         <is>
@@ -6599,16 +6604,16 @@
         </is>
       </c>
       <c r="E56" t="n">
-        <v>221946</v>
+        <v>221945</v>
       </c>
       <c r="F56" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G56" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H56" t="inlineStr">
@@ -6623,17 +6628,17 @@
       <c r="N56" t="inlineStr"/>
       <c r="P56" t="inlineStr">
         <is>
-          <t>Ungfars kärr, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q56" t="n">
-        <v>687329</v>
+        <v>687317</v>
       </c>
       <c r="R56" t="n">
-        <v>6563235</v>
+        <v>6563366</v>
       </c>
       <c r="S56" t="n">
-        <v>3</v>
+        <v>10</v>
       </c>
       <c r="T56" t="inlineStr">
         <is>
@@ -6657,22 +6662,12 @@
       </c>
       <c r="Y56" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="Z56" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AA56" t="inlineStr">
         <is>
-          <t>2025-10-22</t>
-        </is>
-      </c>
-      <c r="AB56" t="inlineStr">
-        <is>
-          <t>11:08</t>
+          <t>2026-03-16</t>
         </is>
       </c>
       <c r="AD56" t="b">
@@ -6681,33 +6676,34 @@
       <c r="AE56" t="b">
         <v>0</v>
       </c>
+      <c r="AF56" t="inlineStr"/>
       <c r="AG56" t="b">
         <v>0</v>
       </c>
       <c r="AT56" t="inlineStr"/>
       <c r="AW56" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX56" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY56" t="inlineStr"/>
       <c r="AZ56" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129262166</t>
+          <t>https://artportalen.se/Sighting/131694769</t>
         </is>
       </c>
     </row>
     <row r="57">
       <c r="A57" t="n">
-        <v>126234839</v>
+        <v>129262166</v>
       </c>
       <c r="B57" t="n">
-        <v>99140</v>
+        <v>97986</v>
       </c>
       <c r="D57" t="inlineStr">
         <is>
@@ -6715,53 +6711,41 @@
         </is>
       </c>
       <c r="E57" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F57" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G57" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H57" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I57" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J57" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
-      <c r="K57" t="inlineStr">
-        <is>
-          <t>överblommad</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I57" t="inlineStr"/>
+      <c r="J57" t="inlineStr"/>
+      <c r="K57" t="inlineStr"/>
       <c r="L57" t="inlineStr"/>
       <c r="N57" t="inlineStr"/>
       <c r="P57" t="inlineStr">
         <is>
-          <t>Vargklova mosse S om, Srm</t>
+          <t>Ungfars kärr, Srm</t>
         </is>
       </c>
       <c r="Q57" t="n">
-        <v>687489</v>
+        <v>687329</v>
       </c>
       <c r="R57" t="n">
-        <v>6563516</v>
+        <v>6563235</v>
       </c>
       <c r="S57" t="n">
-        <v>10</v>
+        <v>3</v>
       </c>
       <c r="T57" t="inlineStr">
         <is>
@@ -6785,12 +6769,22 @@
       </c>
       <c r="Y57" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="Z57" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AA57" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-10-22</t>
+        </is>
+      </c>
+      <c r="AB57" t="inlineStr">
+        <is>
+          <t>11:08</t>
         </is>
       </c>
       <c r="AD57" t="b">
@@ -6799,34 +6793,33 @@
       <c r="AE57" t="b">
         <v>0</v>
       </c>
-      <c r="AF57" t="inlineStr"/>
       <c r="AG57" t="b">
         <v>0</v>
       </c>
       <c r="AT57" t="inlineStr"/>
       <c r="AW57" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX57" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY57" t="inlineStr"/>
       <c r="AZ57" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234839</t>
+          <t>https://artportalen.se/Sighting/129262166</t>
         </is>
       </c>
     </row>
     <row r="58">
       <c r="A58" t="n">
-        <v>134488457</v>
+        <v>126234839</v>
       </c>
       <c r="B58" t="n">
-        <v>99217</v>
+        <v>99140</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -6851,25 +6844,33 @@
           <t>(L.) Rich.</t>
         </is>
       </c>
-      <c r="I58" t="inlineStr"/>
-      <c r="J58" t="inlineStr"/>
+      <c r="I58" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J58" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K58" t="inlineStr">
         <is>
-          <t>blomning</t>
+          <t>överblommad</t>
         </is>
       </c>
       <c r="L58" t="inlineStr"/>
       <c r="N58" t="inlineStr"/>
       <c r="P58" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Vargklova mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q58" t="n">
-        <v>687294</v>
+        <v>687489</v>
       </c>
       <c r="R58" t="n">
-        <v>6563391</v>
+        <v>6563516</v>
       </c>
       <c r="S58" t="n">
         <v>10</v>
@@ -6896,17 +6897,12 @@
       </c>
       <c r="Y58" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA58" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC58" t="inlineStr">
-        <is>
-          <t>2 i blom samt fler med endast blad.</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD58" t="b">
@@ -6922,62 +6918,70 @@
       <c r="AT58" t="inlineStr"/>
       <c r="AW58" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX58" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY58" t="inlineStr"/>
       <c r="AZ58" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134488457</t>
+          <t>https://artportalen.se/Sighting/126234839</t>
         </is>
       </c>
     </row>
     <row r="59">
       <c r="A59" t="n">
-        <v>121859625</v>
+        <v>134488457</v>
       </c>
       <c r="B59" t="n">
-        <v>97358</v>
+        <v>99217</v>
       </c>
       <c r="D59" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E59" t="n">
-        <v>53</v>
+        <v>221952</v>
       </c>
       <c r="F59" t="inlineStr">
         <is>
-          <t>Vedtrappmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G59" t="inlineStr">
         <is>
-          <t>Crossocalyx hellerianus</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H59" t="inlineStr">
         <is>
-          <t>(Nees ex Lindenb.) Meyl.</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I59" t="inlineStr"/>
+      <c r="J59" t="inlineStr"/>
+      <c r="K59" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L59" t="inlineStr"/>
+      <c r="N59" t="inlineStr"/>
       <c r="P59" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q59" t="n">
-        <v>686615</v>
+        <v>687294</v>
       </c>
       <c r="R59" t="n">
-        <v>6563007</v>
+        <v>6563391</v>
       </c>
       <c r="S59" t="n">
         <v>10</v>
@@ -7004,22 +7008,17 @@
       </c>
       <c r="Y59" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z59" t="inlineStr">
-        <is>
-          <t>17:29</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA59" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB59" t="inlineStr">
-        <is>
-          <t>17:29</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC59" t="inlineStr">
+        <is>
+          <t>2 i blom samt fler med endast blad.</t>
         </is>
       </c>
       <c r="AD59" t="b">
@@ -7028,80 +7027,69 @@
       <c r="AE59" t="b">
         <v>0</v>
       </c>
+      <c r="AF59" t="inlineStr"/>
       <c r="AG59" t="b">
         <v>0</v>
       </c>
       <c r="AT59" t="inlineStr"/>
       <c r="AW59" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX59" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY59" t="inlineStr"/>
       <c r="AZ59" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859625</t>
+          <t>https://artportalen.se/Sighting/134488457</t>
         </is>
       </c>
     </row>
     <row r="60">
       <c r="A60" t="n">
-        <v>100252080</v>
+        <v>121859625</v>
       </c>
       <c r="B60" t="n">
-        <v>96554</v>
+        <v>97358</v>
       </c>
       <c r="D60" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E60" t="n">
-        <v>210</v>
+        <v>53</v>
       </c>
       <c r="F60" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vedtrappmossa</t>
         </is>
       </c>
       <c r="G60" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Crossocalyx hellerianus</t>
         </is>
       </c>
       <c r="H60" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I60" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
-      <c r="J60" t="inlineStr"/>
-      <c r="K60" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L60" t="inlineStr"/>
-      <c r="N60" t="inlineStr"/>
+          <t>(Nees ex Lindenb.) Meyl.</t>
+        </is>
+      </c>
+      <c r="I60" t="inlineStr"/>
       <c r="P60" t="inlineStr">
         <is>
-          <t>S Norrby mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q60" t="n">
-        <v>686510</v>
+        <v>686615</v>
       </c>
       <c r="R60" t="n">
-        <v>6562916</v>
+        <v>6563007</v>
       </c>
       <c r="S60" t="n">
         <v>10</v>
@@ -7128,12 +7116,22 @@
       </c>
       <c r="Y60" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z60" t="inlineStr">
+        <is>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AA60" t="inlineStr">
         <is>
-          <t>2022-04-26</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB60" t="inlineStr">
+        <is>
+          <t>17:29</t>
         </is>
       </c>
       <c r="AD60" t="b">
@@ -7142,75 +7140,83 @@
       <c r="AE60" t="b">
         <v>0</v>
       </c>
-      <c r="AF60" t="inlineStr"/>
       <c r="AG60" t="b">
         <v>0</v>
       </c>
       <c r="AT60" t="inlineStr"/>
       <c r="AW60" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX60" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY60" t="inlineStr"/>
       <c r="AZ60" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/100252080</t>
+          <t>https://artportalen.se/Sighting/121859625</t>
         </is>
       </c>
     </row>
     <row r="61">
       <c r="A61" t="n">
-        <v>89470832</v>
+        <v>100252080</v>
       </c>
       <c r="B61" t="n">
-        <v>90946</v>
+        <v>96554</v>
       </c>
       <c r="D61" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E61" t="n">
-        <v>889</v>
+        <v>210</v>
       </c>
       <c r="F61" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G61" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H61" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
-        </is>
-      </c>
-      <c r="I61" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I61" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J61" t="inlineStr"/>
-      <c r="K61" t="inlineStr"/>
+      <c r="K61" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L61" t="inlineStr"/>
       <c r="N61" t="inlineStr"/>
       <c r="P61" t="inlineStr">
         <is>
-          <t>Norrby Mosse, Srm</t>
+          <t>S Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q61" t="n">
-        <v>686764</v>
+        <v>686510</v>
       </c>
       <c r="R61" t="n">
-        <v>6563157</v>
+        <v>6562916</v>
       </c>
       <c r="S61" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T61" t="inlineStr">
         <is>
@@ -7234,17 +7240,12 @@
       </c>
       <c r="Y61" t="inlineStr">
         <is>
-          <t>2020-12-09</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AA61" t="inlineStr">
         <is>
-          <t>2020-12-09</t>
-        </is>
-      </c>
-      <c r="AC61" t="inlineStr">
-        <is>
-          <t>På en mycket liten senvuxen tall.</t>
+          <t>2022-04-26</t>
         </is>
       </c>
       <c r="AD61" t="b">
@@ -7271,13 +7272,13 @@
       <c r="AY61" t="inlineStr"/>
       <c r="AZ61" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89470832</t>
+          <t>https://artportalen.se/Sighting/100252080</t>
         </is>
       </c>
     </row>
     <row r="62">
       <c r="A62" t="n">
-        <v>113689593</v>
+        <v>89470832</v>
       </c>
       <c r="B62" t="n">
         <v>90946</v>
@@ -7311,17 +7312,17 @@
       <c r="N62" t="inlineStr"/>
       <c r="P62" t="inlineStr">
         <is>
-          <t>S Norrby mosse, Srm</t>
+          <t>Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q62" t="n">
-        <v>686682</v>
+        <v>686764</v>
       </c>
       <c r="R62" t="n">
-        <v>6563034</v>
+        <v>6563157</v>
       </c>
       <c r="S62" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T62" t="inlineStr">
         <is>
@@ -7345,17 +7346,17 @@
       </c>
       <c r="Y62" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2020-12-09</t>
         </is>
       </c>
       <c r="AA62" t="inlineStr">
         <is>
-          <t>2023-12-19</t>
+          <t>2020-12-09</t>
         </is>
       </c>
       <c r="AC62" t="inlineStr">
         <is>
-          <t>På två levande tallar.</t>
+          <t>På en mycket liten senvuxen tall.</t>
         </is>
       </c>
       <c r="AD62" t="b">
@@ -7382,13 +7383,13 @@
       <c r="AY62" t="inlineStr"/>
       <c r="AZ62" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/113689593</t>
+          <t>https://artportalen.se/Sighting/89470832</t>
         </is>
       </c>
     </row>
     <row r="63">
       <c r="A63" t="n">
-        <v>129563617</v>
+        <v>113689593</v>
       </c>
       <c r="B63" t="n">
         <v>90946</v>
@@ -7422,14 +7423,14 @@
       <c r="N63" t="inlineStr"/>
       <c r="P63" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>S Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q63" t="n">
-        <v>686665</v>
+        <v>686682</v>
       </c>
       <c r="R63" t="n">
-        <v>6563014</v>
+        <v>6563034</v>
       </c>
       <c r="S63" t="n">
         <v>10</v>
@@ -7456,17 +7457,17 @@
       </c>
       <c r="Y63" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AA63" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2023-12-19</t>
         </is>
       </c>
       <c r="AC63" t="inlineStr">
         <is>
-          <t>På¨levande tall.</t>
+          <t>På två levande tallar.</t>
         </is>
       </c>
       <c r="AD63" t="b">
@@ -7493,13 +7494,13 @@
       <c r="AY63" t="inlineStr"/>
       <c r="AZ63" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129563617</t>
+          <t>https://artportalen.se/Sighting/113689593</t>
         </is>
       </c>
     </row>
     <row r="64">
       <c r="A64" t="n">
-        <v>129563797</v>
+        <v>129563617</v>
       </c>
       <c r="B64" t="n">
         <v>90946</v>
@@ -7537,10 +7538,10 @@
         </is>
       </c>
       <c r="Q64" t="n">
-        <v>686675</v>
+        <v>686665</v>
       </c>
       <c r="R64" t="n">
-        <v>6563032</v>
+        <v>6563014</v>
       </c>
       <c r="S64" t="n">
         <v>10</v>
@@ -7577,7 +7578,7 @@
       </c>
       <c r="AC64" t="inlineStr">
         <is>
-          <t>På levande tall. Återfynd, rapporterad 2023.</t>
+          <t>På¨levande tall.</t>
         </is>
       </c>
       <c r="AD64" t="b">
@@ -7604,13 +7605,13 @@
       <c r="AY64" t="inlineStr"/>
       <c r="AZ64" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129563797</t>
+          <t>https://artportalen.se/Sighting/129563617</t>
         </is>
       </c>
     </row>
     <row r="65">
       <c r="A65" t="n">
-        <v>129563832</v>
+        <v>129563797</v>
       </c>
       <c r="B65" t="n">
         <v>90946</v>
@@ -7648,10 +7649,10 @@
         </is>
       </c>
       <c r="Q65" t="n">
-        <v>686685</v>
+        <v>686675</v>
       </c>
       <c r="R65" t="n">
-        <v>6563036</v>
+        <v>6563032</v>
       </c>
       <c r="S65" t="n">
         <v>10</v>
@@ -7688,7 +7689,7 @@
       </c>
       <c r="AC65" t="inlineStr">
         <is>
-          <t>På död tall. Återfynd, rapporterad 2023.</t>
+          <t>På levande tall. Återfynd, rapporterad 2023.</t>
         </is>
       </c>
       <c r="AD65" t="b">
@@ -7715,13 +7716,13 @@
       <c r="AY65" t="inlineStr"/>
       <c r="AZ65" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129563832</t>
+          <t>https://artportalen.se/Sighting/129563797</t>
         </is>
       </c>
     </row>
     <row r="66">
       <c r="A66" t="n">
-        <v>129564415</v>
+        <v>129563832</v>
       </c>
       <c r="B66" t="n">
         <v>90946</v>
@@ -7759,10 +7760,10 @@
         </is>
       </c>
       <c r="Q66" t="n">
-        <v>686657</v>
+        <v>686685</v>
       </c>
       <c r="R66" t="n">
-        <v>6563135</v>
+        <v>6563036</v>
       </c>
       <c r="S66" t="n">
         <v>10</v>
@@ -7799,7 +7800,7 @@
       </c>
       <c r="AC66" t="inlineStr">
         <is>
-          <t>På smal och hög levande tall.</t>
+          <t>På död tall. Återfynd, rapporterad 2023.</t>
         </is>
       </c>
       <c r="AD66" t="b">
@@ -7826,13 +7827,13 @@
       <c r="AY66" t="inlineStr"/>
       <c r="AZ66" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129564415</t>
+          <t>https://artportalen.se/Sighting/129563832</t>
         </is>
       </c>
     </row>
     <row r="67">
       <c r="A67" t="n">
-        <v>129565002</v>
+        <v>129564415</v>
       </c>
       <c r="B67" t="n">
         <v>90946</v>
@@ -7870,10 +7871,10 @@
         </is>
       </c>
       <c r="Q67" t="n">
-        <v>686675</v>
+        <v>686657</v>
       </c>
       <c r="R67" t="n">
-        <v>6563225</v>
+        <v>6563135</v>
       </c>
       <c r="S67" t="n">
         <v>10</v>
@@ -7908,6 +7909,11 @@
           <t>2025-11-06</t>
         </is>
       </c>
+      <c r="AC67" t="inlineStr">
+        <is>
+          <t>På smal och hög levande tall.</t>
+        </is>
+      </c>
       <c r="AD67" t="b">
         <v>0</v>
       </c>
@@ -7932,16 +7938,16 @@
       <c r="AY67" t="inlineStr"/>
       <c r="AZ67" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129565002</t>
+          <t>https://artportalen.se/Sighting/129564415</t>
         </is>
       </c>
     </row>
     <row r="68">
       <c r="A68" t="n">
-        <v>129214787</v>
+        <v>129565002</v>
       </c>
       <c r="B68" t="n">
-        <v>91909</v>
+        <v>90946</v>
       </c>
       <c r="D68" t="inlineStr">
         <is>
@@ -7949,21 +7955,21 @@
         </is>
       </c>
       <c r="E68" t="n">
-        <v>1202</v>
+        <v>889</v>
       </c>
       <c r="F68" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G68" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H68" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I68" t="inlineStr"/>
@@ -7976,10 +7982,10 @@
         </is>
       </c>
       <c r="Q68" t="n">
-        <v>686486</v>
+        <v>686675</v>
       </c>
       <c r="R68" t="n">
-        <v>6562977</v>
+        <v>6563225</v>
       </c>
       <c r="S68" t="n">
         <v>10</v>
@@ -8006,12 +8012,12 @@
       </c>
       <c r="Y68" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA68" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD68" t="b">
@@ -8038,38 +8044,38 @@
       <c r="AY68" t="inlineStr"/>
       <c r="AZ68" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129214787</t>
+          <t>https://artportalen.se/Sighting/129565002</t>
         </is>
       </c>
     </row>
     <row r="69">
       <c r="A69" t="n">
-        <v>129736615</v>
+        <v>129214787</v>
       </c>
       <c r="B69" t="n">
-        <v>91923</v>
+        <v>91909</v>
       </c>
       <c r="D69" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E69" t="n">
-        <v>1204</v>
+        <v>1202</v>
       </c>
       <c r="F69" t="inlineStr">
         <is>
-          <t>Gränsticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G69" t="inlineStr">
         <is>
-          <t>Phellopilus nigrolimitatus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H69" t="inlineStr">
         <is>
-          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I69" t="inlineStr"/>
@@ -8082,10 +8088,10 @@
         </is>
       </c>
       <c r="Q69" t="n">
-        <v>686778</v>
+        <v>686486</v>
       </c>
       <c r="R69" t="n">
-        <v>6563279</v>
+        <v>6562977</v>
       </c>
       <c r="S69" t="n">
         <v>10</v>
@@ -8112,17 +8118,12 @@
       </c>
       <c r="Y69" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA69" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="AC69" t="inlineStr">
-        <is>
-          <t>Precis på gränsen Tyresta NP. Lågan lika mycket innanför som utanför.</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD69" t="b">
@@ -8149,16 +8150,16 @@
       <c r="AY69" t="inlineStr"/>
       <c r="AZ69" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129736615</t>
+          <t>https://artportalen.se/Sighting/129214787</t>
         </is>
       </c>
     </row>
     <row r="70">
       <c r="A70" t="n">
-        <v>128886693</v>
+        <v>129736615</v>
       </c>
       <c r="B70" t="n">
-        <v>90659</v>
+        <v>91923</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8166,21 +8167,21 @@
         </is>
       </c>
       <c r="E70" t="n">
-        <v>1593</v>
+        <v>1204</v>
       </c>
       <c r="F70" t="inlineStr">
         <is>
-          <t>Lakritsmusseron</t>
+          <t>Gränsticka</t>
         </is>
       </c>
       <c r="G70" t="inlineStr">
         <is>
-          <t>Tricholoma apium</t>
+          <t>Phellopilus nigrolimitatus</t>
         </is>
       </c>
       <c r="H70" t="inlineStr">
         <is>
-          <t>Jul.Schäff.</t>
+          <t>(Romell) Niemelä, T.Wagner &amp; M.Fisch.</t>
         </is>
       </c>
       <c r="I70" t="inlineStr"/>
@@ -8193,10 +8194,10 @@
         </is>
       </c>
       <c r="Q70" t="n">
-        <v>686640</v>
+        <v>686778</v>
       </c>
       <c r="R70" t="n">
-        <v>6563199</v>
+        <v>6563279</v>
       </c>
       <c r="S70" t="n">
         <v>10</v>
@@ -8223,12 +8224,17 @@
       </c>
       <c r="Y70" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="AA70" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-11-17</t>
+        </is>
+      </c>
+      <c r="AC70" t="inlineStr">
+        <is>
+          <t>Precis på gränsen Tyresta NP. Lågan lika mycket innanför som utanför.</t>
         </is>
       </c>
       <c r="AD70" t="b">
@@ -8255,38 +8261,38 @@
       <c r="AY70" t="inlineStr"/>
       <c r="AZ70" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128886693</t>
+          <t>https://artportalen.se/Sighting/129736615</t>
         </is>
       </c>
     </row>
     <row r="71">
       <c r="A71" t="n">
-        <v>122435803</v>
+        <v>128886693</v>
       </c>
       <c r="B71" t="n">
-        <v>92632</v>
+        <v>90659</v>
       </c>
       <c r="D71" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E71" t="n">
-        <v>3298</v>
+        <v>1593</v>
       </c>
       <c r="F71" t="inlineStr">
         <is>
-          <t>Trådticka</t>
+          <t>Lakritsmusseron</t>
         </is>
       </c>
       <c r="G71" t="inlineStr">
         <is>
-          <t>Climacocystis borealis</t>
+          <t>Tricholoma apium</t>
         </is>
       </c>
       <c r="H71" t="inlineStr">
         <is>
-          <t>(Fr.) Kotl. &amp; Pouzar</t>
+          <t>Jul.Schäff.</t>
         </is>
       </c>
       <c r="I71" t="inlineStr"/>
@@ -8295,14 +8301,14 @@
       <c r="N71" t="inlineStr"/>
       <c r="P71" t="inlineStr">
         <is>
-          <t>SV Norrby Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q71" t="n">
-        <v>686469</v>
+        <v>686640</v>
       </c>
       <c r="R71" t="n">
-        <v>6563016</v>
+        <v>6563199</v>
       </c>
       <c r="S71" t="n">
         <v>10</v>
@@ -8329,12 +8335,12 @@
       </c>
       <c r="Y71" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA71" t="inlineStr">
         <is>
-          <t>2025-02-02</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD71" t="b">
@@ -8361,51 +8367,54 @@
       <c r="AY71" t="inlineStr"/>
       <c r="AZ71" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122435803</t>
+          <t>https://artportalen.se/Sighting/128886693</t>
         </is>
       </c>
     </row>
     <row r="72">
       <c r="A72" t="n">
-        <v>121859626</v>
+        <v>122435803</v>
       </c>
       <c r="B72" t="n">
-        <v>91930</v>
+        <v>92632</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E72" t="n">
-        <v>5442</v>
+        <v>3298</v>
       </c>
       <c r="F72" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Trådticka</t>
         </is>
       </c>
       <c r="G72" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Climacocystis borealis</t>
         </is>
       </c>
       <c r="H72" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
+          <t>(Fr.) Kotl. &amp; Pouzar</t>
         </is>
       </c>
       <c r="I72" t="inlineStr"/>
+      <c r="J72" t="inlineStr"/>
+      <c r="K72" t="inlineStr"/>
+      <c r="N72" t="inlineStr"/>
       <c r="P72" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>SV Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q72" t="n">
-        <v>686670</v>
+        <v>686469</v>
       </c>
       <c r="R72" t="n">
-        <v>6563032</v>
+        <v>6563016</v>
       </c>
       <c r="S72" t="n">
         <v>10</v>
@@ -8432,22 +8441,12 @@
       </c>
       <c r="Y72" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z72" t="inlineStr">
-        <is>
-          <t>17:20</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AA72" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB72" t="inlineStr">
-        <is>
-          <t>17:20</t>
+          <t>2025-02-02</t>
         </is>
       </c>
       <c r="AD72" t="b">
@@ -8456,50 +8455,31 @@
       <c r="AE72" t="b">
         <v>0</v>
       </c>
+      <c r="AF72" t="inlineStr"/>
       <c r="AG72" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ72" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK72" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL72" t="inlineStr">
-        <is>
-          <t>Levande äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO72" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Levande äldre tall.</t>
-        </is>
       </c>
       <c r="AT72" t="inlineStr"/>
       <c r="AW72" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX72" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY72" t="inlineStr"/>
       <c r="AZ72" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859626</t>
+          <t>https://artportalen.se/Sighting/122435803</t>
         </is>
       </c>
     </row>
     <row r="73">
       <c r="A73" t="n">
-        <v>128457948</v>
+        <v>121859626</v>
       </c>
       <c r="B73" t="n">
         <v>91930</v>
@@ -8528,19 +8508,16 @@
         </is>
       </c>
       <c r="I73" t="inlineStr"/>
-      <c r="J73" t="inlineStr"/>
-      <c r="K73" t="inlineStr"/>
-      <c r="N73" t="inlineStr"/>
       <c r="P73" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q73" t="n">
-        <v>686513</v>
+        <v>686670</v>
       </c>
       <c r="R73" t="n">
-        <v>6563109</v>
+        <v>6563032</v>
       </c>
       <c r="S73" t="n">
         <v>10</v>
@@ -8567,12 +8544,22 @@
       </c>
       <c r="Y73" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z73" t="inlineStr">
+        <is>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA73" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB73" t="inlineStr">
+        <is>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD73" t="b">
@@ -8581,31 +8568,50 @@
       <c r="AE73" t="b">
         <v>0</v>
       </c>
-      <c r="AF73" t="inlineStr"/>
       <c r="AG73" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ73" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL73" t="inlineStr">
+        <is>
+          <t>Levande äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO73" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Levande äldre tall.</t>
+        </is>
       </c>
       <c r="AT73" t="inlineStr"/>
       <c r="AW73" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX73" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY73" t="inlineStr"/>
       <c r="AZ73" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128457948</t>
+          <t>https://artportalen.se/Sighting/121859626</t>
         </is>
       </c>
     </row>
     <row r="74">
       <c r="A74" t="n">
-        <v>129564462</v>
+        <v>128457948</v>
       </c>
       <c r="B74" t="n">
         <v>91930</v>
@@ -8633,11 +8639,7 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I74" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I74" t="inlineStr"/>
       <c r="J74" t="inlineStr"/>
       <c r="K74" t="inlineStr"/>
       <c r="N74" t="inlineStr"/>
@@ -8647,10 +8649,10 @@
         </is>
       </c>
       <c r="Q74" t="n">
-        <v>686728</v>
+        <v>686513</v>
       </c>
       <c r="R74" t="n">
-        <v>6563110</v>
+        <v>6563109</v>
       </c>
       <c r="S74" t="n">
         <v>10</v>
@@ -8677,17 +8679,12 @@
       </c>
       <c r="Y74" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA74" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AC74" t="inlineStr">
-        <is>
-          <t>Död tallticka på död tallraka.</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD74" t="b">
@@ -8714,13 +8711,13 @@
       <c r="AY74" t="inlineStr"/>
       <c r="AZ74" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129564462</t>
+          <t>https://artportalen.se/Sighting/128457948</t>
         </is>
       </c>
     </row>
     <row r="75">
       <c r="A75" t="n">
-        <v>129564997</v>
+        <v>129564462</v>
       </c>
       <c r="B75" t="n">
         <v>91930</v>
@@ -8748,7 +8745,11 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I75" t="inlineStr"/>
+      <c r="I75" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J75" t="inlineStr"/>
       <c r="K75" t="inlineStr"/>
       <c r="N75" t="inlineStr"/>
@@ -8758,10 +8759,10 @@
         </is>
       </c>
       <c r="Q75" t="n">
-        <v>686661</v>
+        <v>686728</v>
       </c>
       <c r="R75" t="n">
-        <v>6563208</v>
+        <v>6563110</v>
       </c>
       <c r="S75" t="n">
         <v>10</v>
@@ -8796,6 +8797,11 @@
           <t>2025-11-06</t>
         </is>
       </c>
+      <c r="AC75" t="inlineStr">
+        <is>
+          <t>Död tallticka på död tallraka.</t>
+        </is>
+      </c>
       <c r="AD75" t="b">
         <v>0</v>
       </c>
@@ -8820,13 +8826,13 @@
       <c r="AY75" t="inlineStr"/>
       <c r="AZ75" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129564997</t>
+          <t>https://artportalen.se/Sighting/129564462</t>
         </is>
       </c>
     </row>
     <row r="76">
       <c r="A76" t="n">
-        <v>129591539</v>
+        <v>129564997</v>
       </c>
       <c r="B76" t="n">
         <v>91930</v>
@@ -8864,10 +8870,10 @@
         </is>
       </c>
       <c r="Q76" t="n">
-        <v>686710</v>
+        <v>686661</v>
       </c>
       <c r="R76" t="n">
-        <v>6563231</v>
+        <v>6563208</v>
       </c>
       <c r="S76" t="n">
         <v>10</v>
@@ -8894,12 +8900,12 @@
       </c>
       <c r="Y76" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA76" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD76" t="b">
@@ -8926,13 +8932,13 @@
       <c r="AY76" t="inlineStr"/>
       <c r="AZ76" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129591539</t>
+          <t>https://artportalen.se/Sighting/129564997</t>
         </is>
       </c>
     </row>
     <row r="77">
       <c r="A77" t="n">
-        <v>129591551</v>
+        <v>129591539</v>
       </c>
       <c r="B77" t="n">
         <v>91930</v>
@@ -8973,7 +8979,7 @@
         <v>686710</v>
       </c>
       <c r="R77" t="n">
-        <v>6563248</v>
+        <v>6563231</v>
       </c>
       <c r="S77" t="n">
         <v>10</v>
@@ -9032,38 +9038,38 @@
       <c r="AY77" t="inlineStr"/>
       <c r="AZ77" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129591551</t>
+          <t>https://artportalen.se/Sighting/129591539</t>
         </is>
       </c>
     </row>
     <row r="78">
       <c r="A78" t="n">
-        <v>129230377</v>
+        <v>129591551</v>
       </c>
       <c r="B78" t="n">
-        <v>91872</v>
+        <v>91930</v>
       </c>
       <c r="D78" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E78" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F78" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G78" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H78" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I78" t="inlineStr"/>
@@ -9076,10 +9082,10 @@
         </is>
       </c>
       <c r="Q78" t="n">
-        <v>686662</v>
+        <v>686710</v>
       </c>
       <c r="R78" t="n">
-        <v>6563219</v>
+        <v>6563248</v>
       </c>
       <c r="S78" t="n">
         <v>10</v>
@@ -9106,12 +9112,12 @@
       </c>
       <c r="Y78" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA78" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD78" t="b">
@@ -9138,13 +9144,13 @@
       <c r="AY78" t="inlineStr"/>
       <c r="AZ78" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129230377</t>
+          <t>https://artportalen.se/Sighting/129591551</t>
         </is>
       </c>
     </row>
     <row r="79">
       <c r="A79" t="n">
-        <v>129230409</v>
+        <v>129230377</v>
       </c>
       <c r="B79" t="n">
         <v>91872</v>
@@ -9182,10 +9188,10 @@
         </is>
       </c>
       <c r="Q79" t="n">
-        <v>686777</v>
+        <v>686662</v>
       </c>
       <c r="R79" t="n">
-        <v>6563285</v>
+        <v>6563219</v>
       </c>
       <c r="S79" t="n">
         <v>10</v>
@@ -9244,38 +9250,38 @@
       <c r="AY79" t="inlineStr"/>
       <c r="AZ79" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129230409</t>
+          <t>https://artportalen.se/Sighting/129230377</t>
         </is>
       </c>
     </row>
     <row r="80">
       <c r="A80" t="n">
-        <v>128886665</v>
+        <v>129230409</v>
       </c>
       <c r="B80" t="n">
-        <v>93223</v>
+        <v>91872</v>
       </c>
       <c r="D80" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E80" t="n">
-        <v>5448</v>
+        <v>5447</v>
       </c>
       <c r="F80" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G80" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H80" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I80" t="inlineStr"/>
@@ -9288,10 +9294,10 @@
         </is>
       </c>
       <c r="Q80" t="n">
-        <v>686681</v>
+        <v>686777</v>
       </c>
       <c r="R80" t="n">
-        <v>6563136</v>
+        <v>6563285</v>
       </c>
       <c r="S80" t="n">
         <v>10</v>
@@ -9318,12 +9324,12 @@
       </c>
       <c r="Y80" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA80" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD80" t="b">
@@ -9350,16 +9356,16 @@
       <c r="AY80" t="inlineStr"/>
       <c r="AZ80" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128886665</t>
+          <t>https://artportalen.se/Sighting/129230409</t>
         </is>
       </c>
     </row>
     <row r="81">
       <c r="A81" t="n">
-        <v>128342127</v>
+        <v>128886665</v>
       </c>
       <c r="B81" t="n">
-        <v>93235</v>
+        <v>93223</v>
       </c>
       <c r="D81" t="inlineStr">
         <is>
@@ -9367,21 +9373,21 @@
         </is>
       </c>
       <c r="E81" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F81" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G81" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H81" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I81" t="inlineStr"/>
@@ -9394,10 +9400,10 @@
         </is>
       </c>
       <c r="Q81" t="n">
-        <v>686643</v>
+        <v>686681</v>
       </c>
       <c r="R81" t="n">
-        <v>6563078</v>
+        <v>6563136</v>
       </c>
       <c r="S81" t="n">
         <v>10</v>
@@ -9424,12 +9430,12 @@
       </c>
       <c r="Y81" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA81" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD81" t="b">
@@ -9456,13 +9462,13 @@
       <c r="AY81" t="inlineStr"/>
       <c r="AZ81" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128342127</t>
+          <t>https://artportalen.se/Sighting/128886665</t>
         </is>
       </c>
     </row>
     <row r="82">
       <c r="A82" t="n">
-        <v>128457671</v>
+        <v>128342127</v>
       </c>
       <c r="B82" t="n">
         <v>93235</v>
@@ -9500,10 +9506,10 @@
         </is>
       </c>
       <c r="Q82" t="n">
-        <v>686516</v>
+        <v>686643</v>
       </c>
       <c r="R82" t="n">
-        <v>6563005</v>
+        <v>6563078</v>
       </c>
       <c r="S82" t="n">
         <v>10</v>
@@ -9530,12 +9536,12 @@
       </c>
       <c r="Y82" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA82" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD82" t="b">
@@ -9562,13 +9568,13 @@
       <c r="AY82" t="inlineStr"/>
       <c r="AZ82" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128457671</t>
+          <t>https://artportalen.se/Sighting/128342127</t>
         </is>
       </c>
     </row>
     <row r="83">
       <c r="A83" t="n">
-        <v>128457697</v>
+        <v>128457671</v>
       </c>
       <c r="B83" t="n">
         <v>93235</v>
@@ -9606,10 +9612,10 @@
         </is>
       </c>
       <c r="Q83" t="n">
-        <v>686585</v>
+        <v>686516</v>
       </c>
       <c r="R83" t="n">
-        <v>6563030</v>
+        <v>6563005</v>
       </c>
       <c r="S83" t="n">
         <v>10</v>
@@ -9668,13 +9674,13 @@
       <c r="AY83" t="inlineStr"/>
       <c r="AZ83" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128457697</t>
+          <t>https://artportalen.se/Sighting/128457671</t>
         </is>
       </c>
     </row>
     <row r="84">
       <c r="A84" t="n">
-        <v>128457855</v>
+        <v>128457697</v>
       </c>
       <c r="B84" t="n">
         <v>93235</v>
@@ -9712,10 +9718,10 @@
         </is>
       </c>
       <c r="Q84" t="n">
-        <v>686750</v>
+        <v>686585</v>
       </c>
       <c r="R84" t="n">
-        <v>6563149</v>
+        <v>6563030</v>
       </c>
       <c r="S84" t="n">
         <v>10</v>
@@ -9774,13 +9780,13 @@
       <c r="AY84" t="inlineStr"/>
       <c r="AZ84" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128457855</t>
+          <t>https://artportalen.se/Sighting/128457697</t>
         </is>
       </c>
     </row>
     <row r="85">
       <c r="A85" t="n">
-        <v>128457938</v>
+        <v>128457855</v>
       </c>
       <c r="B85" t="n">
         <v>93235</v>
@@ -9818,10 +9824,10 @@
         </is>
       </c>
       <c r="Q85" t="n">
-        <v>686520</v>
+        <v>686750</v>
       </c>
       <c r="R85" t="n">
-        <v>6563068</v>
+        <v>6563149</v>
       </c>
       <c r="S85" t="n">
         <v>10</v>
@@ -9880,13 +9886,13 @@
       <c r="AY85" t="inlineStr"/>
       <c r="AZ85" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128457938</t>
+          <t>https://artportalen.se/Sighting/128457855</t>
         </is>
       </c>
     </row>
     <row r="86">
       <c r="A86" t="n">
-        <v>128510579</v>
+        <v>128457938</v>
       </c>
       <c r="B86" t="n">
         <v>93235</v>
@@ -9924,10 +9930,10 @@
         </is>
       </c>
       <c r="Q86" t="n">
-        <v>686754</v>
+        <v>686520</v>
       </c>
       <c r="R86" t="n">
-        <v>6563192</v>
+        <v>6563068</v>
       </c>
       <c r="S86" t="n">
         <v>10</v>
@@ -9954,12 +9960,12 @@
       </c>
       <c r="Y86" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA86" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD86" t="b">
@@ -9986,38 +9992,38 @@
       <c r="AY86" t="inlineStr"/>
       <c r="AZ86" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128510579</t>
+          <t>https://artportalen.se/Sighting/128457938</t>
         </is>
       </c>
     </row>
     <row r="87">
       <c r="A87" t="n">
-        <v>128646813</v>
+        <v>128510579</v>
       </c>
       <c r="B87" t="n">
-        <v>92567</v>
+        <v>93235</v>
       </c>
       <c r="D87" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E87" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F87" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G87" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H87" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I87" t="inlineStr"/>
@@ -10030,10 +10036,10 @@
         </is>
       </c>
       <c r="Q87" t="n">
-        <v>686827</v>
+        <v>686754</v>
       </c>
       <c r="R87" t="n">
-        <v>6563224</v>
+        <v>6563192</v>
       </c>
       <c r="S87" t="n">
         <v>10</v>
@@ -10060,12 +10066,12 @@
       </c>
       <c r="Y87" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA87" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD87" t="b">
@@ -10092,58 +10098,54 @@
       <c r="AY87" t="inlineStr"/>
       <c r="AZ87" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128646813</t>
+          <t>https://artportalen.se/Sighting/128510579</t>
         </is>
       </c>
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>112337759</v>
+        <v>128646813</v>
       </c>
       <c r="B88" t="n">
-        <v>90691</v>
+        <v>92567</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E88" t="n">
-        <v>6276</v>
+        <v>6031</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Wulfen:Fr.) Fr.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr"/>
       <c r="J88" t="inlineStr"/>
       <c r="K88" t="inlineStr"/>
       <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Norrby Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>686738</v>
+        <v>686827</v>
       </c>
       <c r="R88" t="n">
-        <v>6563118</v>
+        <v>6563224</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10170,12 +10172,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10202,16 +10204,16 @@
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112337759</t>
+          <t>https://artportalen.se/Sighting/128646813</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>129591415</v>
+        <v>112337759</v>
       </c>
       <c r="B89" t="n">
-        <v>79327</v>
+        <v>90691</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10219,37 +10221,41 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>6425</v>
+        <v>6276</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
       <c r="P89" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>686678</v>
+        <v>686738</v>
       </c>
       <c r="R89" t="n">
-        <v>6563229</v>
+        <v>6563118</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10276,17 +10282,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC89" t="inlineStr">
-        <is>
-          <t>På tallstam samt några delar av bålen som lossnat och hamnat på en liten gran.</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10313,38 +10314,38 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129591415</t>
+          <t>https://artportalen.se/Sighting/112337759</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>96643356</v>
+        <v>129591415</v>
       </c>
       <c r="B90" t="n">
-        <v>79351</v>
+        <v>79327</v>
       </c>
       <c r="D90" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E90" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F90" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G90" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H90" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I90" t="inlineStr"/>
@@ -10353,14 +10354,14 @@
       <c r="N90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>Norrby mosse S om, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>686692</v>
+        <v>686678</v>
       </c>
       <c r="R90" t="n">
-        <v>6563028</v>
+        <v>6563229</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10387,12 +10388,17 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC90" t="inlineStr">
+        <is>
+          <t>På tallstam samt några delar av bålen som lossnat och hamnat på en liten gran.</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10408,24 +10414,24 @@
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96643356</t>
+          <t>https://artportalen.se/Sighting/129591415</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>97239536</v>
+        <v>96643356</v>
       </c>
       <c r="B91" t="n">
         <v>79351</v>
@@ -10459,17 +10465,17 @@
       <c r="N91" t="inlineStr"/>
       <c r="P91" t="inlineStr">
         <is>
-          <t>S Norrby mosse, Srm</t>
+          <t>Norrby mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>686697</v>
+        <v>686692</v>
       </c>
       <c r="R91" t="n">
-        <v>6563033</v>
+        <v>6563028</v>
       </c>
       <c r="S91" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T91" t="inlineStr">
         <is>
@@ -10493,27 +10499,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="Z91" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="AB91" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC91" t="inlineStr">
-        <is>
-          <t>Förevisade av Bodil och Ulf</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10529,24 +10520,24 @@
       <c r="AT91" t="inlineStr"/>
       <c r="AW91" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX91" t="inlineStr">
         <is>
-          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97239536</t>
+          <t>https://artportalen.se/Sighting/96643356</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>106813853</v>
+        <v>97239536</v>
       </c>
       <c r="B92" t="n">
         <v>79351</v>
@@ -10580,17 +10571,17 @@
       <c r="N92" t="inlineStr"/>
       <c r="P92" t="inlineStr">
         <is>
-          <t>Österhaninge, Srm</t>
+          <t>S Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>686702</v>
+        <v>686697</v>
       </c>
       <c r="R92" t="n">
-        <v>6563040</v>
+        <v>6563033</v>
       </c>
       <c r="S92" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T92" t="inlineStr">
         <is>
@@ -10617,9 +10608,24 @@
           <t>2021-11-20</t>
         </is>
       </c>
+      <c r="Z92" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
       <c r="AA92" t="inlineStr">
         <is>
           <t>2021-11-20</t>
+        </is>
+      </c>
+      <c r="AB92" t="inlineStr">
+        <is>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Förevisade av Bodil och Ulf</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10632,21 +10638,6 @@
       <c r="AG92" t="b">
         <v>0</v>
       </c>
-      <c r="AI92" t="inlineStr">
-        <is>
-          <t>tallhällmark, på bark av Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AP92" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR92" t="inlineStr">
-        <is>
-          <t>21-1065</t>
-        </is>
-      </c>
       <c r="AT92" t="inlineStr"/>
       <c r="AW92" t="inlineStr">
         <is>
@@ -10655,19 +10646,19 @@
       </c>
       <c r="AX92" t="inlineStr">
         <is>
-          <t>Thomas Strid, Göran Odelvik, Tiina Laantee, Ulf Johansson, Bodil Ravn</t>
+          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
         </is>
       </c>
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106813853</t>
+          <t>https://artportalen.se/Sighting/97239536</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>121859628</v>
+        <v>106813853</v>
       </c>
       <c r="B93" t="n">
         <v>79351</v>
@@ -10696,16 +10687,19 @@
         </is>
       </c>
       <c r="I93" t="inlineStr"/>
+      <c r="J93" t="inlineStr"/>
+      <c r="K93" t="inlineStr"/>
+      <c r="N93" t="inlineStr"/>
       <c r="P93" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>Österhaninge, Srm</t>
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>686697</v>
+        <v>686702</v>
       </c>
       <c r="R93" t="n">
-        <v>6563030</v>
+        <v>6563040</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10732,22 +10726,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z93" t="inlineStr">
-        <is>
-          <t>17:09</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB93" t="inlineStr">
-        <is>
-          <t>17:09</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10756,53 +10740,49 @@
       <c r="AE93" t="b">
         <v>0</v>
       </c>
+      <c r="AF93" t="inlineStr"/>
       <c r="AG93" t="b">
         <v>0</v>
       </c>
-      <c r="AJ93" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL93" t="inlineStr">
-        <is>
-          <t>Levande äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO93" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Levande äldre tall.</t>
+      <c r="AI93" t="inlineStr">
+        <is>
+          <t>tallhällmark, på bark av Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AP93" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR93" t="inlineStr">
+        <is>
+          <t>21-1065</t>
         </is>
       </c>
       <c r="AT93" t="inlineStr"/>
       <c r="AW93" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX93" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Thomas Strid, Göran Odelvik, Tiina Laantee, Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859628</t>
+          <t>https://artportalen.se/Sighting/106813853</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>121859622</v>
+        <v>121859628</v>
       </c>
       <c r="B94" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
@@ -10810,42 +10790,34 @@
         </is>
       </c>
       <c r="E94" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
-      <c r="K94" t="inlineStr"/>
-      <c r="L94" t="inlineStr"/>
-      <c r="M94" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
-      <c r="N94" t="inlineStr"/>
       <c r="P94" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>686574</v>
+        <v>686697</v>
       </c>
       <c r="R94" t="n">
-        <v>6562988</v>
+        <v>6563030</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10877,7 +10849,7 @@
       </c>
       <c r="Z94" t="inlineStr">
         <is>
-          <t>17:37</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
@@ -10887,12 +10859,7 @@
       </c>
       <c r="AB94" t="inlineStr">
         <is>
-          <t>17:37</t>
-        </is>
-      </c>
-      <c r="AC94" t="inlineStr">
-        <is>
-          <t>Födosökshack långt ner på stående död tall.</t>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10903,6 +10870,26 @@
       </c>
       <c r="AG94" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ94" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL94" t="inlineStr">
+        <is>
+          <t>Levande äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO94" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Levande äldre tall.</t>
+        </is>
       </c>
       <c r="AT94" t="inlineStr"/>
       <c r="AW94" t="inlineStr">
@@ -10918,13 +10905,13 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859622</t>
+          <t>https://artportalen.se/Sighting/121859628</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>122929399</v>
+        <v>121859622</v>
       </c>
       <c r="B95" t="n">
         <v>57950</v>
@@ -10952,28 +10939,28 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I95" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+      <c r="I95" t="inlineStr"/>
       <c r="K95" t="inlineStr"/>
       <c r="L95" t="inlineStr"/>
-      <c r="M95" t="inlineStr"/>
+      <c r="M95" t="inlineStr">
+        <is>
+          <t>äldre spår</t>
+        </is>
+      </c>
       <c r="N95" t="inlineStr"/>
       <c r="P95" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>686567</v>
+        <v>686574</v>
       </c>
       <c r="R95" t="n">
-        <v>6562954</v>
+        <v>6562988</v>
       </c>
       <c r="S95" t="n">
-        <v>13</v>
+        <v>10</v>
       </c>
       <c r="T95" t="inlineStr">
         <is>
@@ -10997,22 +10984,27 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="Z95" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2024-05-09</t>
         </is>
       </c>
       <c r="AB95" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AC95" t="inlineStr">
+        <is>
+          <t>Födosökshack långt ner på stående död tall.</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11027,27 +11019,27 @@
       <c r="AT95" t="inlineStr"/>
       <c r="AW95" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX95" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929399</t>
+          <t>https://artportalen.se/Sighting/121859622</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>126418797</v>
+        <v>122929399</v>
       </c>
       <c r="B96" t="n">
-        <v>56895</v>
+        <v>57950</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11055,16 +11047,16 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>100088</v>
+        <v>100049</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
@@ -11077,24 +11069,23 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J96" t="inlineStr"/>
       <c r="K96" t="inlineStr"/>
       <c r="L96" t="inlineStr"/>
       <c r="M96" t="inlineStr"/>
       <c r="N96" t="inlineStr"/>
       <c r="P96" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>686803</v>
+        <v>686567</v>
       </c>
       <c r="R96" t="n">
-        <v>6563297</v>
+        <v>6562954</v>
       </c>
       <c r="S96" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T96" t="inlineStr">
         <is>
@@ -11118,12 +11109,22 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z96" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB96" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11132,34 +11133,33 @@
       <c r="AE96" t="b">
         <v>0</v>
       </c>
-      <c r="AF96" t="inlineStr"/>
       <c r="AG96" t="b">
         <v>0</v>
       </c>
       <c r="AT96" t="inlineStr"/>
       <c r="AW96" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX96" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418797</t>
+          <t>https://artportalen.se/Sighting/122929399</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>134100841</v>
+        <v>126418797</v>
       </c>
       <c r="B97" t="n">
-        <v>56915</v>
+        <v>56895</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11200,10 +11200,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>686486</v>
+        <v>686803</v>
       </c>
       <c r="R97" t="n">
-        <v>6563086</v>
+        <v>6563297</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11230,12 +11230,12 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11262,16 +11262,16 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134100841</t>
+          <t>https://artportalen.se/Sighting/126418797</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>121859623</v>
+        <v>134100841</v>
       </c>
       <c r="B98" t="n">
-        <v>5179</v>
+        <v>56915</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
@@ -11279,39 +11279,43 @@
         </is>
       </c>
       <c r="E98" t="n">
-        <v>100526</v>
+        <v>100088</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
-        </is>
-      </c>
-      <c r="I98" t="inlineStr"/>
-      <c r="M98" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I98" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J98" t="inlineStr"/>
+      <c r="K98" t="inlineStr"/>
+      <c r="L98" t="inlineStr"/>
+      <c r="M98" t="inlineStr"/>
+      <c r="N98" t="inlineStr"/>
       <c r="P98" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>686581</v>
+        <v>686486</v>
       </c>
       <c r="R98" t="n">
-        <v>6562989</v>
+        <v>6563086</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11338,22 +11342,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z98" t="inlineStr">
-        <is>
-          <t>17:36</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB98" t="inlineStr">
-        <is>
-          <t>17:36</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11362,96 +11356,74 @@
       <c r="AE98" t="b">
         <v>0</v>
       </c>
+      <c r="AF98" t="inlineStr"/>
       <c r="AG98" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ98" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK98" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL98" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO98" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT98" t="inlineStr"/>
       <c r="AW98" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX98" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859623</t>
+          <t>https://artportalen.se/Sighting/134100841</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128510434</v>
+        <v>121859623</v>
       </c>
       <c r="B99" t="n">
-        <v>58114</v>
+        <v>5179</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
-      <c r="K99" t="inlineStr"/>
-      <c r="L99" t="inlineStr"/>
       <c r="M99" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N99" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P99" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>686650</v>
+        <v>686581</v>
       </c>
       <c r="R99" t="n">
-        <v>6563214</v>
+        <v>6562989</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11478,12 +11450,22 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z99" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB99" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11494,28 +11476,48 @@
       </c>
       <c r="AG99" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ99" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK99" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL99" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO99" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT99" t="inlineStr"/>
       <c r="AW99" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX99" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128510434</t>
+          <t>https://artportalen.se/Sighting/121859623</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128886960</v>
+        <v>128510434</v>
       </c>
       <c r="B100" t="n">
         <v>58114</v>
@@ -11558,13 +11560,13 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>686792</v>
+        <v>686650</v>
       </c>
       <c r="R100" t="n">
-        <v>6563221</v>
+        <v>6563214</v>
       </c>
       <c r="S100" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T100" t="inlineStr">
         <is>
@@ -11588,12 +11590,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11619,13 +11621,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128886960</t>
+          <t>https://artportalen.se/Sighting/128510434</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>129230389</v>
+        <v>128886960</v>
       </c>
       <c r="B101" t="n">
         <v>58114</v>
@@ -11668,10 +11670,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>686793</v>
+        <v>686792</v>
       </c>
       <c r="R101" t="n">
-        <v>6563302</v>
+        <v>6563221</v>
       </c>
       <c r="S101" t="n">
         <v>25</v>
@@ -11698,12 +11700,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11729,13 +11731,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129230389</t>
+          <t>https://artportalen.se/Sighting/128886960</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>129591579</v>
+        <v>129230389</v>
       </c>
       <c r="B102" t="n">
         <v>58114</v>
@@ -11778,10 +11780,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>686618</v>
+        <v>686793</v>
       </c>
       <c r="R102" t="n">
-        <v>6563047</v>
+        <v>6563302</v>
       </c>
       <c r="S102" t="n">
         <v>25</v>
@@ -11808,12 +11810,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11839,16 +11841,16 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129591579</t>
+          <t>https://artportalen.se/Sighting/129230389</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>133115563</v>
+        <v>129591579</v>
       </c>
       <c r="B103" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
@@ -11878,7 +11880,7 @@
       <c r="L103" t="inlineStr"/>
       <c r="M103" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N103" t="inlineStr"/>
@@ -11888,13 +11890,13 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>686651</v>
+        <v>686618</v>
       </c>
       <c r="R103" t="n">
-        <v>6563184</v>
+        <v>6563047</v>
       </c>
       <c r="S103" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T103" t="inlineStr">
         <is>
@@ -11918,12 +11920,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11949,55 +11951,59 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133115563</t>
+          <t>https://artportalen.se/Sighting/129591579</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>109890506</v>
+        <v>133115563</v>
       </c>
       <c r="B104" t="n">
-        <v>99118</v>
+        <v>58136</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I104" t="inlineStr"/>
-      <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="L104" t="inlineStr"/>
+      <c r="M104" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Ö Norrby Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>686831</v>
+        <v>686651</v>
       </c>
       <c r="R104" t="n">
-        <v>6563216</v>
+        <v>6563184</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -12024,12 +12030,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -12038,7 +12044,6 @@
       <c r="AE104" t="b">
         <v>0</v>
       </c>
-      <c r="AF104" t="inlineStr"/>
       <c r="AG104" t="b">
         <v>0</v>
       </c>
@@ -12056,13 +12061,13 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109890506</t>
+          <t>https://artportalen.se/Sighting/133115563</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>122781008</v>
+        <v>109890506</v>
       </c>
       <c r="B105" t="n">
         <v>99118</v>
@@ -12097,14 +12102,14 @@
       <c r="N105" t="inlineStr"/>
       <c r="P105" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>Ö Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>686833</v>
+        <v>686831</v>
       </c>
       <c r="R105" t="n">
-        <v>6563215</v>
+        <v>6563216</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12131,17 +12136,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>Knärot</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12157,24 +12157,24 @@
       <c r="AT105" t="inlineStr"/>
       <c r="AW105" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX105" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122781008</t>
+          <t>https://artportalen.se/Sighting/109890506</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>126418709</v>
+        <v>122781008</v>
       </c>
       <c r="B106" t="n">
         <v>99118</v>
@@ -12202,29 +12202,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I106" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J106" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I106" t="inlineStr"/>
+      <c r="J106" t="inlineStr"/>
       <c r="K106" t="inlineStr"/>
       <c r="L106" t="inlineStr"/>
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>686771</v>
+        <v>686833</v>
       </c>
       <c r="R106" t="n">
-        <v>6563297</v>
+        <v>6563215</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12251,17 +12243,17 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC106" t="inlineStr">
         <is>
-          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12277,24 +12269,24 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418709</t>
+          <t>https://artportalen.se/Sighting/122781008</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>126418756</v>
+        <v>126418709</v>
       </c>
       <c r="B107" t="n">
         <v>99118</v>
@@ -12324,7 +12316,7 @@
       </c>
       <c r="I107" t="inlineStr">
         <is>
-          <t>16</t>
+          <t>15</t>
         </is>
       </c>
       <c r="J107" t="inlineStr">
@@ -12341,10 +12333,10 @@
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>686781</v>
+        <v>686771</v>
       </c>
       <c r="R107" t="n">
-        <v>6563292</v>
+        <v>6563297</v>
       </c>
       <c r="S107" t="n">
         <v>10</v>
@@ -12381,7 +12373,7 @@
       </c>
       <c r="AC107" t="inlineStr">
         <is>
-          <t>En av dem i knopp.</t>
+          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12408,13 +12400,13 @@
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418756</t>
+          <t>https://artportalen.se/Sighting/126418709</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>129564285</v>
+        <v>126418756</v>
       </c>
       <c r="B108" t="n">
         <v>99118</v>
@@ -12442,8 +12434,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I108" t="inlineStr"/>
-      <c r="J108" t="inlineStr"/>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J108" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K108" t="inlineStr"/>
       <c r="L108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
@@ -12453,10 +12453,10 @@
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>686625</v>
+        <v>686781</v>
       </c>
       <c r="R108" t="n">
-        <v>6563000</v>
+        <v>6563292</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12483,12 +12483,17 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC108" t="inlineStr">
+        <is>
+          <t>En av dem i knopp.</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12515,63 +12520,55 @@
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129564285</t>
+          <t>https://artportalen.se/Sighting/126418756</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>126234373</v>
+        <v>129564285</v>
       </c>
       <c r="B109" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I109" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J109" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
       <c r="K109" t="inlineStr"/>
       <c r="L109" t="inlineStr"/>
       <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>686756</v>
+        <v>686625</v>
       </c>
       <c r="R109" t="n">
-        <v>6563092</v>
+        <v>6563000</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12598,12 +12595,12 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12619,27 +12616,27 @@
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234373</t>
+          <t>https://artportalen.se/Sighting/129564285</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>122929342</v>
+        <v>126234373</v>
       </c>
       <c r="B110" t="n">
-        <v>97986</v>
+        <v>106244</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12647,41 +12644,49 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>221946</v>
+        <v>221144</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I110" t="inlineStr"/>
-      <c r="J110" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I110" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J110" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K110" t="inlineStr"/>
       <c r="L110" t="inlineStr"/>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>686569</v>
+        <v>686756</v>
       </c>
       <c r="R110" t="n">
-        <v>6562949</v>
+        <v>6563092</v>
       </c>
       <c r="S110" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T110" t="inlineStr">
         <is>
@@ -12705,22 +12710,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12729,33 +12724,34 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929342</t>
+          <t>https://artportalen.se/Sighting/126234373</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>134487656</v>
+        <v>122929342</v>
       </c>
       <c r="B111" t="n">
-        <v>99217</v>
+        <v>97986</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12763,45 +12759,41 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>221952</v>
+        <v>221946</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I111" t="inlineStr"/>
       <c r="J111" t="inlineStr"/>
-      <c r="K111" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K111" t="inlineStr"/>
       <c r="L111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>686835</v>
+        <v>686569</v>
       </c>
       <c r="R111" t="n">
-        <v>6563212</v>
+        <v>6562949</v>
       </c>
       <c r="S111" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12825,17 +12817,22 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z111" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC111" t="inlineStr">
-        <is>
-          <t>2 i blom samt några plantor med endast blad.</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB111" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12844,72 +12841,76 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
-      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134487656</t>
+          <t>https://artportalen.se/Sighting/122929342</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>118843519</v>
+        <v>134487656</v>
       </c>
       <c r="B112" t="n">
-        <v>91431</v>
+        <v>99217</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E112" t="n">
-        <v>6039941</v>
+        <v>221952</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
-      <c r="K112" t="inlineStr"/>
+      <c r="K112" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>Norrby Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>686668</v>
+        <v>686835</v>
       </c>
       <c r="R112" t="n">
-        <v>6563218</v>
+        <v>6563212</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12936,17 +12937,17 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AC112" t="inlineStr">
         <is>
-          <t>Kollekt BR55. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/112337794</t>
+          <t>2 i blom samt några plantor med endast blad.</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12962,78 +12963,65 @@
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY112" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - extern</t>
-        </is>
-      </c>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118843519</t>
+          <t>https://artportalen.se/Sighting/134487656</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>122203249</v>
+        <v>118843519</v>
       </c>
       <c r="B113" t="n">
-        <v>96554</v>
+        <v>91431</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E113" t="n">
-        <v>210</v>
+        <v>6039941</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gelatinfingersvamp</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Ramaria primulina</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
-      <c r="L113" t="inlineStr"/>
+      <c r="K113" t="inlineStr"/>
       <c r="N113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>Ö Norrbytorp, Srm</t>
+          <t>Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>687968</v>
+        <v>686668</v>
       </c>
       <c r="R113" t="n">
-        <v>6562733</v>
+        <v>6563218</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -13060,17 +13048,17 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AC113" t="inlineStr">
         <is>
-          <t>På murken granlåga i äldre skog.</t>
+          <t>Kollekt BR55. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/112337794</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13086,24 +13074,28 @@
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AY113" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY113" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122203249</t>
+          <t>https://artportalen.se/Sighting/118843519</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>122780924</v>
+        <v>122203249</v>
       </c>
       <c r="B114" t="n">
         <v>96554</v>
@@ -13131,21 +13123,29 @@
           <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
-      <c r="I114" t="inlineStr"/>
+      <c r="I114" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="J114" t="inlineStr"/>
-      <c r="K114" t="inlineStr"/>
+      <c r="K114" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L114" t="inlineStr"/>
       <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
-          <t>Grön sköldmossa, Srm</t>
+          <t>Ö Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>687970</v>
+        <v>687968</v>
       </c>
       <c r="R114" t="n">
-        <v>6562732</v>
+        <v>6562733</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13172,17 +13172,17 @@
       </c>
       <c r="Y114" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AC114" t="inlineStr">
         <is>
-          <t>Grön sköldmossa på rutten stam</t>
+          <t>På murken granlåga i äldre skog.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13198,65 +13198,66 @@
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX114" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122780924</t>
+          <t>https://artportalen.se/Sighting/122203249</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>129624531</v>
+        <v>122780924</v>
       </c>
       <c r="B115" t="n">
-        <v>90946</v>
+        <v>96554</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>889</v>
+        <v>210</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I115" t="inlineStr"/>
       <c r="J115" t="inlineStr"/>
       <c r="K115" t="inlineStr"/>
+      <c r="L115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Grön sköldmossa, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>687931</v>
+        <v>687970</v>
       </c>
       <c r="R115" t="n">
-        <v>6562811</v>
+        <v>6562732</v>
       </c>
       <c r="S115" t="n">
         <v>10</v>
@@ -13283,12 +13284,17 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC115" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa på rutten stam</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13304,24 +13310,24 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129624531</t>
+          <t>https://artportalen.se/Sighting/122780924</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>129624696</v>
+        <v>129624531</v>
       </c>
       <c r="B116" t="n">
         <v>90946</v>
@@ -13359,10 +13365,10 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>687973</v>
+        <v>687931</v>
       </c>
       <c r="R116" t="n">
-        <v>6562815</v>
+        <v>6562811</v>
       </c>
       <c r="S116" t="n">
         <v>10</v>
@@ -13397,11 +13403,6 @@
           <t>2025-11-09</t>
         </is>
       </c>
-      <c r="AC116" t="inlineStr">
-        <is>
-          <t>På död tall.</t>
-        </is>
-      </c>
       <c r="AD116" t="b">
         <v>0</v>
       </c>
@@ -13426,16 +13427,16 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129624696</t>
+          <t>https://artportalen.se/Sighting/129624531</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>122203275</v>
+        <v>129624696</v>
       </c>
       <c r="B117" t="n">
-        <v>91909</v>
+        <v>90946</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
@@ -13443,21 +13444,21 @@
         </is>
       </c>
       <c r="E117" t="n">
-        <v>1202</v>
+        <v>889</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I117" t="inlineStr"/>
@@ -13466,14 +13467,14 @@
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
-          <t>Ö Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>687981</v>
+        <v>687973</v>
       </c>
       <c r="R117" t="n">
-        <v>6562724</v>
+        <v>6562815</v>
       </c>
       <c r="S117" t="n">
         <v>10</v>
@@ -13500,12 +13501,17 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC117" t="inlineStr">
+        <is>
+          <t>På död tall.</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13532,62 +13538,54 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122203275</t>
+          <t>https://artportalen.se/Sighting/129624696</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>128314411</v>
+        <v>122203275</v>
       </c>
       <c r="B118" t="n">
-        <v>92348</v>
+        <v>91909</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>5420</v>
+        <v>1202</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I118" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J118" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+        </is>
+      </c>
+      <c r="I118" t="inlineStr"/>
+      <c r="J118" t="inlineStr"/>
       <c r="K118" t="inlineStr"/>
       <c r="N118" t="inlineStr"/>
       <c r="P118" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>688088</v>
+        <v>687981</v>
       </c>
       <c r="R118" t="n">
-        <v>6562722</v>
+        <v>6562724</v>
       </c>
       <c r="S118" t="n">
         <v>10</v>
@@ -13614,12 +13612,12 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13646,41 +13644,45 @@
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128314411</t>
+          <t>https://artportalen.se/Sighting/122203275</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>128314833</v>
+        <v>135358856</v>
       </c>
       <c r="B119" t="n">
-        <v>93235</v>
+        <v>91531</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E119" t="n">
-        <v>5966</v>
+        <v>2051</v>
       </c>
       <c r="F119" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G119" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H119" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I119" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I119" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J119" t="inlineStr"/>
       <c r="K119" t="inlineStr"/>
       <c r="N119" t="inlineStr"/>
@@ -13690,10 +13692,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>688073</v>
+        <v>688004</v>
       </c>
       <c r="R119" t="n">
-        <v>6562768</v>
+        <v>6562799</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13720,12 +13722,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13752,42 +13754,50 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128314833</t>
+          <t>https://artportalen.se/Sighting/135358856</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>128317789</v>
+        <v>128314411</v>
       </c>
       <c r="B120" t="n">
-        <v>93235</v>
+        <v>92348</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I120" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J120" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K120" t="inlineStr"/>
       <c r="N120" t="inlineStr"/>
       <c r="P120" t="inlineStr">
@@ -13796,10 +13806,10 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>688094</v>
+        <v>688088</v>
       </c>
       <c r="R120" t="n">
-        <v>6562777</v>
+        <v>6562722</v>
       </c>
       <c r="S120" t="n">
         <v>10</v>
@@ -13858,13 +13868,13 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317789</t>
+          <t>https://artportalen.se/Sighting/128314411</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>128526064</v>
+        <v>128314833</v>
       </c>
       <c r="B121" t="n">
         <v>93235</v>
@@ -13902,10 +13912,10 @@
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>687952</v>
+        <v>688073</v>
       </c>
       <c r="R121" t="n">
-        <v>6562790</v>
+        <v>6562768</v>
       </c>
       <c r="S121" t="n">
         <v>10</v>
@@ -13932,12 +13942,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13964,13 +13974,13 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128526064</t>
+          <t>https://artportalen.se/Sighting/128314833</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>128646583</v>
+        <v>128317789</v>
       </c>
       <c r="B122" t="n">
         <v>93235</v>
@@ -14008,10 +14018,10 @@
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>688067</v>
+        <v>688094</v>
       </c>
       <c r="R122" t="n">
-        <v>6562731</v>
+        <v>6562777</v>
       </c>
       <c r="S122" t="n">
         <v>10</v>
@@ -14038,12 +14048,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14070,16 +14080,16 @@
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128646583</t>
+          <t>https://artportalen.se/Sighting/128317789</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>17285491</v>
+        <v>128526064</v>
       </c>
       <c r="B123" t="n">
-        <v>80432</v>
+        <v>93235</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
@@ -14087,36 +14097,37 @@
         </is>
       </c>
       <c r="E123" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I123" t="inlineStr"/>
       <c r="J123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
+      <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
-          <t>Norrby torp, 480 m Ö, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>688111</v>
+        <v>687952</v>
       </c>
       <c r="R123" t="n">
-        <v>6562706</v>
+        <v>6562790</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14143,17 +14154,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14162,38 +14168,34 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
+      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
-      </c>
-      <c r="AI123" t="inlineStr">
-        <is>
-          <t>Yngre gallrad blandskog</t>
-        </is>
       </c>
       <c r="AT123" t="inlineStr"/>
       <c r="AW123" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX123" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17285491</t>
+          <t>https://artportalen.se/Sighting/128526064</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>79273786</v>
+        <v>128646583</v>
       </c>
       <c r="B124" t="n">
-        <v>80432</v>
+        <v>93235</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
@@ -14201,34 +14203,37 @@
         </is>
       </c>
       <c r="E124" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I124" t="inlineStr"/>
+      <c r="J124" t="inlineStr"/>
+      <c r="K124" t="inlineStr"/>
+      <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
-          <t>Åvadal, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>688109</v>
+        <v>688067</v>
       </c>
       <c r="R124" t="n">
-        <v>6562704</v>
+        <v>6562731</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14255,12 +14260,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14269,45 +14274,31 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
+      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ124" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK124" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO124" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
       </c>
       <c r="AT124" t="inlineStr"/>
       <c r="AW124" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX124" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79273786</t>
+          <t>https://artportalen.se/Sighting/128646583</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>89840770</v>
+        <v>17285491</v>
       </c>
       <c r="B125" t="n">
         <v>80432</v>
@@ -14338,17 +14329,16 @@
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
-      <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
-          <t>Ö Norrby Torp, Srm</t>
+          <t>Norrby torp, 480 m Ö, Srm</t>
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>688146</v>
+        <v>688111</v>
       </c>
       <c r="R125" t="n">
-        <v>6562738</v>
+        <v>6562706</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14375,17 +14365,17 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2015-04-02</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2015-04-02</t>
         </is>
       </c>
       <c r="AC125" t="inlineStr">
         <is>
-          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
+          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14394,31 +14384,35 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
+      </c>
+      <c r="AI125" t="inlineStr">
+        <is>
+          <t>Yngre gallrad blandskog</t>
+        </is>
       </c>
       <c r="AT125" t="inlineStr"/>
       <c r="AW125" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX125" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89840770</t>
+          <t>https://artportalen.se/Sighting/17285491</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>112384453</v>
+        <v>79273786</v>
       </c>
       <c r="B126" t="n">
         <v>80432</v>
@@ -14447,19 +14441,16 @@
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
-      <c r="K126" t="inlineStr"/>
-      <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Norrby torp Ö om, Srm</t>
+          <t>Åvadal, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>688145</v>
+        <v>688109</v>
       </c>
       <c r="R126" t="n">
-        <v>6562737</v>
+        <v>6562704</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14486,17 +14477,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC126" t="inlineStr">
-        <is>
-          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14505,31 +14491,45 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ126" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK126" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO126" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112384453</t>
+          <t>https://artportalen.se/Sighting/79273786</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122779297</v>
+        <v>89840770</v>
       </c>
       <c r="B127" t="n">
         <v>80432</v>
@@ -14563,14 +14563,14 @@
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Lunglav, Srm</t>
+          <t>Ö Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>688116</v>
+        <v>688146</v>
       </c>
       <c r="R127" t="n">
-        <v>6562703</v>
+        <v>6562738</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14597,17 +14597,17 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AC127" t="inlineStr">
         <is>
-          <t>Lunglav på gammal ek</t>
+          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14623,81 +14623,68 @@
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122779297</t>
+          <t>https://artportalen.se/Sighting/89840770</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>125923864</v>
+        <v>112384453</v>
       </c>
       <c r="B128" t="n">
-        <v>57754</v>
+        <v>80432</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>102118</v>
+        <v>6458</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I128" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I128" t="inlineStr"/>
+      <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
-      <c r="L128" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M128" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby torp Ö om, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>687916</v>
+        <v>688145</v>
       </c>
       <c r="R128" t="n">
-        <v>6562815</v>
+        <v>6562737</v>
       </c>
       <c r="S128" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T128" t="inlineStr">
         <is>
@@ -14721,17 +14708,17 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
+          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14740,33 +14727,34 @@
       <c r="AE128" t="b">
         <v>0</v>
       </c>
+      <c r="AF128" t="inlineStr"/>
       <c r="AG128" t="b">
         <v>0</v>
       </c>
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125923864</t>
+          <t>https://artportalen.se/Sighting/112384453</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>128317861</v>
+        <v>122779297</v>
       </c>
       <c r="B129" t="n">
-        <v>58114</v>
+        <v>80432</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
@@ -14774,45 +14762,40 @@
         </is>
       </c>
       <c r="E129" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
-      <c r="L129" t="inlineStr"/>
-      <c r="M129" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Lunglav, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>688058</v>
+        <v>688116</v>
       </c>
       <c r="R129" t="n">
-        <v>6562805</v>
+        <v>6562703</v>
       </c>
       <c r="S129" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T129" t="inlineStr">
         <is>
@@ -14836,12 +14819,17 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC129" t="inlineStr">
+        <is>
+          <t>Lunglav på gammal ek</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14850,33 +14838,34 @@
       <c r="AE129" t="b">
         <v>0</v>
       </c>
+      <c r="AF129" t="inlineStr"/>
       <c r="AG129" t="b">
         <v>0</v>
       </c>
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317861</t>
+          <t>https://artportalen.se/Sighting/122779297</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122692266</v>
+        <v>125923864</v>
       </c>
       <c r="B130" t="n">
-        <v>58826</v>
+        <v>57754</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
@@ -14884,21 +14873,21 @@
         </is>
       </c>
       <c r="E130" t="n">
-        <v>208242</v>
+        <v>102118</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>Linnaeus, 1758</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
@@ -14906,32 +14895,31 @@
           <t>1</t>
         </is>
       </c>
-      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
-      <c r="L130" t="inlineStr"/>
+      <c r="L130" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M130" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N130" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
+      <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>687868</v>
+        <v>687916</v>
       </c>
       <c r="R130" t="n">
-        <v>6562755</v>
+        <v>6562815</v>
       </c>
       <c r="S130" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T130" t="inlineStr">
         <is>
@@ -14955,17 +14943,17 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14974,73 +14962,76 @@
       <c r="AE130" t="b">
         <v>0</v>
       </c>
-      <c r="AF130" t="inlineStr"/>
       <c r="AG130" t="b">
         <v>0</v>
       </c>
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122692266</t>
+          <t>https://artportalen.se/Sighting/125923864</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>101544040</v>
+        <v>128317861</v>
       </c>
       <c r="B131" t="n">
-        <v>99035</v>
+        <v>58114</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>219790</v>
+        <v>103021</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
+      <c r="M131" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>NO Norrby Torp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>687896</v>
+        <v>688058</v>
       </c>
       <c r="R131" t="n">
-        <v>6562764</v>
+        <v>6562805</v>
       </c>
       <c r="S131" t="n">
         <v>25</v>
@@ -15067,12 +15058,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15081,7 +15072,6 @@
       <c r="AE131" t="b">
         <v>0</v>
       </c>
-      <c r="AF131" t="inlineStr"/>
       <c r="AG131" t="b">
         <v>0</v>
       </c>
@@ -15099,16 +15089,16 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101544040</t>
+          <t>https://artportalen.se/Sighting/128317861</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>122930166</v>
+        <v>122692266</v>
       </c>
       <c r="B132" t="n">
-        <v>96554</v>
+        <v>58826</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
@@ -15116,41 +15106,54 @@
         </is>
       </c>
       <c r="E132" t="n">
-        <v>210</v>
+        <v>208242</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J132" t="inlineStr"/>
       <c r="K132" t="inlineStr"/>
       <c r="L132" t="inlineStr"/>
-      <c r="N132" t="inlineStr"/>
+      <c r="M132" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N132" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Mindre vattensalamander, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>686762</v>
+        <v>687868</v>
       </c>
       <c r="R132" t="n">
-        <v>6562715</v>
+        <v>6562755</v>
       </c>
       <c r="S132" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T132" t="inlineStr">
         <is>
@@ -15174,22 +15177,17 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z132" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB132" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15198,33 +15196,34 @@
       <c r="AE132" t="b">
         <v>0</v>
       </c>
+      <c r="AF132" t="inlineStr"/>
       <c r="AG132" t="b">
         <v>0</v>
       </c>
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122930166</t>
+          <t>https://artportalen.se/Sighting/122692266</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122929535</v>
+        <v>101544040</v>
       </c>
       <c r="B133" t="n">
-        <v>8455</v>
+        <v>99035</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
@@ -15232,46 +15231,41 @@
         </is>
       </c>
       <c r="E133" t="n">
-        <v>106545</v>
+        <v>219790</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I133" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Soó</t>
+        </is>
+      </c>
+      <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
       <c r="L133" t="inlineStr"/>
-      <c r="M133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>NO Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>686612</v>
+        <v>687896</v>
       </c>
       <c r="R133" t="n">
-        <v>6562882</v>
+        <v>6562764</v>
       </c>
       <c r="S133" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15295,22 +15289,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15319,33 +15303,34 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929535</t>
+          <t>https://artportalen.se/Sighting/101544040</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>122928987</v>
+        <v>122930166</v>
       </c>
       <c r="B134" t="n">
-        <v>97983</v>
+        <v>96554</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15353,21 +15338,21 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>221945</v>
+        <v>210</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
@@ -15381,13 +15366,13 @@
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>686389</v>
+        <v>686762</v>
       </c>
       <c r="R134" t="n">
-        <v>6562967</v>
+        <v>6562715</v>
       </c>
       <c r="S134" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T134" t="inlineStr">
         <is>
@@ -15416,7 +15401,7 @@
       </c>
       <c r="Z134" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
@@ -15426,7 +15411,7 @@
       </c>
       <c r="AB134" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15452,51 +15437,54 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122928987</t>
+          <t>https://artportalen.se/Sighting/122930166</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>126061106</v>
+        <v>119061006</v>
       </c>
       <c r="B135" t="n">
-        <v>91333</v>
+        <v>91531</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2008</v>
+        <v>2051</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
+      <c r="J135" t="inlineStr"/>
+      <c r="K135" t="inlineStr"/>
+      <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>S Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>686883</v>
+        <v>686477</v>
       </c>
       <c r="R135" t="n">
-        <v>6562742</v>
+        <v>6562857</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15523,22 +15511,17 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z135" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB135" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Brukad skog nära kant mot gammal.</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15547,33 +15530,34 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
+      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061106</t>
+          <t>https://artportalen.se/Sighting/119061006</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>126061107</v>
+        <v>122929535</v>
       </c>
       <c r="B136" t="n">
-        <v>96458</v>
+        <v>8455</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15581,37 +15565,46 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2818</v>
+        <v>106545</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J136" t="inlineStr"/>
+      <c r="K136" t="inlineStr"/>
+      <c r="L136" t="inlineStr"/>
+      <c r="M136" t="inlineStr"/>
+      <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>686880</v>
+        <v>686612</v>
       </c>
       <c r="R136" t="n">
-        <v>6562745</v>
+        <v>6562882</v>
       </c>
       <c r="S136" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15635,22 +15628,22 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z136" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB136" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15665,27 +15658,27 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061107</t>
+          <t>https://artportalen.se/Sighting/122929535</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>129215187</v>
+        <v>122928987</v>
       </c>
       <c r="B137" t="n">
-        <v>91872</v>
+        <v>97983</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15693,37 +15686,38 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>5447</v>
+        <v>221945</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>686977</v>
+        <v>686389</v>
       </c>
       <c r="R137" t="n">
-        <v>6562706</v>
+        <v>6562967</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15750,12 +15744,22 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z137" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB137" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15764,56 +15768,55 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
-      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215187</t>
+          <t>https://artportalen.se/Sighting/122928987</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>126061104</v>
+        <v>126061106</v>
       </c>
       <c r="B138" t="n">
-        <v>4775</v>
+        <v>91333</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>100299</v>
+        <v>2008</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I138" t="inlineStr"/>
@@ -15823,10 +15826,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>686868</v>
+        <v>686883</v>
       </c>
       <c r="R138" t="n">
-        <v>6562739</v>
+        <v>6562742</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15858,7 +15861,7 @@
       </c>
       <c r="Z138" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
@@ -15868,7 +15871,7 @@
       </c>
       <c r="AB138" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15879,26 +15882,6 @@
       </c>
       <c r="AG138" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ138" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK138" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL138" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO138" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT138" t="inlineStr"/>
       <c r="AW138" t="inlineStr">
@@ -15914,16 +15897,16 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061104</t>
+          <t>https://artportalen.se/Sighting/126061106</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>126061116</v>
+        <v>126061107</v>
       </c>
       <c r="B139" t="n">
-        <v>44177</v>
+        <v>96458</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -15931,21 +15914,21 @@
         </is>
       </c>
       <c r="E139" t="n">
-        <v>101735</v>
+        <v>2818</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15955,10 +15938,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>686928</v>
+        <v>686880</v>
       </c>
       <c r="R139" t="n">
-        <v>6562716</v>
+        <v>6562745</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15990,7 +15973,7 @@
       </c>
       <c r="Z139" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
@@ -16000,7 +15983,7 @@
       </c>
       <c r="AB139" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -16011,26 +15994,6 @@
       </c>
       <c r="AG139" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ139" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK139" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AL139" t="inlineStr">
-        <is>
-          <t>Fnöskticka på björk.</t>
-        </is>
-      </c>
-      <c r="AO139" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius # Fnöskticka på björk.</t>
-        </is>
       </c>
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
@@ -16046,16 +16009,16 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061116</t>
+          <t>https://artportalen.se/Sighting/126061107</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>125974903</v>
+        <v>129215187</v>
       </c>
       <c r="B140" t="n">
-        <v>8444</v>
+        <v>91872</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -16063,50 +16026,40 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>106554</v>
+        <v>5447</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I140" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I140" t="inlineStr"/>
       <c r="J140" t="inlineStr"/>
       <c r="K140" t="inlineStr"/>
-      <c r="L140" t="inlineStr"/>
-      <c r="M140" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>686838</v>
+        <v>686977</v>
       </c>
       <c r="R140" t="n">
-        <v>6562733</v>
+        <v>6562706</v>
       </c>
       <c r="S140" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T140" t="inlineStr">
         <is>
@@ -16130,17 +16083,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC140" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16153,50 +16101,30 @@
       <c r="AG140" t="b">
         <v>0</v>
       </c>
-      <c r="AJ140" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK140" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM140" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO140" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
-        </is>
-      </c>
       <c r="AT140" t="inlineStr"/>
       <c r="AW140" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX140" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974903</t>
+          <t>https://artportalen.se/Sighting/129215187</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>126061105</v>
+        <v>126061104</v>
       </c>
       <c r="B141" t="n">
-        <v>8444</v>
+        <v>4775</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
@@ -16204,21 +16132,21 @@
         </is>
       </c>
       <c r="E141" t="n">
-        <v>106554</v>
+        <v>100299</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I141" t="inlineStr"/>
@@ -16228,10 +16156,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>686860</v>
+        <v>686868</v>
       </c>
       <c r="R141" t="n">
-        <v>6562743</v>
+        <v>6562739</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16263,7 +16191,7 @@
       </c>
       <c r="Z141" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
@@ -16273,7 +16201,7 @@
       </c>
       <c r="AB141" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16287,17 +16215,22 @@
       </c>
       <c r="AJ141" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK141" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL141" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
         </is>
       </c>
       <c r="AO141" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Picea abies # Stående död gran.</t>
         </is>
       </c>
       <c r="AT141" t="inlineStr"/>
@@ -16313,6 +16246,406 @@
       </c>
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061104</t>
+        </is>
+      </c>
+    </row>
+    <row r="142">
+      <c r="A142" t="n">
+        <v>126061116</v>
+      </c>
+      <c r="B142" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D142" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E142" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F142" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G142" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H142" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I142" t="inlineStr"/>
+      <c r="P142" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q142" t="n">
+        <v>686928</v>
+      </c>
+      <c r="R142" t="n">
+        <v>6562716</v>
+      </c>
+      <c r="S142" t="n">
+        <v>10</v>
+      </c>
+      <c r="T142" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U142" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V142" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W142" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y142" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA142" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG142" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ142" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK142" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AL142" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
+        </is>
+      </c>
+      <c r="AO142" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius # Fnöskticka på björk.</t>
+        </is>
+      </c>
+      <c r="AT142" t="inlineStr"/>
+      <c r="AW142" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX142" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY142" t="inlineStr"/>
+      <c r="AZ142" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061116</t>
+        </is>
+      </c>
+    </row>
+    <row r="143">
+      <c r="A143" t="n">
+        <v>125974903</v>
+      </c>
+      <c r="B143" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D143" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E143" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F143" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G143" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H143" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="L143" t="inlineStr"/>
+      <c r="M143" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N143" t="inlineStr"/>
+      <c r="P143" t="inlineStr">
+        <is>
+          <t>söder om Tyresta, Srm</t>
+        </is>
+      </c>
+      <c r="Q143" t="n">
+        <v>686838</v>
+      </c>
+      <c r="R143" t="n">
+        <v>6562733</v>
+      </c>
+      <c r="S143" t="n">
+        <v>5</v>
+      </c>
+      <c r="T143" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U143" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V143" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W143" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y143" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA143" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC143" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
+        </is>
+      </c>
+      <c r="AD143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF143" t="inlineStr"/>
+      <c r="AG143" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ143" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK143" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM143" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO143" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Betula pendula</t>
+        </is>
+      </c>
+      <c r="AT143" t="inlineStr"/>
+      <c r="AW143" t="inlineStr">
+        <is>
+          <t>Nette Bygren</t>
+        </is>
+      </c>
+      <c r="AX143" t="inlineStr">
+        <is>
+          <t>Nette Bygren</t>
+        </is>
+      </c>
+      <c r="AY143" t="inlineStr"/>
+      <c r="AZ143" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125974903</t>
+        </is>
+      </c>
+    </row>
+    <row r="144">
+      <c r="A144" t="n">
+        <v>126061105</v>
+      </c>
+      <c r="B144" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D144" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E144" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F144" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G144" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H144" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="P144" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q144" t="n">
+        <v>686860</v>
+      </c>
+      <c r="R144" t="n">
+        <v>6562743</v>
+      </c>
+      <c r="S144" t="n">
+        <v>10</v>
+      </c>
+      <c r="T144" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U144" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V144" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W144" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y144" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA144" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG144" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ144" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK144" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO144" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT144" t="inlineStr"/>
+      <c r="AW144" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX144" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY144" t="inlineStr"/>
+      <c r="AZ144" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126061105</t>
         </is>
@@ -16460,6 +16793,9 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ139" r:id="rId138"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ140" r:id="rId139"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ141" r:id="rId140"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ142" r:id="rId141"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ143" r:id="rId142"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ144" r:id="rId143"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -6148,7 +6148,7 @@
         <v>135827249</v>
       </c>
       <c r="B52" t="n">
-        <v>98142</v>
+        <v>98144</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>135358856</v>
       </c>
       <c r="B119" t="n">
-        <v>91531</v>
+        <v>91533</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -15446,7 +15446,7 @@
         <v>119061006</v>
       </c>
       <c r="B135" t="n">
-        <v>91531</v>
+        <v>91533</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -6148,7 +6148,7 @@
         <v>135827249</v>
       </c>
       <c r="B52" t="n">
-        <v>98144</v>
+        <v>98161</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -13653,7 +13653,7 @@
         <v>135358856</v>
       </c>
       <c r="B119" t="n">
-        <v>91533</v>
+        <v>91535</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -6800,7 +6800,7 @@
         <v>135827249</v>
       </c>
       <c r="B58" t="n">
-        <v>98161</v>
+        <v>98162</v>
       </c>
       <c r="D58" t="inlineStr">
         <is>
@@ -14305,7 +14305,7 @@
         <v>135358856</v>
       </c>
       <c r="B125" t="n">
-        <v>91535</v>
+        <v>91536</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ166"/>
+  <dimension ref="A1:AZ167"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1976,7 +1976,7 @@
         <v>136261113</v>
       </c>
       <c r="B14" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>136138429</v>
       </c>
       <c r="B23" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136159959</v>
       </c>
       <c r="B24" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>136193282</v>
       </c>
       <c r="B25" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>136193424</v>
       </c>
       <c r="B26" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136232449</v>
       </c>
       <c r="B27" t="n">
-        <v>93364</v>
+        <v>93365</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>136259823</v>
       </c>
       <c r="B41" t="n">
-        <v>80063</v>
+        <v>80064</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>136138543</v>
       </c>
       <c r="B50" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136138586</v>
       </c>
       <c r="B51" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136159945</v>
       </c>
       <c r="B52" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>136160087</v>
       </c>
       <c r="B53" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>135827249</v>
       </c>
       <c r="B65" t="n">
-        <v>98163</v>
+        <v>98164</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>136234180</v>
       </c>
       <c r="B70" t="n">
-        <v>98157</v>
+        <v>98158</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>136234148</v>
       </c>
       <c r="B72" t="n">
-        <v>98160</v>
+        <v>98161</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>135358856</v>
       </c>
       <c r="B135" t="n">
-        <v>91537</v>
+        <v>91538</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>136241603</v>
       </c>
       <c r="B136" t="n">
-        <v>96880</v>
+        <v>96881</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>136231090</v>
       </c>
       <c r="B137" t="n">
-        <v>96598</v>
+        <v>96599</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15860,32 +15860,32 @@
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>128314833</v>
+        <v>136268106</v>
       </c>
       <c r="B139" t="n">
-        <v>93235</v>
+        <v>92030</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15898,10 +15898,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>688073</v>
+        <v>687910</v>
       </c>
       <c r="R139" t="n">
-        <v>6562768</v>
+        <v>6562787</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15928,12 +15928,17 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AC139" t="inlineStr">
+        <is>
+          <t>På rätt klen, senvuxen?, lutande granlåga i ett kärr.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15960,13 +15965,13 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128314833</t>
+          <t>https://artportalen.se/Sighting/136268106</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128317789</v>
+        <v>128314833</v>
       </c>
       <c r="B140" t="n">
         <v>93235</v>
@@ -16004,10 +16009,10 @@
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>688094</v>
+        <v>688073</v>
       </c>
       <c r="R140" t="n">
-        <v>6562777</v>
+        <v>6562768</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16066,13 +16071,13 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317789</t>
+          <t>https://artportalen.se/Sighting/128314833</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128526064</v>
+        <v>128317789</v>
       </c>
       <c r="B141" t="n">
         <v>93235</v>
@@ -16110,10 +16115,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>687952</v>
+        <v>688094</v>
       </c>
       <c r="R141" t="n">
-        <v>6562790</v>
+        <v>6562777</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16140,12 +16145,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16172,13 +16177,13 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128526064</t>
+          <t>https://artportalen.se/Sighting/128317789</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128646583</v>
+        <v>128526064</v>
       </c>
       <c r="B142" t="n">
         <v>93235</v>
@@ -16216,10 +16221,10 @@
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>688067</v>
+        <v>687952</v>
       </c>
       <c r="R142" t="n">
-        <v>6562731</v>
+        <v>6562790</v>
       </c>
       <c r="S142" t="n">
         <v>10</v>
@@ -16246,12 +16251,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16278,16 +16283,16 @@
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128646583</t>
+          <t>https://artportalen.se/Sighting/128526064</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>136241765</v>
+        <v>128646583</v>
       </c>
       <c r="B143" t="n">
-        <v>80063</v>
+        <v>93235</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
@@ -16295,44 +16300,40 @@
         </is>
       </c>
       <c r="E143" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
       <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K143" t="inlineStr"/>
       <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>688014</v>
+        <v>688067</v>
       </c>
       <c r="R143" t="n">
-        <v>6562734</v>
+        <v>6562731</v>
       </c>
       <c r="S143" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T143" t="inlineStr">
         <is>
@@ -16356,22 +16357,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z143" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB143" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16387,27 +16378,27 @@
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241765</t>
+          <t>https://artportalen.se/Sighting/128646583</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>17285491</v>
+        <v>136241765</v>
       </c>
       <c r="B144" t="n">
-        <v>80432</v>
+        <v>80064</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16415,39 +16406,44 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I144" t="inlineStr"/>
       <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr"/>
+      <c r="K144" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Norrby torp, 480 m Ö, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>688111</v>
+        <v>688014</v>
       </c>
       <c r="R144" t="n">
-        <v>6562706</v>
+        <v>6562734</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16471,17 +16467,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
-        </is>
-      </c>
-      <c r="AC144" t="inlineStr">
-        <is>
-          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16490,35 +16491,31 @@
       <c r="AE144" t="b">
         <v>0</v>
       </c>
+      <c r="AF144" t="inlineStr"/>
       <c r="AG144" t="b">
         <v>0</v>
-      </c>
-      <c r="AI144" t="inlineStr">
-        <is>
-          <t>Yngre gallrad blandskog</t>
-        </is>
       </c>
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17285491</t>
+          <t>https://artportalen.se/Sighting/136241765</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>79273786</v>
+        <v>17285491</v>
       </c>
       <c r="B145" t="n">
         <v>80432</v>
@@ -16547,16 +16544,18 @@
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
+      <c r="J145" t="inlineStr"/>
+      <c r="K145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Åvadal, Srm</t>
+          <t>Norrby torp, 480 m Ö, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>688109</v>
+        <v>688111</v>
       </c>
       <c r="R145" t="n">
-        <v>6562704</v>
+        <v>6562706</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16583,12 +16582,17 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2015-04-02</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2015-04-02</t>
+        </is>
+      </c>
+      <c r="AC145" t="inlineStr">
+        <is>
+          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16600,42 +16604,32 @@
       <c r="AG145" t="b">
         <v>0</v>
       </c>
-      <c r="AJ145" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK145" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO145" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
+      <c r="AI145" t="inlineStr">
+        <is>
+          <t>Yngre gallrad blandskog</t>
         </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79273786</t>
+          <t>https://artportalen.se/Sighting/17285491</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>89840770</v>
+        <v>79273786</v>
       </c>
       <c r="B146" t="n">
         <v>80432</v>
@@ -16664,19 +16658,16 @@
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
-      <c r="K146" t="inlineStr"/>
-      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Ö Norrby Torp, Srm</t>
+          <t>Åvadal, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>688146</v>
+        <v>688109</v>
       </c>
       <c r="R146" t="n">
-        <v>6562738</v>
+        <v>6562704</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16703,17 +16694,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
-        </is>
-      </c>
-      <c r="AC146" t="inlineStr">
-        <is>
-          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16722,31 +16708,45 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
-      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ146" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK146" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO146" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89840770</t>
+          <t>https://artportalen.se/Sighting/79273786</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>112384453</v>
+        <v>89840770</v>
       </c>
       <c r="B147" t="n">
         <v>80432</v>
@@ -16780,14 +16780,14 @@
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Norrby torp Ö om, Srm</t>
+          <t>Ö Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>688145</v>
+        <v>688146</v>
       </c>
       <c r="R147" t="n">
-        <v>6562737</v>
+        <v>6562738</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16814,17 +16814,17 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AC147" t="inlineStr">
         <is>
-          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
+          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16840,24 +16840,24 @@
       <c r="AT147" t="inlineStr"/>
       <c r="AW147" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX147" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112384453</t>
+          <t>https://artportalen.se/Sighting/89840770</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>122779297</v>
+        <v>112384453</v>
       </c>
       <c r="B148" t="n">
         <v>80432</v>
@@ -16891,14 +16891,14 @@
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Lunglav, Srm</t>
+          <t>Norrby torp Ö om, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>688116</v>
+        <v>688145</v>
       </c>
       <c r="R148" t="n">
-        <v>6562703</v>
+        <v>6562737</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16925,17 +16925,17 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC148" t="inlineStr">
         <is>
-          <t>Lunglav på gammal ek</t>
+          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16951,81 +16951,68 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122779297</t>
+          <t>https://artportalen.se/Sighting/112384453</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>125923864</v>
+        <v>122779297</v>
       </c>
       <c r="B149" t="n">
-        <v>57754</v>
+        <v>80432</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E149" t="n">
-        <v>102118</v>
+        <v>6458</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I149" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I149" t="inlineStr"/>
+      <c r="J149" t="inlineStr"/>
       <c r="K149" t="inlineStr"/>
-      <c r="L149" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M149" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Lunglav, Srm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>687916</v>
+        <v>688116</v>
       </c>
       <c r="R149" t="n">
-        <v>6562815</v>
+        <v>6562703</v>
       </c>
       <c r="S149" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T149" t="inlineStr">
         <is>
@@ -17049,17 +17036,17 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC149" t="inlineStr">
         <is>
-          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
+          <t>Lunglav på gammal ek</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17068,63 +17055,72 @@
       <c r="AE149" t="b">
         <v>0</v>
       </c>
+      <c r="AF149" t="inlineStr"/>
       <c r="AG149" t="b">
         <v>0</v>
       </c>
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125923864</t>
+          <t>https://artportalen.se/Sighting/122779297</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>128317861</v>
+        <v>125923864</v>
       </c>
       <c r="B150" t="n">
-        <v>58114</v>
+        <v>57754</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr"/>
+      <c r="L150" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M150" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
@@ -17134,10 +17130,10 @@
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>688058</v>
+        <v>687916</v>
       </c>
       <c r="R150" t="n">
-        <v>6562805</v>
+        <v>6562815</v>
       </c>
       <c r="S150" t="n">
         <v>25</v>
@@ -17164,12 +17160,17 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC150" t="inlineStr">
+        <is>
+          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17195,16 +17196,16 @@
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317861</t>
+          <t>https://artportalen.se/Sighting/125923864</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>136138855</v>
+        <v>128317861</v>
       </c>
       <c r="B151" t="n">
-        <v>58143</v>
+        <v>58114</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17244,13 +17245,13 @@
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>687836</v>
+        <v>688058</v>
       </c>
       <c r="R151" t="n">
-        <v>6562786</v>
+        <v>6562805</v>
       </c>
       <c r="S151" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17274,12 +17275,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17305,16 +17306,16 @@
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136138855</t>
+          <t>https://artportalen.se/Sighting/128317861</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>136138971</v>
+        <v>136138855</v>
       </c>
       <c r="B152" t="n">
-        <v>58143</v>
+        <v>58144</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17354,13 +17355,13 @@
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>687977</v>
+        <v>687836</v>
       </c>
       <c r="R152" t="n">
-        <v>6562735</v>
+        <v>6562786</v>
       </c>
       <c r="S152" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17415,71 +17416,62 @@
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136138971</t>
+          <t>https://artportalen.se/Sighting/136138855</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>122692266</v>
+        <v>136138971</v>
       </c>
       <c r="B153" t="n">
-        <v>58826</v>
+        <v>58144</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E153" t="n">
-        <v>208242</v>
+        <v>103021</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I153" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J153" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
       <c r="L153" t="inlineStr"/>
       <c r="M153" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N153" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>687868</v>
+        <v>687977</v>
       </c>
       <c r="R153" t="n">
-        <v>6562755</v>
+        <v>6562735</v>
       </c>
       <c r="S153" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17503,17 +17495,12 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC153" t="inlineStr">
-        <is>
-          <t>Mindre vattensalamander</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17522,34 +17509,33 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122692266</t>
+          <t>https://artportalen.se/Sighting/136138971</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>136241491</v>
+        <v>122692266</v>
       </c>
       <c r="B154" t="n">
-        <v>58819</v>
+        <v>58826</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
@@ -17557,16 +17543,16 @@
         </is>
       </c>
       <c r="E154" t="n">
-        <v>208245</v>
+        <v>208242</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
@@ -17574,19 +17560,31 @@
           <t>(Linnaeus, 1758)</t>
         </is>
       </c>
-      <c r="I154" t="inlineStr"/>
+      <c r="I154" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
       <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
+      <c r="M154" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N154" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P154" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Mindre vattensalamander, Srm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>687873</v>
+        <v>687868</v>
       </c>
       <c r="R154" t="n">
         <v>6562755</v>
@@ -17616,17 +17614,17 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Troligen årsunge.</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17642,27 +17640,27 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241491</t>
+          <t>https://artportalen.se/Sighting/122692266</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>101544040</v>
+        <v>136241491</v>
       </c>
       <c r="B155" t="n">
-        <v>99035</v>
+        <v>58820</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
@@ -17670,41 +17668,42 @@
         </is>
       </c>
       <c r="E155" t="n">
-        <v>219790</v>
+        <v>208245</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
       <c r="L155" t="inlineStr"/>
+      <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>NO Norrby Torp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>687896</v>
+        <v>687873</v>
       </c>
       <c r="R155" t="n">
-        <v>6562764</v>
+        <v>6562755</v>
       </c>
       <c r="S155" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T155" t="inlineStr">
         <is>
@@ -17728,12 +17727,17 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AC155" t="inlineStr">
+        <is>
+          <t>Troligen årsunge.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17760,16 +17764,16 @@
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101544040</t>
+          <t>https://artportalen.se/Sighting/136241491</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>122930166</v>
+        <v>101544040</v>
       </c>
       <c r="B156" t="n">
-        <v>96554</v>
+        <v>99035</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17777,21 +17781,21 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>210</v>
+        <v>219790</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I156" t="inlineStr"/>
@@ -17801,17 +17805,17 @@
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>NO Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>686762</v>
+        <v>687896</v>
       </c>
       <c r="R156" t="n">
-        <v>6562715</v>
+        <v>6562764</v>
       </c>
       <c r="S156" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17835,22 +17839,12 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z156" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB156" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17859,74 +17853,76 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122930166</t>
+          <t>https://artportalen.se/Sighting/101544040</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>119061006</v>
+        <v>122930166</v>
       </c>
       <c r="B157" t="n">
-        <v>91533</v>
+        <v>96554</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>2051</v>
+        <v>210</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
       <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
+      <c r="L157" t="inlineStr"/>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>S Norrby mosse, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>686477</v>
+        <v>686762</v>
       </c>
       <c r="R157" t="n">
-        <v>6562857</v>
+        <v>6562715</v>
       </c>
       <c r="S157" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17950,17 +17946,22 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z157" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC157" t="inlineStr">
-        <is>
-          <t>Brukad skog nära kant mot gammal.</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB157" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17969,81 +17970,74 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
-      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119061006</t>
+          <t>https://artportalen.se/Sighting/122930166</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>122929535</v>
+        <v>119061006</v>
       </c>
       <c r="B158" t="n">
-        <v>8455</v>
+        <v>91533</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>106545</v>
+        <v>2051</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr"/>
       <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
-      <c r="M158" t="inlineStr"/>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>S Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>686612</v>
+        <v>686477</v>
       </c>
       <c r="R158" t="n">
-        <v>6562882</v>
+        <v>6562857</v>
       </c>
       <c r="S158" t="n">
-        <v>9</v>
+        <v>10</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18067,22 +18061,17 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z158" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB158" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Brukad skog nära kant mot gammal.</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18091,33 +18080,34 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
+      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
       <c r="AT158" t="inlineStr"/>
       <c r="AW158" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX158" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929535</t>
+          <t>https://artportalen.se/Sighting/119061006</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>122928987</v>
+        <v>122929535</v>
       </c>
       <c r="B159" t="n">
-        <v>97983</v>
+        <v>8455</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18125,27 +18115,32 @@
         </is>
       </c>
       <c r="E159" t="n">
-        <v>221945</v>
+        <v>106545</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
+      <c r="M159" t="inlineStr"/>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
@@ -18153,13 +18148,13 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>686389</v>
+        <v>686612</v>
       </c>
       <c r="R159" t="n">
-        <v>6562967</v>
+        <v>6562882</v>
       </c>
       <c r="S159" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18188,7 +18183,7 @@
       </c>
       <c r="Z159" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
@@ -18198,7 +18193,7 @@
       </c>
       <c r="AB159" t="inlineStr">
         <is>
-          <t>10:36</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18224,51 +18219,55 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122928987</t>
+          <t>https://artportalen.se/Sighting/122929535</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>126061106</v>
+        <v>122928987</v>
       </c>
       <c r="B160" t="n">
-        <v>91333</v>
+        <v>97983</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>2008</v>
+        <v>221945</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I160" t="inlineStr"/>
+      <c r="J160" t="inlineStr"/>
+      <c r="K160" t="inlineStr"/>
+      <c r="L160" t="inlineStr"/>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>686883</v>
+        <v>686389</v>
       </c>
       <c r="R160" t="n">
-        <v>6562742</v>
+        <v>6562967</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18295,22 +18294,22 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z160" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB160" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18325,49 +18324,49 @@
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061106</t>
+          <t>https://artportalen.se/Sighting/122928987</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126061107</v>
+        <v>126061106</v>
       </c>
       <c r="B161" t="n">
-        <v>96458</v>
+        <v>91333</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2818</v>
+        <v>2008</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
@@ -18377,10 +18376,10 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>686880</v>
+        <v>686883</v>
       </c>
       <c r="R161" t="n">
-        <v>6562745</v>
+        <v>6562742</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18412,7 +18411,7 @@
       </c>
       <c r="Z161" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
@@ -18422,7 +18421,7 @@
       </c>
       <c r="AB161" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18448,16 +18447,16 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061107</t>
+          <t>https://artportalen.se/Sighting/126061106</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>129215187</v>
+        <v>126061107</v>
       </c>
       <c r="B162" t="n">
-        <v>91872</v>
+        <v>96458</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18465,37 +18464,34 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>5447</v>
+        <v>2818</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
-      <c r="J162" t="inlineStr"/>
-      <c r="K162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>686977</v>
+        <v>686880</v>
       </c>
       <c r="R162" t="n">
-        <v>6562706</v>
+        <v>6562745</v>
       </c>
       <c r="S162" t="n">
         <v>10</v>
@@ -18522,12 +18518,22 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z162" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB162" t="inlineStr">
+        <is>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18536,34 +18542,33 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
-      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215187</t>
+          <t>https://artportalen.se/Sighting/126061107</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>126061104</v>
+        <v>129215187</v>
       </c>
       <c r="B163" t="n">
-        <v>4775</v>
+        <v>91872</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18571,34 +18576,37 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>100299</v>
+        <v>5447</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
+      <c r="J163" t="inlineStr"/>
+      <c r="K163" t="inlineStr"/>
+      <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>686868</v>
+        <v>686977</v>
       </c>
       <c r="R163" t="n">
-        <v>6562739</v>
+        <v>6562706</v>
       </c>
       <c r="S163" t="n">
         <v>10</v>
@@ -18625,22 +18633,12 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18649,53 +18647,34 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ163" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK163" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL163" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO163" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061104</t>
+          <t>https://artportalen.se/Sighting/129215187</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126061116</v>
+        <v>126061104</v>
       </c>
       <c r="B164" t="n">
-        <v>44177</v>
+        <v>4775</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
@@ -18703,21 +18682,21 @@
         </is>
       </c>
       <c r="E164" t="n">
-        <v>101735</v>
+        <v>100299</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Kraatz, 1881)</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
@@ -18727,10 +18706,10 @@
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>686928</v>
+        <v>686868</v>
       </c>
       <c r="R164" t="n">
-        <v>6562716</v>
+        <v>6562739</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18762,7 +18741,7 @@
       </c>
       <c r="Z164" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
@@ -18772,7 +18751,7 @@
       </c>
       <c r="AB164" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18786,22 +18765,22 @@
       </c>
       <c r="AJ164" t="inlineStr">
         <is>
-          <t>fnöskticka</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK164" t="inlineStr">
         <is>
-          <t>Fomes fomentarius</t>
+          <t>Picea abies</t>
         </is>
       </c>
       <c r="AL164" t="inlineStr">
         <is>
-          <t>Fnöskticka på björk.</t>
+          <t>Stående död gran.</t>
         </is>
       </c>
       <c r="AO164" t="inlineStr">
         <is>
-          <t>Fomes fomentarius # Fnöskticka på björk.</t>
+          <t>Picea abies # Stående död gran.</t>
         </is>
       </c>
       <c r="AT164" t="inlineStr"/>
@@ -18818,16 +18797,16 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061116</t>
+          <t>https://artportalen.se/Sighting/126061104</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>125974903</v>
+        <v>126061116</v>
       </c>
       <c r="B165" t="n">
-        <v>8444</v>
+        <v>44177</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18835,50 +18814,37 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J165" t="inlineStr"/>
-      <c r="K165" t="inlineStr"/>
-      <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N165" t="inlineStr"/>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>686838</v>
+        <v>686928</v>
       </c>
       <c r="R165" t="n">
-        <v>6562733</v>
+        <v>6562716</v>
       </c>
       <c r="S165" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18905,14 +18871,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z165" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
       <c r="AA165" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC165" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+      <c r="AB165" t="inlineStr">
+        <is>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18921,51 +18892,50 @@
       <c r="AE165" t="b">
         <v>0</v>
       </c>
-      <c r="AF165" t="inlineStr"/>
       <c r="AG165" t="b">
         <v>0</v>
       </c>
       <c r="AJ165" t="inlineStr">
         <is>
-          <t>vårtbjörk</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK165" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM165" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AL165" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AO165" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
+          <t>Fomes fomentarius # Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974903</t>
+          <t>https://artportalen.se/Sighting/126061116</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>126061105</v>
+        <v>125974903</v>
       </c>
       <c r="B166" t="n">
         <v>8444</v>
@@ -18993,20 +18963,33 @@
           <t>Janson, 1856</t>
         </is>
       </c>
-      <c r="I166" t="inlineStr"/>
+      <c r="I166" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J166" t="inlineStr"/>
+      <c r="K166" t="inlineStr"/>
+      <c r="L166" t="inlineStr"/>
+      <c r="M166" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>söder om Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>686860</v>
+        <v>686838</v>
       </c>
       <c r="R166" t="n">
-        <v>6562743</v>
+        <v>6562733</v>
       </c>
       <c r="S166" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19033,19 +19016,14 @@
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>13:36</t>
-        </is>
-      </c>
       <c r="AA166" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>13:36</t>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19054,37 +19032,170 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AJ166" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>vårtbjörk</t>
         </is>
       </c>
       <c r="AK166" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM166" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
         </is>
       </c>
       <c r="AO166" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Wood surface of dead wood # Betula pendula</t>
         </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Nette Bygren</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125974903</t>
+        </is>
+      </c>
+    </row>
+    <row r="167">
+      <c r="A167" t="n">
+        <v>126061105</v>
+      </c>
+      <c r="B167" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D167" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E167" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F167" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G167" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H167" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr"/>
+      <c r="P167" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q167" t="n">
+        <v>686860</v>
+      </c>
+      <c r="R167" t="n">
+        <v>6562743</v>
+      </c>
+      <c r="S167" t="n">
+        <v>10</v>
+      </c>
+      <c r="T167" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U167" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V167" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W167" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y167" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z167" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA167" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB167" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG167" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ167" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK167" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO167" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT167" t="inlineStr"/>
+      <c r="AW167" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX167" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY167" t="inlineStr"/>
+      <c r="AZ167" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126061105</t>
         </is>
@@ -19257,6 +19368,7 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ164" r:id="rId163"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -1976,7 +1976,7 @@
         <v>136261113</v>
       </c>
       <c r="B14" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>136138429</v>
       </c>
       <c r="B23" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136159959</v>
       </c>
       <c r="B24" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>136193282</v>
       </c>
       <c r="B25" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>136193424</v>
       </c>
       <c r="B26" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136232449</v>
       </c>
       <c r="B27" t="n">
-        <v>93365</v>
+        <v>93371</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>136259823</v>
       </c>
       <c r="B41" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>136138543</v>
       </c>
       <c r="B50" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136138586</v>
       </c>
       <c r="B51" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136159945</v>
       </c>
       <c r="B52" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>136160087</v>
       </c>
       <c r="B53" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>135827249</v>
       </c>
       <c r="B65" t="n">
-        <v>98164</v>
+        <v>98170</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>136234180</v>
       </c>
       <c r="B70" t="n">
-        <v>98158</v>
+        <v>98164</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>136234148</v>
       </c>
       <c r="B72" t="n">
-        <v>98161</v>
+        <v>98167</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -15420,7 +15420,7 @@
         <v>135358856</v>
       </c>
       <c r="B135" t="n">
-        <v>91538</v>
+        <v>91544</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
@@ -15530,7 +15530,7 @@
         <v>136241603</v>
       </c>
       <c r="B136" t="n">
-        <v>96881</v>
+        <v>96887</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15647,7 +15647,7 @@
         <v>136231090</v>
       </c>
       <c r="B137" t="n">
-        <v>96599</v>
+        <v>96605</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15863,7 +15863,7 @@
         <v>136268106</v>
       </c>
       <c r="B139" t="n">
-        <v>92030</v>
+        <v>92036</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
@@ -16398,7 +16398,7 @@
         <v>136241765</v>
       </c>
       <c r="B144" t="n">
-        <v>80064</v>
+        <v>80068</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -17315,7 +17315,7 @@
         <v>136138855</v>
       </c>
       <c r="B152" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17425,7 +17425,7 @@
         <v>136138971</v>
       </c>
       <c r="B153" t="n">
-        <v>58144</v>
+        <v>58148</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17660,7 +17660,7 @@
         <v>136241491</v>
       </c>
       <c r="B155" t="n">
-        <v>58820</v>
+        <v>58824</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ167"/>
+  <dimension ref="A1:AZ173"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -1976,7 +1976,7 @@
         <v>136261113</v>
       </c>
       <c r="B14" t="n">
-        <v>96887</v>
+        <v>96888</v>
       </c>
       <c r="D14" t="inlineStr">
         <is>
@@ -2951,7 +2951,7 @@
         <v>136138429</v>
       </c>
       <c r="B23" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D23" t="inlineStr">
         <is>
@@ -3057,7 +3057,7 @@
         <v>136159959</v>
       </c>
       <c r="B24" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D24" t="inlineStr">
         <is>
@@ -3163,7 +3163,7 @@
         <v>136193282</v>
       </c>
       <c r="B25" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D25" t="inlineStr">
         <is>
@@ -3269,7 +3269,7 @@
         <v>136193424</v>
       </c>
       <c r="B26" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D26" t="inlineStr">
         <is>
@@ -3375,7 +3375,7 @@
         <v>136232449</v>
       </c>
       <c r="B27" t="n">
-        <v>93371</v>
+        <v>93372</v>
       </c>
       <c r="D27" t="inlineStr">
         <is>
@@ -4892,7 +4892,7 @@
         <v>136259823</v>
       </c>
       <c r="B41" t="n">
-        <v>80068</v>
+        <v>80069</v>
       </c>
       <c r="D41" t="inlineStr">
         <is>
@@ -5914,7 +5914,7 @@
         <v>136138543</v>
       </c>
       <c r="B50" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D50" t="inlineStr">
         <is>
@@ -6024,7 +6024,7 @@
         <v>136138586</v>
       </c>
       <c r="B51" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D51" t="inlineStr">
         <is>
@@ -6134,7 +6134,7 @@
         <v>136159945</v>
       </c>
       <c r="B52" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D52" t="inlineStr">
         <is>
@@ -6244,7 +6244,7 @@
         <v>136160087</v>
       </c>
       <c r="B53" t="n">
-        <v>58148</v>
+        <v>58149</v>
       </c>
       <c r="D53" t="inlineStr">
         <is>
@@ -7599,7 +7599,7 @@
         <v>135827249</v>
       </c>
       <c r="B65" t="n">
-        <v>98170</v>
+        <v>98171</v>
       </c>
       <c r="D65" t="inlineStr">
         <is>
@@ -8154,7 +8154,7 @@
         <v>136234180</v>
       </c>
       <c r="B70" t="n">
-        <v>98164</v>
+        <v>98165</v>
       </c>
       <c r="D70" t="inlineStr">
         <is>
@@ -8372,7 +8372,7 @@
         <v>136234148</v>
       </c>
       <c r="B72" t="n">
-        <v>98167</v>
+        <v>98168</v>
       </c>
       <c r="D72" t="inlineStr">
         <is>
@@ -10134,10 +10134,10 @@
     </row>
     <row r="88">
       <c r="A88" t="n">
-        <v>121859626</v>
+        <v>136329952</v>
       </c>
       <c r="B88" t="n">
-        <v>91930</v>
+        <v>93372</v>
       </c>
       <c r="D88" t="inlineStr">
         <is>
@@ -10145,34 +10145,45 @@
         </is>
       </c>
       <c r="E88" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F88" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G88" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H88" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I88" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I88" t="inlineStr">
+        <is>
+          <t>8</t>
+        </is>
+      </c>
+      <c r="J88" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K88" t="inlineStr"/>
+      <c r="N88" t="inlineStr"/>
       <c r="P88" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q88" t="n">
-        <v>686670</v>
+        <v>686664</v>
       </c>
       <c r="R88" t="n">
-        <v>6563032</v>
+        <v>6563111</v>
       </c>
       <c r="S88" t="n">
         <v>10</v>
@@ -10199,22 +10210,12 @@
       </c>
       <c r="Y88" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z88" t="inlineStr">
-        <is>
-          <t>17:20</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA88" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB88" t="inlineStr">
-        <is>
-          <t>17:20</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD88" t="b">
@@ -10223,53 +10224,34 @@
       <c r="AE88" t="b">
         <v>0</v>
       </c>
+      <c r="AF88" t="inlineStr"/>
       <c r="AG88" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ88" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK88" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL88" t="inlineStr">
-        <is>
-          <t>Levande äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO88" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Levande äldre tall.</t>
-        </is>
       </c>
       <c r="AT88" t="inlineStr"/>
       <c r="AW88" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX88" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY88" t="inlineStr"/>
       <c r="AZ88" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859626</t>
+          <t>https://artportalen.se/Sighting/136329952</t>
         </is>
       </c>
     </row>
     <row r="89">
       <c r="A89" t="n">
-        <v>128457948</v>
+        <v>136330044</v>
       </c>
       <c r="B89" t="n">
-        <v>91930</v>
+        <v>93372</v>
       </c>
       <c r="D89" t="inlineStr">
         <is>
@@ -10277,24 +10259,28 @@
         </is>
       </c>
       <c r="E89" t="n">
-        <v>5442</v>
+        <v>4364</v>
       </c>
       <c r="F89" t="inlineStr">
         <is>
-          <t>Tallticka</t>
+          <t>Dropptaggsvamp</t>
         </is>
       </c>
       <c r="G89" t="inlineStr">
         <is>
-          <t>Porodaedalea pini</t>
+          <t>Hydnellum ferrugineum</t>
         </is>
       </c>
       <c r="H89" t="inlineStr">
         <is>
-          <t>(Brot.) Murrill</t>
-        </is>
-      </c>
-      <c r="I89" t="inlineStr"/>
+          <t>(Fr.:Fr.) P. Karst.</t>
+        </is>
+      </c>
+      <c r="I89" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J89" t="inlineStr"/>
       <c r="K89" t="inlineStr"/>
       <c r="N89" t="inlineStr"/>
@@ -10304,10 +10290,10 @@
         </is>
       </c>
       <c r="Q89" t="n">
-        <v>686513</v>
+        <v>686676</v>
       </c>
       <c r="R89" t="n">
-        <v>6563109</v>
+        <v>6563139</v>
       </c>
       <c r="S89" t="n">
         <v>10</v>
@@ -10334,12 +10320,12 @@
       </c>
       <c r="Y89" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA89" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD89" t="b">
@@ -10366,13 +10352,13 @@
       <c r="AY89" t="inlineStr"/>
       <c r="AZ89" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128457948</t>
+          <t>https://artportalen.se/Sighting/136330044</t>
         </is>
       </c>
     </row>
     <row r="90">
       <c r="A90" t="n">
-        <v>129564462</v>
+        <v>121859626</v>
       </c>
       <c r="B90" t="n">
         <v>91930</v>
@@ -10400,24 +10386,17 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I90" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J90" t="inlineStr"/>
-      <c r="K90" t="inlineStr"/>
-      <c r="N90" t="inlineStr"/>
+      <c r="I90" t="inlineStr"/>
       <c r="P90" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q90" t="n">
-        <v>686728</v>
+        <v>686670</v>
       </c>
       <c r="R90" t="n">
-        <v>6563110</v>
+        <v>6563032</v>
       </c>
       <c r="S90" t="n">
         <v>10</v>
@@ -10444,17 +10423,22 @@
       </c>
       <c r="Y90" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z90" t="inlineStr">
+        <is>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AA90" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
-        </is>
-      </c>
-      <c r="AC90" t="inlineStr">
-        <is>
-          <t>Död tallticka på död tallraka.</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB90" t="inlineStr">
+        <is>
+          <t>17:20</t>
         </is>
       </c>
       <c r="AD90" t="b">
@@ -10463,31 +10447,50 @@
       <c r="AE90" t="b">
         <v>0</v>
       </c>
-      <c r="AF90" t="inlineStr"/>
       <c r="AG90" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ90" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK90" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL90" t="inlineStr">
+        <is>
+          <t>Levande äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO90" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Levande äldre tall.</t>
+        </is>
       </c>
       <c r="AT90" t="inlineStr"/>
       <c r="AW90" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX90" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY90" t="inlineStr"/>
       <c r="AZ90" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129564462</t>
+          <t>https://artportalen.se/Sighting/121859626</t>
         </is>
       </c>
     </row>
     <row r="91">
       <c r="A91" t="n">
-        <v>129564997</v>
+        <v>128457948</v>
       </c>
       <c r="B91" t="n">
         <v>91930</v>
@@ -10525,10 +10528,10 @@
         </is>
       </c>
       <c r="Q91" t="n">
-        <v>686661</v>
+        <v>686513</v>
       </c>
       <c r="R91" t="n">
-        <v>6563208</v>
+        <v>6563109</v>
       </c>
       <c r="S91" t="n">
         <v>10</v>
@@ -10555,12 +10558,12 @@
       </c>
       <c r="Y91" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA91" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD91" t="b">
@@ -10587,13 +10590,13 @@
       <c r="AY91" t="inlineStr"/>
       <c r="AZ91" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129564997</t>
+          <t>https://artportalen.se/Sighting/128457948</t>
         </is>
       </c>
     </row>
     <row r="92">
       <c r="A92" t="n">
-        <v>129591539</v>
+        <v>129564462</v>
       </c>
       <c r="B92" t="n">
         <v>91930</v>
@@ -10621,7 +10624,11 @@
           <t>(Brot.) Murrill</t>
         </is>
       </c>
-      <c r="I92" t="inlineStr"/>
+      <c r="I92" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J92" t="inlineStr"/>
       <c r="K92" t="inlineStr"/>
       <c r="N92" t="inlineStr"/>
@@ -10631,10 +10638,10 @@
         </is>
       </c>
       <c r="Q92" t="n">
-        <v>686710</v>
+        <v>686728</v>
       </c>
       <c r="R92" t="n">
-        <v>6563231</v>
+        <v>6563110</v>
       </c>
       <c r="S92" t="n">
         <v>10</v>
@@ -10661,12 +10668,17 @@
       </c>
       <c r="Y92" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA92" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-06</t>
+        </is>
+      </c>
+      <c r="AC92" t="inlineStr">
+        <is>
+          <t>Död tallticka på död tallraka.</t>
         </is>
       </c>
       <c r="AD92" t="b">
@@ -10693,13 +10705,13 @@
       <c r="AY92" t="inlineStr"/>
       <c r="AZ92" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129591539</t>
+          <t>https://artportalen.se/Sighting/129564462</t>
         </is>
       </c>
     </row>
     <row r="93">
       <c r="A93" t="n">
-        <v>129591551</v>
+        <v>129564997</v>
       </c>
       <c r="B93" t="n">
         <v>91930</v>
@@ -10737,10 +10749,10 @@
         </is>
       </c>
       <c r="Q93" t="n">
-        <v>686710</v>
+        <v>686661</v>
       </c>
       <c r="R93" t="n">
-        <v>6563248</v>
+        <v>6563208</v>
       </c>
       <c r="S93" t="n">
         <v>10</v>
@@ -10767,12 +10779,12 @@
       </c>
       <c r="Y93" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA93" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD93" t="b">
@@ -10799,38 +10811,38 @@
       <c r="AY93" t="inlineStr"/>
       <c r="AZ93" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129591551</t>
+          <t>https://artportalen.se/Sighting/129564997</t>
         </is>
       </c>
     </row>
     <row r="94">
       <c r="A94" t="n">
-        <v>129230377</v>
+        <v>129591539</v>
       </c>
       <c r="B94" t="n">
-        <v>91872</v>
+        <v>91930</v>
       </c>
       <c r="D94" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E94" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F94" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G94" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H94" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I94" t="inlineStr"/>
@@ -10843,10 +10855,10 @@
         </is>
       </c>
       <c r="Q94" t="n">
-        <v>686662</v>
+        <v>686710</v>
       </c>
       <c r="R94" t="n">
-        <v>6563219</v>
+        <v>6563231</v>
       </c>
       <c r="S94" t="n">
         <v>10</v>
@@ -10873,12 +10885,12 @@
       </c>
       <c r="Y94" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA94" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD94" t="b">
@@ -10905,38 +10917,38 @@
       <c r="AY94" t="inlineStr"/>
       <c r="AZ94" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129230377</t>
+          <t>https://artportalen.se/Sighting/129591539</t>
         </is>
       </c>
     </row>
     <row r="95">
       <c r="A95" t="n">
-        <v>129230409</v>
+        <v>129591551</v>
       </c>
       <c r="B95" t="n">
-        <v>91872</v>
+        <v>91930</v>
       </c>
       <c r="D95" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E95" t="n">
-        <v>5447</v>
+        <v>5442</v>
       </c>
       <c r="F95" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G95" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H95" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I95" t="inlineStr"/>
@@ -10949,10 +10961,10 @@
         </is>
       </c>
       <c r="Q95" t="n">
-        <v>686777</v>
+        <v>686710</v>
       </c>
       <c r="R95" t="n">
-        <v>6563285</v>
+        <v>6563248</v>
       </c>
       <c r="S95" t="n">
         <v>10</v>
@@ -10979,12 +10991,12 @@
       </c>
       <c r="Y95" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA95" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD95" t="b">
@@ -11011,16 +11023,16 @@
       <c r="AY95" t="inlineStr"/>
       <c r="AZ95" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129230409</t>
+          <t>https://artportalen.se/Sighting/129591551</t>
         </is>
       </c>
     </row>
     <row r="96">
       <c r="A96" t="n">
-        <v>128886665</v>
+        <v>136330155</v>
       </c>
       <c r="B96" t="n">
-        <v>93223</v>
+        <v>92095</v>
       </c>
       <c r="D96" t="inlineStr">
         <is>
@@ -11028,21 +11040,21 @@
         </is>
       </c>
       <c r="E96" t="n">
-        <v>5448</v>
+        <v>5442</v>
       </c>
       <c r="F96" t="inlineStr">
         <is>
-          <t>Svartvit taggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G96" t="inlineStr">
         <is>
-          <t>Phellodon melaleucus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H96" t="inlineStr">
         <is>
-          <t>(Sw. ex Fr.) P.Karst.</t>
+          <t>(Brot.) Murrill</t>
         </is>
       </c>
       <c r="I96" t="inlineStr"/>
@@ -11055,10 +11067,10 @@
         </is>
       </c>
       <c r="Q96" t="n">
-        <v>686681</v>
+        <v>686723</v>
       </c>
       <c r="R96" t="n">
-        <v>6563136</v>
+        <v>6563229</v>
       </c>
       <c r="S96" t="n">
         <v>10</v>
@@ -11085,12 +11097,12 @@
       </c>
       <c r="Y96" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA96" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD96" t="b">
@@ -11117,16 +11129,16 @@
       <c r="AY96" t="inlineStr"/>
       <c r="AZ96" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128886665</t>
+          <t>https://artportalen.se/Sighting/136330155</t>
         </is>
       </c>
     </row>
     <row r="97">
       <c r="A97" t="n">
-        <v>128342127</v>
+        <v>136330904</v>
       </c>
       <c r="B97" t="n">
-        <v>93235</v>
+        <v>92095</v>
       </c>
       <c r="D97" t="inlineStr">
         <is>
@@ -11134,25 +11146,33 @@
         </is>
       </c>
       <c r="E97" t="n">
-        <v>5966</v>
+        <v>5442</v>
       </c>
       <c r="F97" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Tallticka</t>
         </is>
       </c>
       <c r="G97" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Porodaedalea pini</t>
         </is>
       </c>
       <c r="H97" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I97" t="inlineStr"/>
-      <c r="J97" t="inlineStr"/>
+          <t>(Brot.) Murrill</t>
+        </is>
+      </c>
+      <c r="I97" t="inlineStr">
+        <is>
+          <t>2</t>
+        </is>
+      </c>
+      <c r="J97" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K97" t="inlineStr"/>
       <c r="N97" t="inlineStr"/>
       <c r="P97" t="inlineStr">
@@ -11161,10 +11181,10 @@
         </is>
       </c>
       <c r="Q97" t="n">
-        <v>686643</v>
+        <v>686707</v>
       </c>
       <c r="R97" t="n">
-        <v>6563078</v>
+        <v>6563221</v>
       </c>
       <c r="S97" t="n">
         <v>10</v>
@@ -11191,12 +11211,17 @@
       </c>
       <c r="Y97" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA97" t="inlineStr">
         <is>
-          <t>2025-09-09</t>
+          <t>2026-09-03</t>
+        </is>
+      </c>
+      <c r="AC97" t="inlineStr">
+        <is>
+          <t>På tall med jaktsnitsel runt stammen.</t>
         </is>
       </c>
       <c r="AD97" t="b">
@@ -11223,38 +11248,38 @@
       <c r="AY97" t="inlineStr"/>
       <c r="AZ97" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128342127</t>
+          <t>https://artportalen.se/Sighting/136330904</t>
         </is>
       </c>
     </row>
     <row r="98">
       <c r="A98" t="n">
-        <v>128457671</v>
+        <v>129230377</v>
       </c>
       <c r="B98" t="n">
-        <v>93235</v>
+        <v>91872</v>
       </c>
       <c r="D98" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E98" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F98" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G98" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H98" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I98" t="inlineStr"/>
@@ -11267,10 +11292,10 @@
         </is>
       </c>
       <c r="Q98" t="n">
-        <v>686516</v>
+        <v>686662</v>
       </c>
       <c r="R98" t="n">
-        <v>6563005</v>
+        <v>6563219</v>
       </c>
       <c r="S98" t="n">
         <v>10</v>
@@ -11297,12 +11322,12 @@
       </c>
       <c r="Y98" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA98" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD98" t="b">
@@ -11329,38 +11354,38 @@
       <c r="AY98" t="inlineStr"/>
       <c r="AZ98" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128457671</t>
+          <t>https://artportalen.se/Sighting/129230377</t>
         </is>
       </c>
     </row>
     <row r="99">
       <c r="A99" t="n">
-        <v>128457697</v>
+        <v>129230409</v>
       </c>
       <c r="B99" t="n">
-        <v>93235</v>
+        <v>91872</v>
       </c>
       <c r="D99" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E99" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F99" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G99" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H99" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I99" t="inlineStr"/>
@@ -11373,10 +11398,10 @@
         </is>
       </c>
       <c r="Q99" t="n">
-        <v>686585</v>
+        <v>686777</v>
       </c>
       <c r="R99" t="n">
-        <v>6563030</v>
+        <v>6563285</v>
       </c>
       <c r="S99" t="n">
         <v>10</v>
@@ -11403,12 +11428,12 @@
       </c>
       <c r="Y99" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA99" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD99" t="b">
@@ -11435,16 +11460,16 @@
       <c r="AY99" t="inlineStr"/>
       <c r="AZ99" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128457697</t>
+          <t>https://artportalen.se/Sighting/129230409</t>
         </is>
       </c>
     </row>
     <row r="100">
       <c r="A100" t="n">
-        <v>128457855</v>
+        <v>128886665</v>
       </c>
       <c r="B100" t="n">
-        <v>93235</v>
+        <v>93223</v>
       </c>
       <c r="D100" t="inlineStr">
         <is>
@@ -11452,21 +11477,21 @@
         </is>
       </c>
       <c r="E100" t="n">
-        <v>5966</v>
+        <v>5448</v>
       </c>
       <c r="F100" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Svartvit taggsvamp</t>
         </is>
       </c>
       <c r="G100" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellodon melaleucus</t>
         </is>
       </c>
       <c r="H100" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Sw. ex Fr.) P.Karst.</t>
         </is>
       </c>
       <c r="I100" t="inlineStr"/>
@@ -11479,10 +11504,10 @@
         </is>
       </c>
       <c r="Q100" t="n">
-        <v>686750</v>
+        <v>686681</v>
       </c>
       <c r="R100" t="n">
-        <v>6563149</v>
+        <v>6563136</v>
       </c>
       <c r="S100" t="n">
         <v>10</v>
@@ -11509,12 +11534,12 @@
       </c>
       <c r="Y100" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA100" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD100" t="b">
@@ -11541,13 +11566,13 @@
       <c r="AY100" t="inlineStr"/>
       <c r="AZ100" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128457855</t>
+          <t>https://artportalen.se/Sighting/128886665</t>
         </is>
       </c>
     </row>
     <row r="101">
       <c r="A101" t="n">
-        <v>128457938</v>
+        <v>128342127</v>
       </c>
       <c r="B101" t="n">
         <v>93235</v>
@@ -11585,10 +11610,10 @@
         </is>
       </c>
       <c r="Q101" t="n">
-        <v>686520</v>
+        <v>686643</v>
       </c>
       <c r="R101" t="n">
-        <v>6563068</v>
+        <v>6563078</v>
       </c>
       <c r="S101" t="n">
         <v>10</v>
@@ -11615,12 +11640,12 @@
       </c>
       <c r="Y101" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AA101" t="inlineStr">
         <is>
-          <t>2025-09-13</t>
+          <t>2025-09-09</t>
         </is>
       </c>
       <c r="AD101" t="b">
@@ -11647,13 +11672,13 @@
       <c r="AY101" t="inlineStr"/>
       <c r="AZ101" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128457938</t>
+          <t>https://artportalen.se/Sighting/128342127</t>
         </is>
       </c>
     </row>
     <row r="102">
       <c r="A102" t="n">
-        <v>128510579</v>
+        <v>128457671</v>
       </c>
       <c r="B102" t="n">
         <v>93235</v>
@@ -11691,10 +11716,10 @@
         </is>
       </c>
       <c r="Q102" t="n">
-        <v>686754</v>
+        <v>686516</v>
       </c>
       <c r="R102" t="n">
-        <v>6563192</v>
+        <v>6563005</v>
       </c>
       <c r="S102" t="n">
         <v>10</v>
@@ -11721,12 +11746,12 @@
       </c>
       <c r="Y102" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA102" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD102" t="b">
@@ -11753,38 +11778,38 @@
       <c r="AY102" t="inlineStr"/>
       <c r="AZ102" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128510579</t>
+          <t>https://artportalen.se/Sighting/128457671</t>
         </is>
       </c>
     </row>
     <row r="103">
       <c r="A103" t="n">
-        <v>128646813</v>
+        <v>128457697</v>
       </c>
       <c r="B103" t="n">
-        <v>92567</v>
+        <v>93235</v>
       </c>
       <c r="D103" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E103" t="n">
-        <v>6031</v>
+        <v>5966</v>
       </c>
       <c r="F103" t="inlineStr">
         <is>
-          <t>Blomkålssvamp</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G103" t="inlineStr">
         <is>
-          <t>Sparassis crispa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H103" t="inlineStr">
         <is>
-          <t>(Wulfen:Fr.) Fr.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I103" t="inlineStr"/>
@@ -11797,10 +11822,10 @@
         </is>
       </c>
       <c r="Q103" t="n">
-        <v>686827</v>
+        <v>686585</v>
       </c>
       <c r="R103" t="n">
-        <v>6563224</v>
+        <v>6563030</v>
       </c>
       <c r="S103" t="n">
         <v>10</v>
@@ -11827,12 +11852,12 @@
       </c>
       <c r="Y103" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA103" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD103" t="b">
@@ -11859,58 +11884,54 @@
       <c r="AY103" t="inlineStr"/>
       <c r="AZ103" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128646813</t>
+          <t>https://artportalen.se/Sighting/128457697</t>
         </is>
       </c>
     </row>
     <row r="104">
       <c r="A104" t="n">
-        <v>112337759</v>
+        <v>128457855</v>
       </c>
       <c r="B104" t="n">
-        <v>90691</v>
+        <v>93235</v>
       </c>
       <c r="D104" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E104" t="n">
-        <v>6276</v>
+        <v>5966</v>
       </c>
       <c r="F104" t="inlineStr">
         <is>
-          <t>Goliatmusseron</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G104" t="inlineStr">
         <is>
-          <t>Tricholoma matsutake</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H104" t="inlineStr">
         <is>
-          <t>(S.Ito &amp; S.Imai) Singer</t>
-        </is>
-      </c>
-      <c r="I104" t="inlineStr">
-        <is>
-          <t>4</t>
-        </is>
-      </c>
+          <t>(Schaeff.) Quél.</t>
+        </is>
+      </c>
+      <c r="I104" t="inlineStr"/>
       <c r="J104" t="inlineStr"/>
       <c r="K104" t="inlineStr"/>
       <c r="N104" t="inlineStr"/>
       <c r="P104" t="inlineStr">
         <is>
-          <t>Norrby Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q104" t="n">
-        <v>686738</v>
+        <v>686750</v>
       </c>
       <c r="R104" t="n">
-        <v>6563118</v>
+        <v>6563149</v>
       </c>
       <c r="S104" t="n">
         <v>10</v>
@@ -11937,12 +11958,12 @@
       </c>
       <c r="Y104" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA104" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD104" t="b">
@@ -11969,38 +11990,38 @@
       <c r="AY104" t="inlineStr"/>
       <c r="AZ104" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112337759</t>
+          <t>https://artportalen.se/Sighting/128457855</t>
         </is>
       </c>
     </row>
     <row r="105">
       <c r="A105" t="n">
-        <v>129591415</v>
+        <v>128457938</v>
       </c>
       <c r="B105" t="n">
-        <v>79327</v>
+        <v>93235</v>
       </c>
       <c r="D105" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E105" t="n">
-        <v>6425</v>
+        <v>5966</v>
       </c>
       <c r="F105" t="inlineStr">
         <is>
-          <t>Garnlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G105" t="inlineStr">
         <is>
-          <t>Alectoria sarmentosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H105" t="inlineStr">
         <is>
-          <t>(Ach.) Ach.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I105" t="inlineStr"/>
@@ -12013,10 +12034,10 @@
         </is>
       </c>
       <c r="Q105" t="n">
-        <v>686678</v>
+        <v>686520</v>
       </c>
       <c r="R105" t="n">
-        <v>6563229</v>
+        <v>6563068</v>
       </c>
       <c r="S105" t="n">
         <v>10</v>
@@ -12043,17 +12064,12 @@
       </c>
       <c r="Y105" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AA105" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
-        </is>
-      </c>
-      <c r="AC105" t="inlineStr">
-        <is>
-          <t>På tallstam samt några delar av bålen som lossnat och hamnat på en liten gran.</t>
+          <t>2025-09-13</t>
         </is>
       </c>
       <c r="AD105" t="b">
@@ -12080,38 +12096,38 @@
       <c r="AY105" t="inlineStr"/>
       <c r="AZ105" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129591415</t>
+          <t>https://artportalen.se/Sighting/128457938</t>
         </is>
       </c>
     </row>
     <row r="106">
       <c r="A106" t="n">
-        <v>96643356</v>
+        <v>128510579</v>
       </c>
       <c r="B106" t="n">
-        <v>79351</v>
+        <v>93235</v>
       </c>
       <c r="D106" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E106" t="n">
-        <v>6434</v>
+        <v>5966</v>
       </c>
       <c r="F106" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G106" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H106" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I106" t="inlineStr"/>
@@ -12120,14 +12136,14 @@
       <c r="N106" t="inlineStr"/>
       <c r="P106" t="inlineStr">
         <is>
-          <t>Norrby mosse S om, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q106" t="n">
-        <v>686692</v>
+        <v>686754</v>
       </c>
       <c r="R106" t="n">
-        <v>6563028</v>
+        <v>6563192</v>
       </c>
       <c r="S106" t="n">
         <v>10</v>
@@ -12154,12 +12170,12 @@
       </c>
       <c r="Y106" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA106" t="inlineStr">
         <is>
-          <t>2021-10-12</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD106" t="b">
@@ -12175,27 +12191,27 @@
       <c r="AT106" t="inlineStr"/>
       <c r="AW106" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX106" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY106" t="inlineStr"/>
       <c r="AZ106" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/96643356</t>
+          <t>https://artportalen.se/Sighting/128510579</t>
         </is>
       </c>
     </row>
     <row r="107">
       <c r="A107" t="n">
-        <v>97239536</v>
+        <v>128646813</v>
       </c>
       <c r="B107" t="n">
-        <v>79351</v>
+        <v>92567</v>
       </c>
       <c r="D107" t="inlineStr">
         <is>
@@ -12203,21 +12219,21 @@
         </is>
       </c>
       <c r="E107" t="n">
-        <v>6434</v>
+        <v>6031</v>
       </c>
       <c r="F107" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Blomkålssvamp</t>
         </is>
       </c>
       <c r="G107" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Sparassis crispa</t>
         </is>
       </c>
       <c r="H107" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Wulfen:Fr.) Fr.</t>
         </is>
       </c>
       <c r="I107" t="inlineStr"/>
@@ -12226,17 +12242,17 @@
       <c r="N107" t="inlineStr"/>
       <c r="P107" t="inlineStr">
         <is>
-          <t>S Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q107" t="n">
-        <v>686697</v>
+        <v>686827</v>
       </c>
       <c r="R107" t="n">
-        <v>6563033</v>
+        <v>6563224</v>
       </c>
       <c r="S107" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T107" t="inlineStr">
         <is>
@@ -12260,27 +12276,12 @@
       </c>
       <c r="Y107" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="Z107" t="inlineStr">
-        <is>
-          <t>11:14</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA107" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
-        </is>
-      </c>
-      <c r="AB107" t="inlineStr">
-        <is>
-          <t>11:14</t>
-        </is>
-      </c>
-      <c r="AC107" t="inlineStr">
-        <is>
-          <t>Förevisade av Bodil och Ulf</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD107" t="b">
@@ -12296,65 +12297,69 @@
       <c r="AT107" t="inlineStr"/>
       <c r="AW107" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX107" t="inlineStr">
         <is>
-          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY107" t="inlineStr"/>
       <c r="AZ107" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/97239536</t>
+          <t>https://artportalen.se/Sighting/128646813</t>
         </is>
       </c>
     </row>
     <row r="108">
       <c r="A108" t="n">
-        <v>106813853</v>
+        <v>112337759</v>
       </c>
       <c r="B108" t="n">
-        <v>79351</v>
+        <v>90691</v>
       </c>
       <c r="D108" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E108" t="n">
-        <v>6434</v>
+        <v>6276</v>
       </c>
       <c r="F108" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Goliatmusseron</t>
         </is>
       </c>
       <c r="G108" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Tricholoma matsutake</t>
         </is>
       </c>
       <c r="H108" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
-        </is>
-      </c>
-      <c r="I108" t="inlineStr"/>
+          <t>(S.Ito &amp; S.Imai) Singer</t>
+        </is>
+      </c>
+      <c r="I108" t="inlineStr">
+        <is>
+          <t>4</t>
+        </is>
+      </c>
       <c r="J108" t="inlineStr"/>
       <c r="K108" t="inlineStr"/>
       <c r="N108" t="inlineStr"/>
       <c r="P108" t="inlineStr">
         <is>
-          <t>Österhaninge, Srm</t>
+          <t>Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q108" t="n">
-        <v>686702</v>
+        <v>686738</v>
       </c>
       <c r="R108" t="n">
-        <v>6563040</v>
+        <v>6563118</v>
       </c>
       <c r="S108" t="n">
         <v>10</v>
@@ -12381,12 +12386,12 @@
       </c>
       <c r="Y108" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA108" t="inlineStr">
         <is>
-          <t>2021-11-20</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AD108" t="b">
@@ -12399,80 +12404,68 @@
       <c r="AG108" t="b">
         <v>0</v>
       </c>
-      <c r="AI108" t="inlineStr">
-        <is>
-          <t>tallhällmark, på bark av Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AP108" t="inlineStr">
-        <is>
-          <t>Stockholm-Naturhistoriska riksmuseet</t>
-        </is>
-      </c>
-      <c r="AR108" t="inlineStr">
-        <is>
-          <t>21-1065</t>
-        </is>
-      </c>
       <c r="AT108" t="inlineStr"/>
       <c r="AW108" t="inlineStr">
         <is>
-          <t>Thomas Strid</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX108" t="inlineStr">
         <is>
-          <t>Thomas Strid, Göran Odelvik, Tiina Laantee, Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY108" t="inlineStr"/>
       <c r="AZ108" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/106813853</t>
+          <t>https://artportalen.se/Sighting/112337759</t>
         </is>
       </c>
     </row>
     <row r="109">
       <c r="A109" t="n">
-        <v>121859628</v>
+        <v>129591415</v>
       </c>
       <c r="B109" t="n">
-        <v>79351</v>
+        <v>79327</v>
       </c>
       <c r="D109" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E109" t="n">
-        <v>6434</v>
+        <v>6425</v>
       </c>
       <c r="F109" t="inlineStr">
         <is>
-          <t>Nästlav</t>
+          <t>Garnlav</t>
         </is>
       </c>
       <c r="G109" t="inlineStr">
         <is>
-          <t>Bryoria furcellata</t>
+          <t>Alectoria sarmentosa</t>
         </is>
       </c>
       <c r="H109" t="inlineStr">
         <is>
-          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+          <t>(Ach.) Ach.</t>
         </is>
       </c>
       <c r="I109" t="inlineStr"/>
+      <c r="J109" t="inlineStr"/>
+      <c r="K109" t="inlineStr"/>
+      <c r="N109" t="inlineStr"/>
       <c r="P109" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q109" t="n">
-        <v>686697</v>
+        <v>686678</v>
       </c>
       <c r="R109" t="n">
-        <v>6563030</v>
+        <v>6563229</v>
       </c>
       <c r="S109" t="n">
         <v>10</v>
@@ -12499,22 +12492,17 @@
       </c>
       <c r="Y109" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z109" t="inlineStr">
-        <is>
-          <t>17:09</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA109" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB109" t="inlineStr">
-        <is>
-          <t>17:09</t>
+          <t>2025-11-07</t>
+        </is>
+      </c>
+      <c r="AC109" t="inlineStr">
+        <is>
+          <t>På tallstam samt några delar av bålen som lossnat och hamnat på en liten gran.</t>
         </is>
       </c>
       <c r="AD109" t="b">
@@ -12523,53 +12511,34 @@
       <c r="AE109" t="b">
         <v>0</v>
       </c>
+      <c r="AF109" t="inlineStr"/>
       <c r="AG109" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ109" t="inlineStr">
-        <is>
-          <t>tall</t>
-        </is>
-      </c>
-      <c r="AK109" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris</t>
-        </is>
-      </c>
-      <c r="AL109" t="inlineStr">
-        <is>
-          <t>Levande äldre tall.</t>
-        </is>
-      </c>
-      <c r="AO109" t="inlineStr">
-        <is>
-          <t>Pinus sylvestris # Levande äldre tall.</t>
-        </is>
       </c>
       <c r="AT109" t="inlineStr"/>
       <c r="AW109" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX109" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY109" t="inlineStr"/>
       <c r="AZ109" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859628</t>
+          <t>https://artportalen.se/Sighting/129591415</t>
         </is>
       </c>
     </row>
     <row r="110">
       <c r="A110" t="n">
-        <v>121859622</v>
+        <v>96643356</v>
       </c>
       <c r="B110" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D110" t="inlineStr">
         <is>
@@ -12577,42 +12546,37 @@
         </is>
       </c>
       <c r="E110" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F110" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G110" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H110" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
         </is>
       </c>
       <c r="I110" t="inlineStr"/>
+      <c r="J110" t="inlineStr"/>
       <c r="K110" t="inlineStr"/>
-      <c r="L110" t="inlineStr"/>
-      <c r="M110" t="inlineStr">
-        <is>
-          <t>äldre spår</t>
-        </is>
-      </c>
       <c r="N110" t="inlineStr"/>
       <c r="P110" t="inlineStr">
         <is>
-          <t>Öster om Tyresta by, Tyresta, Srm</t>
+          <t>Norrby mosse S om, Srm</t>
         </is>
       </c>
       <c r="Q110" t="n">
-        <v>686574</v>
+        <v>686692</v>
       </c>
       <c r="R110" t="n">
-        <v>6562988</v>
+        <v>6563028</v>
       </c>
       <c r="S110" t="n">
         <v>10</v>
@@ -12639,27 +12603,12 @@
       </c>
       <c r="Y110" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="Z110" t="inlineStr">
-        <is>
-          <t>17:37</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AA110" t="inlineStr">
         <is>
-          <t>2024-05-09</t>
-        </is>
-      </c>
-      <c r="AB110" t="inlineStr">
-        <is>
-          <t>17:37</t>
-        </is>
-      </c>
-      <c r="AC110" t="inlineStr">
-        <is>
-          <t>Födosökshack långt ner på stående död tall.</t>
+          <t>2021-10-12</t>
         </is>
       </c>
       <c r="AD110" t="b">
@@ -12668,33 +12617,34 @@
       <c r="AE110" t="b">
         <v>0</v>
       </c>
+      <c r="AF110" t="inlineStr"/>
       <c r="AG110" t="b">
         <v>0</v>
       </c>
       <c r="AT110" t="inlineStr"/>
       <c r="AW110" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX110" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY110" t="inlineStr"/>
       <c r="AZ110" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859622</t>
+          <t>https://artportalen.se/Sighting/96643356</t>
         </is>
       </c>
     </row>
     <row r="111">
       <c r="A111" t="n">
-        <v>122929399</v>
+        <v>97239536</v>
       </c>
       <c r="B111" t="n">
-        <v>57950</v>
+        <v>79351</v>
       </c>
       <c r="D111" t="inlineStr">
         <is>
@@ -12702,45 +12652,40 @@
         </is>
       </c>
       <c r="E111" t="n">
-        <v>100049</v>
+        <v>6434</v>
       </c>
       <c r="F111" t="inlineStr">
         <is>
-          <t>Spillkråka</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G111" t="inlineStr">
         <is>
-          <t>Dryocopus martius</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H111" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I111" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I111" t="inlineStr"/>
+      <c r="J111" t="inlineStr"/>
       <c r="K111" t="inlineStr"/>
-      <c r="L111" t="inlineStr"/>
-      <c r="M111" t="inlineStr"/>
       <c r="N111" t="inlineStr"/>
       <c r="P111" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>S Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q111" t="n">
-        <v>686567</v>
+        <v>686697</v>
       </c>
       <c r="R111" t="n">
-        <v>6562954</v>
+        <v>6563033</v>
       </c>
       <c r="S111" t="n">
-        <v>13</v>
+        <v>5</v>
       </c>
       <c r="T111" t="inlineStr">
         <is>
@@ -12764,22 +12709,27 @@
       </c>
       <c r="Y111" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="Z111" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:14</t>
         </is>
       </c>
       <c r="AA111" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AB111" t="inlineStr">
         <is>
-          <t>10:54</t>
+          <t>11:14</t>
+        </is>
+      </c>
+      <c r="AC111" t="inlineStr">
+        <is>
+          <t>Förevisade av Bodil och Ulf</t>
         </is>
       </c>
       <c r="AD111" t="b">
@@ -12788,33 +12738,34 @@
       <c r="AE111" t="b">
         <v>0</v>
       </c>
+      <c r="AF111" t="inlineStr"/>
       <c r="AG111" t="b">
         <v>0</v>
       </c>
       <c r="AT111" t="inlineStr"/>
       <c r="AW111" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX111" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Thomas Strid, Bodil Ravn, Ulf Johansson, Tiina Laantee</t>
         </is>
       </c>
       <c r="AY111" t="inlineStr"/>
       <c r="AZ111" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929399</t>
+          <t>https://artportalen.se/Sighting/97239536</t>
         </is>
       </c>
     </row>
     <row r="112">
       <c r="A112" t="n">
-        <v>126418797</v>
+        <v>106813853</v>
       </c>
       <c r="B112" t="n">
-        <v>56895</v>
+        <v>79351</v>
       </c>
       <c r="D112" t="inlineStr">
         <is>
@@ -12822,43 +12773,37 @@
         </is>
       </c>
       <c r="E112" t="n">
-        <v>100088</v>
+        <v>6434</v>
       </c>
       <c r="F112" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G112" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H112" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I112" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I112" t="inlineStr"/>
       <c r="J112" t="inlineStr"/>
       <c r="K112" t="inlineStr"/>
-      <c r="L112" t="inlineStr"/>
-      <c r="M112" t="inlineStr"/>
       <c r="N112" t="inlineStr"/>
       <c r="P112" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Österhaninge, Srm</t>
         </is>
       </c>
       <c r="Q112" t="n">
-        <v>686803</v>
+        <v>686702</v>
       </c>
       <c r="R112" t="n">
-        <v>6563297</v>
+        <v>6563040</v>
       </c>
       <c r="S112" t="n">
         <v>10</v>
@@ -12885,12 +12830,12 @@
       </c>
       <c r="Y112" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AA112" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2021-11-20</t>
         </is>
       </c>
       <c r="AD112" t="b">
@@ -12903,30 +12848,45 @@
       <c r="AG112" t="b">
         <v>0</v>
       </c>
+      <c r="AI112" t="inlineStr">
+        <is>
+          <t>tallhällmark, på bark av Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AP112" t="inlineStr">
+        <is>
+          <t>Stockholm-Naturhistoriska riksmuseet</t>
+        </is>
+      </c>
+      <c r="AR112" t="inlineStr">
+        <is>
+          <t>21-1065</t>
+        </is>
+      </c>
       <c r="AT112" t="inlineStr"/>
       <c r="AW112" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Thomas Strid</t>
         </is>
       </c>
       <c r="AX112" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Thomas Strid, Göran Odelvik, Tiina Laantee, Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY112" t="inlineStr"/>
       <c r="AZ112" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418797</t>
+          <t>https://artportalen.se/Sighting/106813853</t>
         </is>
       </c>
     </row>
     <row r="113">
       <c r="A113" t="n">
-        <v>134100841</v>
+        <v>121859628</v>
       </c>
       <c r="B113" t="n">
-        <v>56915</v>
+        <v>79351</v>
       </c>
       <c r="D113" t="inlineStr">
         <is>
@@ -12934,43 +12894,34 @@
         </is>
       </c>
       <c r="E113" t="n">
-        <v>100088</v>
+        <v>6434</v>
       </c>
       <c r="F113" t="inlineStr">
         <is>
-          <t>Vanlig snok</t>
+          <t>Nästlav</t>
         </is>
       </c>
       <c r="G113" t="inlineStr">
         <is>
-          <t>Natrix natrix</t>
+          <t>Bryoria furcellata</t>
         </is>
       </c>
       <c r="H113" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I113" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J113" t="inlineStr"/>
-      <c r="K113" t="inlineStr"/>
-      <c r="L113" t="inlineStr"/>
-      <c r="M113" t="inlineStr"/>
-      <c r="N113" t="inlineStr"/>
+          <t>(Fr.) Brodo &amp; D.Hawksw.</t>
+        </is>
+      </c>
+      <c r="I113" t="inlineStr"/>
       <c r="P113" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q113" t="n">
-        <v>686486</v>
+        <v>686697</v>
       </c>
       <c r="R113" t="n">
-        <v>6563086</v>
+        <v>6563030</v>
       </c>
       <c r="S113" t="n">
         <v>10</v>
@@ -12997,12 +12948,22 @@
       </c>
       <c r="Y113" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z113" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AA113" t="inlineStr">
         <is>
-          <t>2026-06-03</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB113" t="inlineStr">
+        <is>
+          <t>17:09</t>
         </is>
       </c>
       <c r="AD113" t="b">
@@ -13011,34 +12972,53 @@
       <c r="AE113" t="b">
         <v>0</v>
       </c>
-      <c r="AF113" t="inlineStr"/>
       <c r="AG113" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ113" t="inlineStr">
+        <is>
+          <t>tall</t>
+        </is>
+      </c>
+      <c r="AK113" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris</t>
+        </is>
+      </c>
+      <c r="AL113" t="inlineStr">
+        <is>
+          <t>Levande äldre tall.</t>
+        </is>
+      </c>
+      <c r="AO113" t="inlineStr">
+        <is>
+          <t>Pinus sylvestris # Levande äldre tall.</t>
+        </is>
       </c>
       <c r="AT113" t="inlineStr"/>
       <c r="AW113" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX113" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY113" t="inlineStr"/>
       <c r="AZ113" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134100841</t>
+          <t>https://artportalen.se/Sighting/121859628</t>
         </is>
       </c>
     </row>
     <row r="114">
       <c r="A114" t="n">
-        <v>121859623</v>
+        <v>121859622</v>
       </c>
       <c r="B114" t="n">
-        <v>5179</v>
+        <v>57950</v>
       </c>
       <c r="D114" t="inlineStr">
         <is>
@@ -13046,39 +13026,42 @@
         </is>
       </c>
       <c r="E114" t="n">
-        <v>100526</v>
+        <v>100049</v>
       </c>
       <c r="F114" t="inlineStr">
         <is>
-          <t>Bronshjon</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G114" t="inlineStr">
         <is>
-          <t>Callidium coriaceum</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H114" t="inlineStr">
         <is>
-          <t>Paykull, 1800</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I114" t="inlineStr"/>
+      <c r="K114" t="inlineStr"/>
+      <c r="L114" t="inlineStr"/>
       <c r="M114" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
+          <t>äldre spår</t>
+        </is>
+      </c>
+      <c r="N114" t="inlineStr"/>
       <c r="P114" t="inlineStr">
         <is>
           <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q114" t="n">
-        <v>686581</v>
+        <v>686574</v>
       </c>
       <c r="R114" t="n">
-        <v>6562989</v>
+        <v>6562988</v>
       </c>
       <c r="S114" t="n">
         <v>10</v>
@@ -13110,7 +13093,7 @@
       </c>
       <c r="Z114" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:37</t>
         </is>
       </c>
       <c r="AA114" t="inlineStr">
@@ -13120,7 +13103,12 @@
       </c>
       <c r="AB114" t="inlineStr">
         <is>
-          <t>17:36</t>
+          <t>17:37</t>
+        </is>
+      </c>
+      <c r="AC114" t="inlineStr">
+        <is>
+          <t>Födosökshack långt ner på stående död tall.</t>
         </is>
       </c>
       <c r="AD114" t="b">
@@ -13131,26 +13119,6 @@
       </c>
       <c r="AG114" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ114" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK114" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL114" t="inlineStr">
-        <is>
-          <t>Granlåga</t>
-        </is>
-      </c>
-      <c r="AO114" t="inlineStr">
-        <is>
-          <t>Picea abies # Granlåga</t>
-        </is>
       </c>
       <c r="AT114" t="inlineStr"/>
       <c r="AW114" t="inlineStr">
@@ -13166,62 +13134,62 @@
       <c r="AY114" t="inlineStr"/>
       <c r="AZ114" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/121859623</t>
+          <t>https://artportalen.se/Sighting/121859622</t>
         </is>
       </c>
     </row>
     <row r="115">
       <c r="A115" t="n">
-        <v>128510434</v>
+        <v>122929399</v>
       </c>
       <c r="B115" t="n">
-        <v>58114</v>
+        <v>57950</v>
       </c>
       <c r="D115" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E115" t="n">
-        <v>103021</v>
+        <v>100049</v>
       </c>
       <c r="F115" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Spillkråka</t>
         </is>
       </c>
       <c r="G115" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Dryocopus martius</t>
         </is>
       </c>
       <c r="H115" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I115" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I115" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K115" t="inlineStr"/>
       <c r="L115" t="inlineStr"/>
-      <c r="M115" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M115" t="inlineStr"/>
       <c r="N115" t="inlineStr"/>
       <c r="P115" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q115" t="n">
-        <v>686650</v>
+        <v>686567</v>
       </c>
       <c r="R115" t="n">
-        <v>6563214</v>
+        <v>6562954</v>
       </c>
       <c r="S115" t="n">
-        <v>10</v>
+        <v>13</v>
       </c>
       <c r="T115" t="inlineStr">
         <is>
@@ -13245,12 +13213,22 @@
       </c>
       <c r="Y115" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z115" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AA115" t="inlineStr">
         <is>
-          <t>2025-09-17</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB115" t="inlineStr">
+        <is>
+          <t>10:54</t>
         </is>
       </c>
       <c r="AD115" t="b">
@@ -13265,59 +13243,60 @@
       <c r="AT115" t="inlineStr"/>
       <c r="AW115" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX115" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY115" t="inlineStr"/>
       <c r="AZ115" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128510434</t>
+          <t>https://artportalen.se/Sighting/122929399</t>
         </is>
       </c>
     </row>
     <row r="116">
       <c r="A116" t="n">
-        <v>128886960</v>
+        <v>126418797</v>
       </c>
       <c r="B116" t="n">
-        <v>58114</v>
+        <v>56895</v>
       </c>
       <c r="D116" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E116" t="n">
-        <v>103021</v>
+        <v>100088</v>
       </c>
       <c r="F116" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G116" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H116" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I116" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I116" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J116" t="inlineStr"/>
       <c r="K116" t="inlineStr"/>
       <c r="L116" t="inlineStr"/>
-      <c r="M116" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M116" t="inlineStr"/>
       <c r="N116" t="inlineStr"/>
       <c r="P116" t="inlineStr">
         <is>
@@ -13325,13 +13304,13 @@
         </is>
       </c>
       <c r="Q116" t="n">
-        <v>686792</v>
+        <v>686803</v>
       </c>
       <c r="R116" t="n">
-        <v>6563221</v>
+        <v>6563297</v>
       </c>
       <c r="S116" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T116" t="inlineStr">
         <is>
@@ -13355,12 +13334,12 @@
       </c>
       <c r="Y116" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA116" t="inlineStr">
         <is>
-          <t>2025-10-03</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AD116" t="b">
@@ -13369,6 +13348,7 @@
       <c r="AE116" t="b">
         <v>0</v>
       </c>
+      <c r="AF116" t="inlineStr"/>
       <c r="AG116" t="b">
         <v>0</v>
       </c>
@@ -13386,48 +13366,49 @@
       <c r="AY116" t="inlineStr"/>
       <c r="AZ116" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128886960</t>
+          <t>https://artportalen.se/Sighting/126418797</t>
         </is>
       </c>
     </row>
     <row r="117">
       <c r="A117" t="n">
-        <v>129230389</v>
+        <v>134100841</v>
       </c>
       <c r="B117" t="n">
-        <v>58114</v>
+        <v>56915</v>
       </c>
       <c r="D117" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E117" t="n">
-        <v>103021</v>
+        <v>100088</v>
       </c>
       <c r="F117" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Vanlig snok</t>
         </is>
       </c>
       <c r="G117" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Natrix natrix</t>
         </is>
       </c>
       <c r="H117" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I117" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I117" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J117" t="inlineStr"/>
       <c r="K117" t="inlineStr"/>
       <c r="L117" t="inlineStr"/>
-      <c r="M117" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
+      <c r="M117" t="inlineStr"/>
       <c r="N117" t="inlineStr"/>
       <c r="P117" t="inlineStr">
         <is>
@@ -13435,13 +13416,13 @@
         </is>
       </c>
       <c r="Q117" t="n">
-        <v>686793</v>
+        <v>686486</v>
       </c>
       <c r="R117" t="n">
-        <v>6563302</v>
+        <v>6563086</v>
       </c>
       <c r="S117" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T117" t="inlineStr">
         <is>
@@ -13465,12 +13446,12 @@
       </c>
       <c r="Y117" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AA117" t="inlineStr">
         <is>
-          <t>2025-10-20</t>
+          <t>2026-06-03</t>
         </is>
       </c>
       <c r="AD117" t="b">
@@ -13479,6 +13460,7 @@
       <c r="AE117" t="b">
         <v>0</v>
       </c>
+      <c r="AF117" t="inlineStr"/>
       <c r="AG117" t="b">
         <v>0</v>
       </c>
@@ -13496,62 +13478,59 @@
       <c r="AY117" t="inlineStr"/>
       <c r="AZ117" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129230389</t>
+          <t>https://artportalen.se/Sighting/134100841</t>
         </is>
       </c>
     </row>
     <row r="118">
       <c r="A118" t="n">
-        <v>129591579</v>
+        <v>121859623</v>
       </c>
       <c r="B118" t="n">
-        <v>58114</v>
+        <v>5179</v>
       </c>
       <c r="D118" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E118" t="n">
-        <v>103021</v>
+        <v>100526</v>
       </c>
       <c r="F118" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Bronshjon</t>
         </is>
       </c>
       <c r="G118" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Callidium coriaceum</t>
         </is>
       </c>
       <c r="H118" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>Paykull, 1800</t>
         </is>
       </c>
       <c r="I118" t="inlineStr"/>
-      <c r="K118" t="inlineStr"/>
-      <c r="L118" t="inlineStr"/>
       <c r="M118" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N118" t="inlineStr"/>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="P118" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Öster om Tyresta by, Tyresta, Srm</t>
         </is>
       </c>
       <c r="Q118" t="n">
-        <v>686618</v>
+        <v>686581</v>
       </c>
       <c r="R118" t="n">
-        <v>6563047</v>
+        <v>6562989</v>
       </c>
       <c r="S118" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T118" t="inlineStr">
         <is>
@@ -13575,12 +13554,22 @@
       </c>
       <c r="Y118" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="Z118" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AA118" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2024-05-09</t>
+        </is>
+      </c>
+      <c r="AB118" t="inlineStr">
+        <is>
+          <t>17:36</t>
         </is>
       </c>
       <c r="AD118" t="b">
@@ -13591,31 +13580,51 @@
       </c>
       <c r="AG118" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ118" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK118" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL118" t="inlineStr">
+        <is>
+          <t>Granlåga</t>
+        </is>
+      </c>
+      <c r="AO118" t="inlineStr">
+        <is>
+          <t>Picea abies # Granlåga</t>
+        </is>
       </c>
       <c r="AT118" t="inlineStr"/>
       <c r="AW118" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX118" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AY118" t="inlineStr"/>
       <c r="AZ118" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129591579</t>
+          <t>https://artportalen.se/Sighting/121859623</t>
         </is>
       </c>
     </row>
     <row r="119">
       <c r="A119" t="n">
-        <v>133115563</v>
+        <v>128510434</v>
       </c>
       <c r="B119" t="n">
-        <v>58136</v>
+        <v>58114</v>
       </c>
       <c r="D119" t="inlineStr">
         <is>
@@ -13645,7 +13654,7 @@
       <c r="L119" t="inlineStr"/>
       <c r="M119" t="inlineStr">
         <is>
-          <t>spel/sång</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N119" t="inlineStr"/>
@@ -13655,10 +13664,10 @@
         </is>
       </c>
       <c r="Q119" t="n">
-        <v>686651</v>
+        <v>686650</v>
       </c>
       <c r="R119" t="n">
-        <v>6563184</v>
+        <v>6563214</v>
       </c>
       <c r="S119" t="n">
         <v>10</v>
@@ -13685,12 +13694,12 @@
       </c>
       <c r="Y119" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AA119" t="inlineStr">
         <is>
-          <t>2026-05-04</t>
+          <t>2025-09-17</t>
         </is>
       </c>
       <c r="AD119" t="b">
@@ -13716,47 +13725,46 @@
       <c r="AY119" t="inlineStr"/>
       <c r="AZ119" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/133115563</t>
+          <t>https://artportalen.se/Sighting/128510434</t>
         </is>
       </c>
     </row>
     <row r="120">
       <c r="A120" t="n">
-        <v>136259916</v>
+        <v>128886960</v>
       </c>
       <c r="B120" t="n">
-        <v>8463</v>
+        <v>58114</v>
       </c>
       <c r="D120" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E120" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F120" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G120" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H120" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I120" t="inlineStr"/>
-      <c r="J120" t="inlineStr"/>
       <c r="K120" t="inlineStr"/>
       <c r="L120" t="inlineStr"/>
       <c r="M120" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N120" t="inlineStr"/>
@@ -13766,13 +13774,13 @@
         </is>
       </c>
       <c r="Q120" t="n">
-        <v>686457</v>
+        <v>686792</v>
       </c>
       <c r="R120" t="n">
-        <v>6563062</v>
+        <v>6563221</v>
       </c>
       <c r="S120" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T120" t="inlineStr">
         <is>
@@ -13796,12 +13804,12 @@
       </c>
       <c r="Y120" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AA120" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2025-10-03</t>
         </is>
       </c>
       <c r="AD120" t="b">
@@ -13810,7 +13818,6 @@
       <c r="AE120" t="b">
         <v>0</v>
       </c>
-      <c r="AF120" t="inlineStr"/>
       <c r="AG120" t="b">
         <v>0</v>
       </c>
@@ -13828,58 +13835,62 @@
       <c r="AY120" t="inlineStr"/>
       <c r="AZ120" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136259916</t>
+          <t>https://artportalen.se/Sighting/128886960</t>
         </is>
       </c>
     </row>
     <row r="121">
       <c r="A121" t="n">
-        <v>109890506</v>
+        <v>129230389</v>
       </c>
       <c r="B121" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D121" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E121" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F121" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G121" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H121" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I121" t="inlineStr"/>
-      <c r="J121" t="inlineStr"/>
       <c r="K121" t="inlineStr"/>
       <c r="L121" t="inlineStr"/>
+      <c r="M121" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N121" t="inlineStr"/>
       <c r="P121" t="inlineStr">
         <is>
-          <t>Ö Norrby Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q121" t="n">
-        <v>686831</v>
+        <v>686793</v>
       </c>
       <c r="R121" t="n">
-        <v>6563216</v>
+        <v>6563302</v>
       </c>
       <c r="S121" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T121" t="inlineStr">
         <is>
@@ -13903,12 +13914,12 @@
       </c>
       <c r="Y121" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AA121" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2025-10-20</t>
         </is>
       </c>
       <c r="AD121" t="b">
@@ -13917,7 +13928,6 @@
       <c r="AE121" t="b">
         <v>0</v>
       </c>
-      <c r="AF121" t="inlineStr"/>
       <c r="AG121" t="b">
         <v>0</v>
       </c>
@@ -13935,58 +13945,62 @@
       <c r="AY121" t="inlineStr"/>
       <c r="AZ121" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109890506</t>
+          <t>https://artportalen.se/Sighting/129230389</t>
         </is>
       </c>
     </row>
     <row r="122">
       <c r="A122" t="n">
-        <v>122781008</v>
+        <v>129591579</v>
       </c>
       <c r="B122" t="n">
-        <v>99118</v>
+        <v>58114</v>
       </c>
       <c r="D122" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E122" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F122" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G122" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H122" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I122" t="inlineStr"/>
-      <c r="J122" t="inlineStr"/>
       <c r="K122" t="inlineStr"/>
       <c r="L122" t="inlineStr"/>
+      <c r="M122" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N122" t="inlineStr"/>
       <c r="P122" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q122" t="n">
-        <v>686833</v>
+        <v>686618</v>
       </c>
       <c r="R122" t="n">
-        <v>6563215</v>
+        <v>6563047</v>
       </c>
       <c r="S122" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T122" t="inlineStr">
         <is>
@@ -14010,17 +14024,12 @@
       </c>
       <c r="Y122" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AA122" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC122" t="inlineStr">
-        <is>
-          <t>Knärot</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="AD122" t="b">
@@ -14029,70 +14038,65 @@
       <c r="AE122" t="b">
         <v>0</v>
       </c>
-      <c r="AF122" t="inlineStr"/>
       <c r="AG122" t="b">
         <v>0</v>
       </c>
       <c r="AT122" t="inlineStr"/>
       <c r="AW122" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX122" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY122" t="inlineStr"/>
       <c r="AZ122" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122781008</t>
+          <t>https://artportalen.se/Sighting/129591579</t>
         </is>
       </c>
     </row>
     <row r="123">
       <c r="A123" t="n">
-        <v>126418709</v>
+        <v>133115563</v>
       </c>
       <c r="B123" t="n">
-        <v>99118</v>
+        <v>58136</v>
       </c>
       <c r="D123" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E123" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F123" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G123" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H123" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I123" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J123" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I123" t="inlineStr"/>
       <c r="K123" t="inlineStr"/>
       <c r="L123" t="inlineStr"/>
+      <c r="M123" t="inlineStr">
+        <is>
+          <t>spel/sång</t>
+        </is>
+      </c>
       <c r="N123" t="inlineStr"/>
       <c r="P123" t="inlineStr">
         <is>
@@ -14100,10 +14104,10 @@
         </is>
       </c>
       <c r="Q123" t="n">
-        <v>686771</v>
+        <v>686651</v>
       </c>
       <c r="R123" t="n">
-        <v>6563297</v>
+        <v>6563184</v>
       </c>
       <c r="S123" t="n">
         <v>10</v>
@@ -14130,17 +14134,12 @@
       </c>
       <c r="Y123" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AA123" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC123" t="inlineStr">
-        <is>
-          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
+          <t>2026-05-04</t>
         </is>
       </c>
       <c r="AD123" t="b">
@@ -14149,7 +14148,6 @@
       <c r="AE123" t="b">
         <v>0</v>
       </c>
-      <c r="AF123" t="inlineStr"/>
       <c r="AG123" t="b">
         <v>0</v>
       </c>
@@ -14167,52 +14165,48 @@
       <c r="AY123" t="inlineStr"/>
       <c r="AZ123" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418709</t>
+          <t>https://artportalen.se/Sighting/133115563</t>
         </is>
       </c>
     </row>
     <row r="124">
       <c r="A124" t="n">
-        <v>126418756</v>
+        <v>136330004</v>
       </c>
       <c r="B124" t="n">
-        <v>99118</v>
+        <v>58149</v>
       </c>
       <c r="D124" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E124" t="n">
-        <v>220787</v>
+        <v>103021</v>
       </c>
       <c r="F124" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G124" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H124" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
-        </is>
-      </c>
-      <c r="I124" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J124" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I124" t="inlineStr"/>
       <c r="K124" t="inlineStr"/>
       <c r="L124" t="inlineStr"/>
+      <c r="M124" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N124" t="inlineStr"/>
       <c r="P124" t="inlineStr">
         <is>
@@ -14220,10 +14214,10 @@
         </is>
       </c>
       <c r="Q124" t="n">
-        <v>686781</v>
+        <v>686477</v>
       </c>
       <c r="R124" t="n">
-        <v>6563292</v>
+        <v>6563053</v>
       </c>
       <c r="S124" t="n">
         <v>10</v>
@@ -14250,17 +14244,12 @@
       </c>
       <c r="Y124" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA124" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC124" t="inlineStr">
-        <is>
-          <t>En av dem i knopp.</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD124" t="b">
@@ -14269,7 +14258,6 @@
       <c r="AE124" t="b">
         <v>0</v>
       </c>
-      <c r="AF124" t="inlineStr"/>
       <c r="AG124" t="b">
         <v>0</v>
       </c>
@@ -14287,44 +14275,49 @@
       <c r="AY124" t="inlineStr"/>
       <c r="AZ124" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418756</t>
+          <t>https://artportalen.se/Sighting/136330004</t>
         </is>
       </c>
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>129564285</v>
+        <v>136259916</v>
       </c>
       <c r="B125" t="n">
-        <v>99118</v>
+        <v>8463</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E125" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
       <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
+      <c r="M125" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N125" t="inlineStr"/>
       <c r="P125" t="inlineStr">
         <is>
@@ -14332,10 +14325,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>686625</v>
+        <v>686457</v>
       </c>
       <c r="R125" t="n">
-        <v>6563000</v>
+        <v>6563062</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14362,12 +14355,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14394,16 +14387,16 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129564285</t>
+          <t>https://artportalen.se/Sighting/136259916</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>126234373</v>
+        <v>136330063</v>
       </c>
       <c r="B126" t="n">
-        <v>106244</v>
+        <v>8463</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14411,46 +14404,43 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>221144</v>
+        <v>106545</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>Sw.</t>
-        </is>
-      </c>
-      <c r="I126" t="inlineStr">
-        <is>
-          <t>12</t>
-        </is>
-      </c>
-      <c r="J126" t="inlineStr">
-        <is>
-          <t>plantor/tuvor</t>
-        </is>
-      </c>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I126" t="inlineStr"/>
+      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
+      <c r="M126" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N126" t="inlineStr"/>
       <c r="P126" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>686756</v>
+        <v>686661</v>
       </c>
       <c r="R126" t="n">
-        <v>6563092</v>
+        <v>6563103</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14477,12 +14467,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14498,49 +14488,49 @@
       <c r="AT126" t="inlineStr"/>
       <c r="AW126" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX126" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234373</t>
+          <t>https://artportalen.se/Sighting/136330063</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>122929342</v>
+        <v>109890506</v>
       </c>
       <c r="B127" t="n">
-        <v>97986</v>
+        <v>99118</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
@@ -14550,17 +14540,17 @@
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Ö Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>686569</v>
+        <v>686831</v>
       </c>
       <c r="R127" t="n">
-        <v>6562949</v>
+        <v>6563216</v>
       </c>
       <c r="S127" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T127" t="inlineStr">
         <is>
@@ -14584,22 +14574,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z127" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB127" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14608,76 +14588,73 @@
       <c r="AE127" t="b">
         <v>0</v>
       </c>
+      <c r="AF127" t="inlineStr"/>
       <c r="AG127" t="b">
         <v>0</v>
       </c>
       <c r="AT127" t="inlineStr"/>
       <c r="AW127" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX127" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929342</t>
+          <t>https://artportalen.se/Sighting/109890506</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>134487656</v>
+        <v>122781008</v>
       </c>
       <c r="B128" t="n">
-        <v>99217</v>
+        <v>99118</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>221952</v>
+        <v>220787</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
-      <c r="K128" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+      <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>686835</v>
+        <v>686833</v>
       </c>
       <c r="R128" t="n">
-        <v>6563212</v>
+        <v>6563215</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14704,17 +14681,17 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC128" t="inlineStr">
         <is>
-          <t>2 i blom samt några plantor med endast blad.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14730,65 +14707,74 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134487656</t>
+          <t>https://artportalen.se/Sighting/122781008</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>118843519</v>
+        <v>126418709</v>
       </c>
       <c r="B129" t="n">
-        <v>91431</v>
+        <v>99118</v>
       </c>
       <c r="D129" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E129" t="n">
-        <v>6039941</v>
+        <v>220787</v>
       </c>
       <c r="F129" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G129" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H129" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
-        </is>
-      </c>
-      <c r="I129" t="inlineStr"/>
-      <c r="J129" t="inlineStr"/>
+          <t>(L.) R. Br.</t>
+        </is>
+      </c>
+      <c r="I129" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J129" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K129" t="inlineStr"/>
+      <c r="L129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>Norrby Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>686668</v>
+        <v>686771</v>
       </c>
       <c r="R129" t="n">
-        <v>6563218</v>
+        <v>6563297</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14815,17 +14801,17 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AC129" t="inlineStr">
         <is>
-          <t>Kollekt BR55. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/112337794</t>
+          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14841,78 +14827,74 @@
       <c r="AT129" t="inlineStr"/>
       <c r="AW129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX129" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY129" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - extern</t>
-        </is>
-      </c>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118843519</t>
+          <t>https://artportalen.se/Sighting/126418709</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>122203249</v>
+        <v>126418756</v>
       </c>
       <c r="B130" t="n">
-        <v>96554</v>
+        <v>99118</v>
       </c>
       <c r="D130" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E130" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F130" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G130" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H130" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I130" t="inlineStr">
         <is>
-          <t>22</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr"/>
-      <c r="K130" t="inlineStr">
-        <is>
-          <t>med kapsel</t>
-        </is>
-      </c>
+          <t>16</t>
+        </is>
+      </c>
+      <c r="J130" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
+      <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>Ö Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>687968</v>
+        <v>686781</v>
       </c>
       <c r="R130" t="n">
-        <v>6562733</v>
+        <v>6563292</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14939,17 +14921,17 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>På murken granlåga i äldre skog.</t>
+          <t>En av dem i knopp.</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14976,38 +14958,38 @@
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122203249</t>
+          <t>https://artportalen.se/Sighting/126418756</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>122780924</v>
+        <v>129564285</v>
       </c>
       <c r="B131" t="n">
-        <v>96554</v>
+        <v>99118</v>
       </c>
       <c r="D131" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E131" t="n">
-        <v>210</v>
+        <v>220787</v>
       </c>
       <c r="F131" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G131" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H131" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I131" t="inlineStr"/>
@@ -15017,14 +14999,14 @@
       <c r="N131" t="inlineStr"/>
       <c r="P131" t="inlineStr">
         <is>
-          <t>Grön sköldmossa, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>687970</v>
+        <v>686625</v>
       </c>
       <c r="R131" t="n">
-        <v>6562732</v>
+        <v>6563000</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15051,17 +15033,12 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC131" t="inlineStr">
-        <is>
-          <t>Grön sköldmossa på rutten stam</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15077,65 +15054,74 @@
       <c r="AT131" t="inlineStr"/>
       <c r="AW131" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX131" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122780924</t>
+          <t>https://artportalen.se/Sighting/129564285</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>129624531</v>
+        <v>126234373</v>
       </c>
       <c r="B132" t="n">
-        <v>90946</v>
+        <v>106244</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>889</v>
+        <v>221144</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
-        </is>
-      </c>
-      <c r="I132" t="inlineStr"/>
-      <c r="J132" t="inlineStr"/>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I132" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J132" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
       <c r="K132" t="inlineStr"/>
+      <c r="L132" t="inlineStr"/>
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>687931</v>
+        <v>686756</v>
       </c>
       <c r="R132" t="n">
-        <v>6562811</v>
+        <v>6563092</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15162,12 +15148,12 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15183,68 +15169,69 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129624531</t>
+          <t>https://artportalen.se/Sighting/126234373</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>129624696</v>
+        <v>122929342</v>
       </c>
       <c r="B133" t="n">
-        <v>90946</v>
+        <v>97986</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>889</v>
+        <v>221946</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
       <c r="J133" t="inlineStr"/>
       <c r="K133" t="inlineStr"/>
+      <c r="L133" t="inlineStr"/>
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>687973</v>
+        <v>686569</v>
       </c>
       <c r="R133" t="n">
-        <v>6562815</v>
+        <v>6562949</v>
       </c>
       <c r="S133" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15268,17 +15255,22 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z133" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
-        </is>
-      </c>
-      <c r="AC133" t="inlineStr">
-        <is>
-          <t>På död tall.</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB133" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15287,72 +15279,76 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
-      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129624696</t>
+          <t>https://artportalen.se/Sighting/122929342</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>122203275</v>
+        <v>134487656</v>
       </c>
       <c r="B134" t="n">
-        <v>91909</v>
+        <v>99217</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E134" t="n">
-        <v>1202</v>
+        <v>221952</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(L.) Rich.</t>
         </is>
       </c>
       <c r="I134" t="inlineStr"/>
       <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr"/>
+      <c r="K134" t="inlineStr">
+        <is>
+          <t>blomning</t>
+        </is>
+      </c>
+      <c r="L134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>Ö Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>687981</v>
+        <v>686835</v>
       </c>
       <c r="R134" t="n">
-        <v>6562724</v>
+        <v>6563212</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15379,12 +15375,17 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2026-06-18</t>
+        </is>
+      </c>
+      <c r="AC134" t="inlineStr">
+        <is>
+          <t>2 i blom samt några plantor med endast blad.</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15411,58 +15412,54 @@
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122203275</t>
+          <t>https://artportalen.se/Sighting/134487656</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>135358856</v>
+        <v>118843519</v>
       </c>
       <c r="B135" t="n">
-        <v>91544</v>
+        <v>91431</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>2051</v>
+        <v>6039941</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Gelatinfingersvamp</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Ramaria primulina</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I135" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>R.H.Petersen</t>
+        </is>
+      </c>
+      <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>688004</v>
+        <v>686668</v>
       </c>
       <c r="R135" t="n">
-        <v>6562799</v>
+        <v>6563218</v>
       </c>
       <c r="S135" t="n">
         <v>10</v>
@@ -15489,12 +15486,17 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2023-09-26</t>
+        </is>
+      </c>
+      <c r="AC135" t="inlineStr">
+        <is>
+          <t>Kollekt BR55. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/112337794</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15510,27 +15512,31 @@
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
-        </is>
-      </c>
-      <c r="AY135" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358856</t>
+          <t>https://artportalen.se/Sighting/118843519</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>136241603</v>
+        <v>122203249</v>
       </c>
       <c r="B136" t="n">
-        <v>96887</v>
+        <v>96554</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15538,41 +15544,49 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>2180</v>
+        <v>210</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="J136" t="inlineStr"/>
-      <c r="K136" t="inlineStr"/>
+      <c r="K136" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
       <c r="L136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>Ö Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>688059</v>
+        <v>687968</v>
       </c>
       <c r="R136" t="n">
-        <v>6562773</v>
+        <v>6562733</v>
       </c>
       <c r="S136" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T136" t="inlineStr">
         <is>
@@ -15596,22 +15610,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z136" t="inlineStr">
-        <is>
-          <t>13:09</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB136" t="inlineStr">
-        <is>
-          <t>13:09</t>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AC136" t="inlineStr">
+        <is>
+          <t>På murken granlåga i äldre skog.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15627,27 +15636,27 @@
       <c r="AT136" t="inlineStr"/>
       <c r="AW136" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX136" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241603</t>
+          <t>https://artportalen.se/Sighting/122203249</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>136231090</v>
+        <v>122780924</v>
       </c>
       <c r="B137" t="n">
-        <v>96605</v>
+        <v>96554</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
@@ -15655,34 +15664,38 @@
         </is>
       </c>
       <c r="E137" t="n">
-        <v>2671</v>
+        <v>210</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
+      <c r="J137" t="inlineStr"/>
+      <c r="K137" t="inlineStr"/>
+      <c r="L137" t="inlineStr"/>
+      <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Norrby torp, Norrby torp, Srm</t>
+          <t>Grön sköldmossa, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>688046</v>
+        <v>687970</v>
       </c>
       <c r="R137" t="n">
-        <v>6562700</v>
+        <v>6562732</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15709,12 +15722,17 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC137" t="inlineStr">
+        <is>
+          <t>Grön sköldmossa på rutten stam</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15723,67 +15741,60 @@
       <c r="AE137" t="b">
         <v>0</v>
       </c>
+      <c r="AF137" t="inlineStr"/>
       <c r="AG137" t="b">
         <v>0</v>
       </c>
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY137" t="inlineStr"/>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136231090</t>
+          <t>https://artportalen.se/Sighting/122780924</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>128314411</v>
+        <v>129624531</v>
       </c>
       <c r="B138" t="n">
-        <v>92348</v>
+        <v>90946</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>5420</v>
+        <v>889</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J138" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr"/>
+      <c r="J138" t="inlineStr"/>
       <c r="K138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
@@ -15792,10 +15803,10 @@
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>688088</v>
+        <v>687931</v>
       </c>
       <c r="R138" t="n">
-        <v>6562722</v>
+        <v>6562811</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15822,12 +15833,12 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15854,38 +15865,38 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128314411</t>
+          <t>https://artportalen.se/Sighting/129624531</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>136268106</v>
+        <v>129624696</v>
       </c>
       <c r="B139" t="n">
-        <v>92036</v>
+        <v>90946</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>5447</v>
+        <v>889</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
@@ -15898,10 +15909,10 @@
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>687910</v>
+        <v>687973</v>
       </c>
       <c r="R139" t="n">
-        <v>6562787</v>
+        <v>6562815</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15928,17 +15939,17 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>På rätt klen, senvuxen?, lutande granlåga i ett kärr.</t>
+          <t>På död tall.</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15965,16 +15976,16 @@
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136268106</t>
+          <t>https://artportalen.se/Sighting/129624696</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>128314833</v>
+        <v>122203275</v>
       </c>
       <c r="B140" t="n">
-        <v>93235</v>
+        <v>91909</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15982,21 +15993,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>5966</v>
+        <v>1202</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16005,14 +16016,14 @@
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>688073</v>
+        <v>687981</v>
       </c>
       <c r="R140" t="n">
-        <v>6562768</v>
+        <v>6562724</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16039,12 +16050,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16071,41 +16082,45 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128314833</t>
+          <t>https://artportalen.se/Sighting/122203275</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>128317789</v>
+        <v>135358856</v>
       </c>
       <c r="B141" t="n">
-        <v>93235</v>
+        <v>91545</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>5966</v>
+        <v>2051</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
@@ -16115,10 +16130,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>688094</v>
+        <v>688004</v>
       </c>
       <c r="R141" t="n">
-        <v>6562777</v>
+        <v>6562799</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16145,12 +16160,12 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16177,57 +16192,58 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317789</t>
+          <t>https://artportalen.se/Sighting/135358856</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>128526064</v>
+        <v>136241603</v>
       </c>
       <c r="B142" t="n">
-        <v>93235</v>
+        <v>96888</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>5966</v>
+        <v>2180</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Ångstr.</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
+      <c r="L142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>687952</v>
+        <v>688059</v>
       </c>
       <c r="R142" t="n">
-        <v>6562790</v>
+        <v>6562773</v>
       </c>
       <c r="S142" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16251,12 +16267,22 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z142" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB142" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16272,65 +16298,62 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128526064</t>
+          <t>https://artportalen.se/Sighting/136241603</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>128646583</v>
+        <v>136231090</v>
       </c>
       <c r="B143" t="n">
-        <v>93235</v>
+        <v>96606</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>5966</v>
+        <v>2671</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I143" t="inlineStr"/>
-      <c r="J143" t="inlineStr"/>
-      <c r="K143" t="inlineStr"/>
-      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby torp, Norrby torp, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>688067</v>
+        <v>688046</v>
       </c>
       <c r="R143" t="n">
-        <v>6562731</v>
+        <v>6562700</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16357,12 +16380,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16371,79 +16394,82 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
-      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128646583</t>
+          <t>https://artportalen.se/Sighting/136231090</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>136241765</v>
+        <v>128314411</v>
       </c>
       <c r="B144" t="n">
-        <v>80068</v>
+        <v>92348</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E144" t="n">
-        <v>6453</v>
+        <v>5420</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr"/>
-      <c r="J144" t="inlineStr"/>
-      <c r="K144" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J144" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
+      <c r="K144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>688014</v>
+        <v>688088</v>
       </c>
       <c r="R144" t="n">
-        <v>6562734</v>
+        <v>6562722</v>
       </c>
       <c r="S144" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16467,22 +16493,12 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z144" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB144" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16498,64 +16514,65 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241765</t>
+          <t>https://artportalen.se/Sighting/128314411</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>17285491</v>
+        <v>136268106</v>
       </c>
       <c r="B145" t="n">
-        <v>80432</v>
+        <v>92037</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E145" t="n">
-        <v>6458</v>
+        <v>5447</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
       <c r="J145" t="inlineStr"/>
       <c r="K145" t="inlineStr"/>
+      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>Norrby torp, 480 m Ö, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>688111</v>
+        <v>687910</v>
       </c>
       <c r="R145" t="n">
-        <v>6562706</v>
+        <v>6562787</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16582,17 +16599,17 @@
       </c>
       <c r="Y145" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA145" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AC145" t="inlineStr">
         <is>
-          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
+          <t>På rätt klen, senvuxen?, lutande granlåga i ett kärr.</t>
         </is>
       </c>
       <c r="AD145" t="b">
@@ -16601,38 +16618,34 @@
       <c r="AE145" t="b">
         <v>0</v>
       </c>
+      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
-      </c>
-      <c r="AI145" t="inlineStr">
-        <is>
-          <t>Yngre gallrad blandskog</t>
-        </is>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17285491</t>
+          <t>https://artportalen.se/Sighting/136268106</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>79273786</v>
+        <v>128314833</v>
       </c>
       <c r="B146" t="n">
-        <v>80432</v>
+        <v>93235</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
@@ -16640,34 +16653,37 @@
         </is>
       </c>
       <c r="E146" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I146" t="inlineStr"/>
+      <c r="J146" t="inlineStr"/>
+      <c r="K146" t="inlineStr"/>
+      <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
         <is>
-          <t>Åvadal, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>688109</v>
+        <v>688073</v>
       </c>
       <c r="R146" t="n">
-        <v>6562704</v>
+        <v>6562768</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16694,12 +16710,12 @@
       </c>
       <c r="Y146" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA146" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD146" t="b">
@@ -16708,48 +16724,34 @@
       <c r="AE146" t="b">
         <v>0</v>
       </c>
+      <c r="AF146" t="inlineStr"/>
       <c r="AG146" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ146" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK146" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO146" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
       </c>
       <c r="AT146" t="inlineStr"/>
       <c r="AW146" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX146" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79273786</t>
+          <t>https://artportalen.se/Sighting/128314833</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>89840770</v>
+        <v>128317789</v>
       </c>
       <c r="B147" t="n">
-        <v>80432</v>
+        <v>93235</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
@@ -16757,21 +16759,21 @@
         </is>
       </c>
       <c r="E147" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16780,14 +16782,14 @@
       <c r="N147" t="inlineStr"/>
       <c r="P147" t="inlineStr">
         <is>
-          <t>Ö Norrby Torp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>688146</v>
+        <v>688094</v>
       </c>
       <c r="R147" t="n">
-        <v>6562738</v>
+        <v>6562777</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16814,17 +16816,12 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
-        </is>
-      </c>
-      <c r="AC147" t="inlineStr">
-        <is>
-          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16851,16 +16848,16 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89840770</t>
+          <t>https://artportalen.se/Sighting/128317789</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>112384453</v>
+        <v>128526064</v>
       </c>
       <c r="B148" t="n">
-        <v>80432</v>
+        <v>93235</v>
       </c>
       <c r="D148" t="inlineStr">
         <is>
@@ -16868,21 +16865,21 @@
         </is>
       </c>
       <c r="E148" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F148" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G148" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H148" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I148" t="inlineStr"/>
@@ -16891,14 +16888,14 @@
       <c r="N148" t="inlineStr"/>
       <c r="P148" t="inlineStr">
         <is>
-          <t>Norrby torp Ö om, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>688145</v>
+        <v>687952</v>
       </c>
       <c r="R148" t="n">
-        <v>6562737</v>
+        <v>6562790</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16925,17 +16922,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC148" t="inlineStr">
-        <is>
-          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16951,27 +16943,27 @@
       <c r="AT148" t="inlineStr"/>
       <c r="AW148" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX148" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112384453</t>
+          <t>https://artportalen.se/Sighting/128526064</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>122779297</v>
+        <v>128646583</v>
       </c>
       <c r="B149" t="n">
-        <v>80432</v>
+        <v>93235</v>
       </c>
       <c r="D149" t="inlineStr">
         <is>
@@ -16979,21 +16971,21 @@
         </is>
       </c>
       <c r="E149" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F149" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G149" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H149" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I149" t="inlineStr"/>
@@ -17002,14 +16994,14 @@
       <c r="N149" t="inlineStr"/>
       <c r="P149" t="inlineStr">
         <is>
-          <t>Lunglav, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>688116</v>
+        <v>688067</v>
       </c>
       <c r="R149" t="n">
-        <v>6562703</v>
+        <v>6562731</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17036,17 +17028,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC149" t="inlineStr">
-        <is>
-          <t>Lunglav på gammal ek</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17062,81 +17049,72 @@
       <c r="AT149" t="inlineStr"/>
       <c r="AW149" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX149" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122779297</t>
+          <t>https://artportalen.se/Sighting/128646583</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>125923864</v>
+        <v>136241765</v>
       </c>
       <c r="B150" t="n">
-        <v>57754</v>
+        <v>80069</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E150" t="n">
-        <v>102118</v>
+        <v>6453</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I150" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="K150" t="inlineStr"/>
-      <c r="L150" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M150" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
+        </is>
+      </c>
+      <c r="I150" t="inlineStr"/>
+      <c r="J150" t="inlineStr"/>
+      <c r="K150" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
         </is>
       </c>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>687916</v>
+        <v>688014</v>
       </c>
       <c r="R150" t="n">
-        <v>6562815</v>
+        <v>6562734</v>
       </c>
       <c r="S150" t="n">
-        <v>25</v>
+        <v>5</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17160,17 +17138,22 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z150" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
-        </is>
-      </c>
-      <c r="AC150" t="inlineStr">
-        <is>
-          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB150" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17179,33 +17162,34 @@
       <c r="AE150" t="b">
         <v>0</v>
       </c>
+      <c r="AF150" t="inlineStr"/>
       <c r="AG150" t="b">
         <v>0</v>
       </c>
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125923864</t>
+          <t>https://artportalen.se/Sighting/136241765</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>128317861</v>
+        <v>17285491</v>
       </c>
       <c r="B151" t="n">
-        <v>58114</v>
+        <v>80432</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17213,45 +17197,39 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
+      <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
-      <c r="L151" t="inlineStr"/>
-      <c r="M151" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby torp, 480 m Ö, Srm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>688058</v>
+        <v>688111</v>
       </c>
       <c r="R151" t="n">
-        <v>6562805</v>
+        <v>6562706</v>
       </c>
       <c r="S151" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T151" t="inlineStr">
         <is>
@@ -17275,12 +17253,17 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2015-04-02</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2015-04-02</t>
+        </is>
+      </c>
+      <c r="AC151" t="inlineStr">
+        <is>
+          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17291,31 +17274,36 @@
       </c>
       <c r="AG151" t="b">
         <v>0</v>
+      </c>
+      <c r="AI151" t="inlineStr">
+        <is>
+          <t>Yngre gallrad blandskog</t>
+        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317861</t>
+          <t>https://artportalen.se/Sighting/17285491</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>136138855</v>
+        <v>79273786</v>
       </c>
       <c r="B152" t="n">
-        <v>58148</v>
+        <v>80432</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17323,42 +17311,34 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
-      <c r="K152" t="inlineStr"/>
-      <c r="L152" t="inlineStr"/>
-      <c r="M152" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
-      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Åvadal, Srm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>687836</v>
+        <v>688109</v>
       </c>
       <c r="R152" t="n">
-        <v>6562786</v>
+        <v>6562704</v>
       </c>
       <c r="S152" t="n">
         <v>10</v>
@@ -17385,12 +17365,12 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17401,31 +17381,46 @@
       </c>
       <c r="AG152" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ152" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK152" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO152" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136138855</t>
+          <t>https://artportalen.se/Sighting/79273786</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>136138971</v>
+        <v>89840770</v>
       </c>
       <c r="B153" t="n">
-        <v>58148</v>
+        <v>80432</v>
       </c>
       <c r="D153" t="inlineStr">
         <is>
@@ -17433,45 +17428,40 @@
         </is>
       </c>
       <c r="E153" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F153" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G153" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H153" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I153" t="inlineStr"/>
+      <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
-      <c r="L153" t="inlineStr"/>
-      <c r="M153" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>687977</v>
+        <v>688146</v>
       </c>
       <c r="R153" t="n">
-        <v>6562735</v>
+        <v>6562738</v>
       </c>
       <c r="S153" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T153" t="inlineStr">
         <is>
@@ -17495,12 +17485,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2020-12-30</t>
+        </is>
+      </c>
+      <c r="AC153" t="inlineStr">
+        <is>
+          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17509,6 +17504,7 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
+      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
       </c>
@@ -17526,68 +17522,54 @@
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136138971</t>
+          <t>https://artportalen.se/Sighting/89840770</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>122692266</v>
+        <v>112384453</v>
       </c>
       <c r="B154" t="n">
-        <v>58826</v>
+        <v>80432</v>
       </c>
       <c r="D154" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E154" t="n">
-        <v>208242</v>
+        <v>6458</v>
       </c>
       <c r="F154" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G154" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H154" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I154" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I154" t="inlineStr"/>
       <c r="J154" t="inlineStr"/>
       <c r="K154" t="inlineStr"/>
-      <c r="L154" t="inlineStr"/>
-      <c r="M154" t="inlineStr">
-        <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N154" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander, Srm</t>
+          <t>Norrby torp Ö om, Srm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>687868</v>
+        <v>688145</v>
       </c>
       <c r="R154" t="n">
-        <v>6562755</v>
+        <v>6562737</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17614,17 +17596,17 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC154" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17640,67 +17622,65 @@
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122692266</t>
+          <t>https://artportalen.se/Sighting/112384453</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>136241491</v>
+        <v>122779297</v>
       </c>
       <c r="B155" t="n">
-        <v>58824</v>
+        <v>80432</v>
       </c>
       <c r="D155" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E155" t="n">
-        <v>208245</v>
+        <v>6458</v>
       </c>
       <c r="F155" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G155" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H155" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I155" t="inlineStr"/>
       <c r="J155" t="inlineStr"/>
       <c r="K155" t="inlineStr"/>
-      <c r="L155" t="inlineStr"/>
-      <c r="M155" t="inlineStr"/>
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Lunglav, Srm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>687873</v>
+        <v>688116</v>
       </c>
       <c r="R155" t="n">
-        <v>6562755</v>
+        <v>6562703</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17727,17 +17707,17 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Troligen årsunge.</t>
+          <t>Lunglav på gammal ek</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17753,27 +17733,27 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241491</t>
+          <t>https://artportalen.se/Sighting/122779297</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>101544040</v>
+        <v>125923864</v>
       </c>
       <c r="B156" t="n">
-        <v>99035</v>
+        <v>57754</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
@@ -17781,38 +17761,50 @@
         </is>
       </c>
       <c r="E156" t="n">
-        <v>219790</v>
+        <v>102118</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr"/>
-      <c r="J156" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr"/>
+      <c r="L156" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
+      <c r="M156" t="inlineStr">
+        <is>
+          <t>bo, ägg/ungar</t>
+        </is>
+      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>NO Norrby Torp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>687896</v>
+        <v>687916</v>
       </c>
       <c r="R156" t="n">
-        <v>6562764</v>
+        <v>6562815</v>
       </c>
       <c r="S156" t="n">
         <v>25</v>
@@ -17839,12 +17831,17 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC156" t="inlineStr">
+        <is>
+          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17853,7 +17850,6 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
-      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
@@ -17871,58 +17867,62 @@
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101544040</t>
+          <t>https://artportalen.se/Sighting/125923864</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>122930166</v>
+        <v>128317861</v>
       </c>
       <c r="B157" t="n">
-        <v>96554</v>
+        <v>58114</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E157" t="n">
-        <v>210</v>
+        <v>103021</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
-      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
       <c r="L157" t="inlineStr"/>
+      <c r="M157" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>686762</v>
+        <v>688058</v>
       </c>
       <c r="R157" t="n">
-        <v>6562715</v>
+        <v>6562805</v>
       </c>
       <c r="S157" t="n">
-        <v>21</v>
+        <v>25</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17946,22 +17946,12 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z157" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB157" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17976,65 +17966,70 @@
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122930166</t>
+          <t>https://artportalen.se/Sighting/128317861</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>119061006</v>
+        <v>136138855</v>
       </c>
       <c r="B158" t="n">
-        <v>91533</v>
+        <v>58149</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>2051</v>
+        <v>103021</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I158" t="inlineStr"/>
-      <c r="J158" t="inlineStr"/>
       <c r="K158" t="inlineStr"/>
+      <c r="L158" t="inlineStr"/>
+      <c r="M158" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N158" t="inlineStr"/>
       <c r="P158" t="inlineStr">
         <is>
-          <t>S Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>686477</v>
+        <v>687836</v>
       </c>
       <c r="R158" t="n">
-        <v>6562857</v>
+        <v>6562786</v>
       </c>
       <c r="S158" t="n">
         <v>10</v>
@@ -18061,17 +18056,12 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC158" t="inlineStr">
-        <is>
-          <t>Brukad skog nära kant mot gammal.</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18080,7 +18070,6 @@
       <c r="AE158" t="b">
         <v>0</v>
       </c>
-      <c r="AF158" t="inlineStr"/>
       <c r="AG158" t="b">
         <v>0</v>
       </c>
@@ -18098,63 +18087,62 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119061006</t>
+          <t>https://artportalen.se/Sighting/136138855</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>122929535</v>
+        <v>136138971</v>
       </c>
       <c r="B159" t="n">
-        <v>8455</v>
+        <v>58149</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E159" t="n">
-        <v>106545</v>
+        <v>103021</v>
       </c>
       <c r="F159" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G159" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H159" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I159" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J159" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I159" t="inlineStr"/>
       <c r="K159" t="inlineStr"/>
       <c r="L159" t="inlineStr"/>
-      <c r="M159" t="inlineStr"/>
+      <c r="M159" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N159" t="inlineStr"/>
       <c r="P159" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>686612</v>
+        <v>687977</v>
       </c>
       <c r="R159" t="n">
-        <v>6562882</v>
+        <v>6562735</v>
       </c>
       <c r="S159" t="n">
-        <v>9</v>
+        <v>25</v>
       </c>
       <c r="T159" t="inlineStr">
         <is>
@@ -18178,22 +18166,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z159" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB159" t="inlineStr">
-        <is>
-          <t>11:01</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18208,27 +18186,27 @@
       <c r="AT159" t="inlineStr"/>
       <c r="AW159" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX159" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929535</t>
+          <t>https://artportalen.se/Sighting/136138971</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>122928987</v>
+        <v>122692266</v>
       </c>
       <c r="B160" t="n">
-        <v>97983</v>
+        <v>58826</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
@@ -18236,38 +18214,51 @@
         </is>
       </c>
       <c r="E160" t="n">
-        <v>221945</v>
+        <v>208242</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>L.</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
-      <c r="N160" t="inlineStr"/>
+      <c r="M160" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>Mindre vattensalamander, Srm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>686389</v>
+        <v>687868</v>
       </c>
       <c r="R160" t="n">
-        <v>6562967</v>
+        <v>6562755</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18294,22 +18285,17 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z160" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB160" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC160" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18318,68 +18304,74 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
+      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122928987</t>
+          <t>https://artportalen.se/Sighting/122692266</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>126061106</v>
+        <v>136241491</v>
       </c>
       <c r="B161" t="n">
-        <v>91333</v>
+        <v>58825</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>2008</v>
+        <v>208245</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
+      <c r="J161" t="inlineStr"/>
+      <c r="K161" t="inlineStr"/>
+      <c r="L161" t="inlineStr"/>
+      <c r="M161" t="inlineStr"/>
+      <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>686883</v>
+        <v>687873</v>
       </c>
       <c r="R161" t="n">
-        <v>6562742</v>
+        <v>6562755</v>
       </c>
       <c r="S161" t="n">
         <v>10</v>
@@ -18406,22 +18398,17 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z161" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB161" t="inlineStr">
-        <is>
-          <t>13:23</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AC161" t="inlineStr">
+        <is>
+          <t>Troligen årsunge.</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18430,33 +18417,34 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
+      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
       <c r="AT161" t="inlineStr"/>
       <c r="AW161" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX161" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061106</t>
+          <t>https://artportalen.se/Sighting/136241491</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>126061107</v>
+        <v>101544040</v>
       </c>
       <c r="B162" t="n">
-        <v>96458</v>
+        <v>99035</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18464,37 +18452,41 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>2818</v>
+        <v>219790</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I162" t="inlineStr"/>
+      <c r="J162" t="inlineStr"/>
+      <c r="K162" t="inlineStr"/>
+      <c r="L162" t="inlineStr"/>
+      <c r="N162" t="inlineStr"/>
       <c r="P162" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>NO Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>686880</v>
+        <v>687896</v>
       </c>
       <c r="R162" t="n">
-        <v>6562745</v>
+        <v>6562764</v>
       </c>
       <c r="S162" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18518,22 +18510,12 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z162" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB162" t="inlineStr">
-        <is>
-          <t>13:19</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18542,33 +18524,34 @@
       <c r="AE162" t="b">
         <v>0</v>
       </c>
+      <c r="AF162" t="inlineStr"/>
       <c r="AG162" t="b">
         <v>0</v>
       </c>
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061107</t>
+          <t>https://artportalen.se/Sighting/101544040</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>129215187</v>
+        <v>122930166</v>
       </c>
       <c r="B163" t="n">
-        <v>91872</v>
+        <v>96554</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18576,40 +18559,41 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>5447</v>
+        <v>210</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
+      <c r="L163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>686977</v>
+        <v>686762</v>
       </c>
       <c r="R163" t="n">
-        <v>6562706</v>
+        <v>6562715</v>
       </c>
       <c r="S163" t="n">
-        <v>10</v>
+        <v>21</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18633,12 +18617,22 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z163" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB163" t="inlineStr">
+        <is>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18647,69 +18641,71 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
-      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215187</t>
+          <t>https://artportalen.se/Sighting/122930166</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>126061104</v>
+        <v>119061006</v>
       </c>
       <c r="B164" t="n">
-        <v>4775</v>
+        <v>91533</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>100299</v>
+        <v>2051</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
+      <c r="J164" t="inlineStr"/>
+      <c r="K164" t="inlineStr"/>
+      <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>S Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>686868</v>
+        <v>686477</v>
       </c>
       <c r="R164" t="n">
-        <v>6562739</v>
+        <v>6562857</v>
       </c>
       <c r="S164" t="n">
         <v>10</v>
@@ -18736,22 +18732,17 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z164" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB164" t="inlineStr">
-        <is>
-          <t>13:41</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC164" t="inlineStr">
+        <is>
+          <t>Brukad skog nära kant mot gammal.</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18760,53 +18751,34 @@
       <c r="AE164" t="b">
         <v>0</v>
       </c>
+      <c r="AF164" t="inlineStr"/>
       <c r="AG164" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ164" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK164" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL164" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO164" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT164" t="inlineStr"/>
       <c r="AW164" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX164" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061104</t>
+          <t>https://artportalen.se/Sighting/119061006</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>126061116</v>
+        <v>122929535</v>
       </c>
       <c r="B165" t="n">
-        <v>44177</v>
+        <v>8455</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18814,37 +18786,46 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>101735</v>
+        <v>106545</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J165" t="inlineStr"/>
+      <c r="K165" t="inlineStr"/>
+      <c r="L165" t="inlineStr"/>
+      <c r="M165" t="inlineStr"/>
+      <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>686928</v>
+        <v>686612</v>
       </c>
       <c r="R165" t="n">
-        <v>6562716</v>
+        <v>6562882</v>
       </c>
       <c r="S165" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18868,22 +18849,22 @@
       </c>
       <c r="Y165" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>11:58</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18894,51 +18875,31 @@
       </c>
       <c r="AG165" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ165" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK165" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AL165" t="inlineStr">
-        <is>
-          <t>Fnöskticka på björk.</t>
-        </is>
-      </c>
-      <c r="AO165" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius # Fnöskticka på björk.</t>
-        </is>
       </c>
       <c r="AT165" t="inlineStr"/>
       <c r="AW165" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX165" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061116</t>
+          <t>https://artportalen.se/Sighting/122929535</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>125974903</v>
+        <v>122928987</v>
       </c>
       <c r="B166" t="n">
-        <v>8444</v>
+        <v>97983</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
@@ -18946,50 +18907,41 @@
         </is>
       </c>
       <c r="E166" t="n">
-        <v>106554</v>
+        <v>221945</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I166" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
+          <t>L.</t>
+        </is>
+      </c>
+      <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
       <c r="L166" t="inlineStr"/>
-      <c r="M166" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>686838</v>
+        <v>686389</v>
       </c>
       <c r="R166" t="n">
-        <v>6562733</v>
+        <v>6562967</v>
       </c>
       <c r="S166" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T166" t="inlineStr">
         <is>
@@ -19013,17 +18965,22 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z166" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AC166" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB166" t="inlineStr">
+        <is>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -19032,76 +18989,55 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
-      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ166" t="inlineStr">
-        <is>
-          <t>vårtbjörk</t>
-        </is>
-      </c>
-      <c r="AK166" t="inlineStr">
-        <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM166" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
-        </is>
-      </c>
-      <c r="AO166" t="inlineStr">
-        <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
-        </is>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974903</t>
+          <t>https://artportalen.se/Sighting/122928987</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126061105</v>
+        <v>126061106</v>
       </c>
       <c r="B167" t="n">
-        <v>8444</v>
+        <v>91333</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>106554</v>
+        <v>2008</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I167" t="inlineStr"/>
@@ -19111,10 +19047,10 @@
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>686860</v>
+        <v>686883</v>
       </c>
       <c r="R167" t="n">
-        <v>6562743</v>
+        <v>6562742</v>
       </c>
       <c r="S167" t="n">
         <v>10</v>
@@ -19146,7 +19082,7 @@
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
@@ -19156,7 +19092,7 @@
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19167,21 +19103,6 @@
       </c>
       <c r="AG167" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ167" t="inlineStr">
-        <is>
-          <t>björkar</t>
-        </is>
-      </c>
-      <c r="AK167" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
-      </c>
-      <c r="AO167" t="inlineStr">
-        <is>
-          <t>Betula</t>
-        </is>
       </c>
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
@@ -19196,6 +19117,756 @@
       </c>
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061106</t>
+        </is>
+      </c>
+    </row>
+    <row r="168">
+      <c r="A168" t="n">
+        <v>126061107</v>
+      </c>
+      <c r="B168" t="n">
+        <v>96458</v>
+      </c>
+      <c r="D168" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E168" t="n">
+        <v>2818</v>
+      </c>
+      <c r="F168" t="inlineStr">
+        <is>
+          <t>Stubbspretmossa</t>
+        </is>
+      </c>
+      <c r="G168" t="inlineStr">
+        <is>
+          <t>Herzogiella seligeri</t>
+        </is>
+      </c>
+      <c r="H168" t="inlineStr">
+        <is>
+          <t>(Brid.) Z.Iwats.</t>
+        </is>
+      </c>
+      <c r="I168" t="inlineStr"/>
+      <c r="P168" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q168" t="n">
+        <v>686880</v>
+      </c>
+      <c r="R168" t="n">
+        <v>6562745</v>
+      </c>
+      <c r="S168" t="n">
+        <v>10</v>
+      </c>
+      <c r="T168" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U168" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V168" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W168" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y168" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z168" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AA168" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB168" t="inlineStr">
+        <is>
+          <t>13:19</t>
+        </is>
+      </c>
+      <c r="AD168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG168" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT168" t="inlineStr"/>
+      <c r="AW168" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX168" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY168" t="inlineStr"/>
+      <c r="AZ168" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061107</t>
+        </is>
+      </c>
+    </row>
+    <row r="169">
+      <c r="A169" t="n">
+        <v>129215187</v>
+      </c>
+      <c r="B169" t="n">
+        <v>91872</v>
+      </c>
+      <c r="D169" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E169" t="n">
+        <v>5447</v>
+      </c>
+      <c r="F169" t="inlineStr">
+        <is>
+          <t>Vedticka</t>
+        </is>
+      </c>
+      <c r="G169" t="inlineStr">
+        <is>
+          <t>Fuscoporia viticola</t>
+        </is>
+      </c>
+      <c r="H169" t="inlineStr">
+        <is>
+          <t>(Schwein.) Murrill</t>
+        </is>
+      </c>
+      <c r="I169" t="inlineStr"/>
+      <c r="J169" t="inlineStr"/>
+      <c r="K169" t="inlineStr"/>
+      <c r="N169" t="inlineStr"/>
+      <c r="P169" t="inlineStr">
+        <is>
+          <t>N Norrbytorp, Srm</t>
+        </is>
+      </c>
+      <c r="Q169" t="n">
+        <v>686977</v>
+      </c>
+      <c r="R169" t="n">
+        <v>6562706</v>
+      </c>
+      <c r="S169" t="n">
+        <v>10</v>
+      </c>
+      <c r="T169" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U169" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V169" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W169" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y169" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AA169" t="inlineStr">
+        <is>
+          <t>2025-10-19</t>
+        </is>
+      </c>
+      <c r="AD169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF169" t="inlineStr"/>
+      <c r="AG169" t="b">
+        <v>0</v>
+      </c>
+      <c r="AT169" t="inlineStr"/>
+      <c r="AW169" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AX169" t="inlineStr">
+        <is>
+          <t>Bodil Ravn</t>
+        </is>
+      </c>
+      <c r="AY169" t="inlineStr"/>
+      <c r="AZ169" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/129215187</t>
+        </is>
+      </c>
+    </row>
+    <row r="170">
+      <c r="A170" t="n">
+        <v>126061104</v>
+      </c>
+      <c r="B170" t="n">
+        <v>4775</v>
+      </c>
+      <c r="D170" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E170" t="n">
+        <v>100299</v>
+      </c>
+      <c r="F170" t="inlineStr">
+        <is>
+          <t>Thomsons trägnagare</t>
+        </is>
+      </c>
+      <c r="G170" t="inlineStr">
+        <is>
+          <t>Cacotemnus thomsoni</t>
+        </is>
+      </c>
+      <c r="H170" t="inlineStr">
+        <is>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I170" t="inlineStr"/>
+      <c r="P170" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q170" t="n">
+        <v>686868</v>
+      </c>
+      <c r="R170" t="n">
+        <v>6562739</v>
+      </c>
+      <c r="S170" t="n">
+        <v>10</v>
+      </c>
+      <c r="T170" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U170" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V170" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W170" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y170" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z170" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AA170" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB170" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
+      <c r="AD170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG170" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ170" t="inlineStr">
+        <is>
+          <t>gran</t>
+        </is>
+      </c>
+      <c r="AK170" t="inlineStr">
+        <is>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL170" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AO170" t="inlineStr">
+        <is>
+          <t>Picea abies # Stående död gran.</t>
+        </is>
+      </c>
+      <c r="AT170" t="inlineStr"/>
+      <c r="AW170" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX170" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY170" t="inlineStr"/>
+      <c r="AZ170" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061104</t>
+        </is>
+      </c>
+    </row>
+    <row r="171">
+      <c r="A171" t="n">
+        <v>126061116</v>
+      </c>
+      <c r="B171" t="n">
+        <v>44177</v>
+      </c>
+      <c r="D171" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E171" t="n">
+        <v>101735</v>
+      </c>
+      <c r="F171" t="inlineStr">
+        <is>
+          <t>Jättesvampmal</t>
+        </is>
+      </c>
+      <c r="G171" t="inlineStr">
+        <is>
+          <t>Scardia boletella</t>
+        </is>
+      </c>
+      <c r="H171" t="inlineStr">
+        <is>
+          <t>(Fabricius, 1794)</t>
+        </is>
+      </c>
+      <c r="I171" t="inlineStr"/>
+      <c r="P171" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q171" t="n">
+        <v>686928</v>
+      </c>
+      <c r="R171" t="n">
+        <v>6562716</v>
+      </c>
+      <c r="S171" t="n">
+        <v>10</v>
+      </c>
+      <c r="T171" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U171" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V171" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W171" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y171" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z171" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AA171" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB171" t="inlineStr">
+        <is>
+          <t>11:58</t>
+        </is>
+      </c>
+      <c r="AD171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG171" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ171" t="inlineStr">
+        <is>
+          <t>fnöskticka</t>
+        </is>
+      </c>
+      <c r="AK171" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AL171" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
+        </is>
+      </c>
+      <c r="AO171" t="inlineStr">
+        <is>
+          <t>Fomes fomentarius # Fnöskticka på björk.</t>
+        </is>
+      </c>
+      <c r="AT171" t="inlineStr"/>
+      <c r="AW171" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX171" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY171" t="inlineStr"/>
+      <c r="AZ171" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061116</t>
+        </is>
+      </c>
+    </row>
+    <row r="172">
+      <c r="A172" t="n">
+        <v>125974903</v>
+      </c>
+      <c r="B172" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D172" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E172" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F172" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G172" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H172" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J172" t="inlineStr"/>
+      <c r="K172" t="inlineStr"/>
+      <c r="L172" t="inlineStr"/>
+      <c r="M172" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N172" t="inlineStr"/>
+      <c r="P172" t="inlineStr">
+        <is>
+          <t>söder om Tyresta, Srm</t>
+        </is>
+      </c>
+      <c r="Q172" t="n">
+        <v>686838</v>
+      </c>
+      <c r="R172" t="n">
+        <v>6562733</v>
+      </c>
+      <c r="S172" t="n">
+        <v>5</v>
+      </c>
+      <c r="T172" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U172" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V172" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W172" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y172" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA172" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC172" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
+        </is>
+      </c>
+      <c r="AD172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF172" t="inlineStr"/>
+      <c r="AG172" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ172" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK172" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM172" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO172" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Betula pendula</t>
+        </is>
+      </c>
+      <c r="AT172" t="inlineStr"/>
+      <c r="AW172" t="inlineStr">
+        <is>
+          <t>Nette Bygren</t>
+        </is>
+      </c>
+      <c r="AX172" t="inlineStr">
+        <is>
+          <t>Nette Bygren</t>
+        </is>
+      </c>
+      <c r="AY172" t="inlineStr"/>
+      <c r="AZ172" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125974903</t>
+        </is>
+      </c>
+    </row>
+    <row r="173">
+      <c r="A173" t="n">
+        <v>126061105</v>
+      </c>
+      <c r="B173" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D173" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E173" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F173" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G173" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H173" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I173" t="inlineStr"/>
+      <c r="P173" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q173" t="n">
+        <v>686860</v>
+      </c>
+      <c r="R173" t="n">
+        <v>6562743</v>
+      </c>
+      <c r="S173" t="n">
+        <v>10</v>
+      </c>
+      <c r="T173" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U173" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V173" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W173" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y173" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z173" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA173" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB173" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG173" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ173" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK173" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO173" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT173" t="inlineStr"/>
+      <c r="AW173" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX173" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY173" t="inlineStr"/>
+      <c r="AZ173" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126061105</t>
         </is>
@@ -19369,6 +20040,12 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ165" r:id="rId164"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ166" r:id="rId165"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ167" r:id="rId166"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ168" r:id="rId167"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ169" r:id="rId168"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ170" r:id="rId169"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>

--- a/artfynd/S 152-2026 artfynd.xlsx
+++ b/artfynd/S 152-2026 artfynd.xlsx
@@ -413,7 +413,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:AZ173"/>
+  <dimension ref="A1:AZ175"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -14281,10 +14281,10 @@
     </row>
     <row r="125">
       <c r="A125" t="n">
-        <v>136259916</v>
+        <v>136346607</v>
       </c>
       <c r="B125" t="n">
-        <v>8463</v>
+        <v>58144</v>
       </c>
       <c r="D125" t="inlineStr">
         <is>
@@ -14292,30 +14292,29 @@
         </is>
       </c>
       <c r="E125" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F125" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G125" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H125" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I125" t="inlineStr"/>
-      <c r="J125" t="inlineStr"/>
       <c r="K125" t="inlineStr"/>
       <c r="L125" t="inlineStr"/>
       <c r="M125" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N125" t="inlineStr"/>
@@ -14325,10 +14324,10 @@
         </is>
       </c>
       <c r="Q125" t="n">
-        <v>686457</v>
+        <v>686529</v>
       </c>
       <c r="R125" t="n">
-        <v>6563062</v>
+        <v>6563051</v>
       </c>
       <c r="S125" t="n">
         <v>10</v>
@@ -14355,12 +14354,12 @@
       </c>
       <c r="Y125" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA125" t="inlineStr">
         <is>
-          <t>2026-08-31</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD125" t="b">
@@ -14369,7 +14368,6 @@
       <c r="AE125" t="b">
         <v>0</v>
       </c>
-      <c r="AF125" t="inlineStr"/>
       <c r="AG125" t="b">
         <v>0</v>
       </c>
@@ -14387,16 +14385,16 @@
       <c r="AY125" t="inlineStr"/>
       <c r="AZ125" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136259916</t>
+          <t>https://artportalen.se/Sighting/136346607</t>
         </is>
       </c>
     </row>
     <row r="126">
       <c r="A126" t="n">
-        <v>136330063</v>
+        <v>136346721</v>
       </c>
       <c r="B126" t="n">
-        <v>8463</v>
+        <v>58144</v>
       </c>
       <c r="D126" t="inlineStr">
         <is>
@@ -14404,30 +14402,29 @@
         </is>
       </c>
       <c r="E126" t="n">
-        <v>106545</v>
+        <v>103023</v>
       </c>
       <c r="F126" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Tofsmes</t>
         </is>
       </c>
       <c r="G126" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Lophophanes cristatus</t>
         </is>
       </c>
       <c r="H126" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I126" t="inlineStr"/>
-      <c r="J126" t="inlineStr"/>
       <c r="K126" t="inlineStr"/>
       <c r="L126" t="inlineStr"/>
       <c r="M126" t="inlineStr">
         <is>
-          <t>äldre gnagspår</t>
+          <t>lockläte, övriga läten</t>
         </is>
       </c>
       <c r="N126" t="inlineStr"/>
@@ -14437,10 +14434,10 @@
         </is>
       </c>
       <c r="Q126" t="n">
-        <v>686661</v>
+        <v>686678</v>
       </c>
       <c r="R126" t="n">
-        <v>6563103</v>
+        <v>6563074</v>
       </c>
       <c r="S126" t="n">
         <v>10</v>
@@ -14467,12 +14464,12 @@
       </c>
       <c r="Y126" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AA126" t="inlineStr">
         <is>
-          <t>2026-09-03</t>
+          <t>2026-09-04</t>
         </is>
       </c>
       <c r="AD126" t="b">
@@ -14481,7 +14478,6 @@
       <c r="AE126" t="b">
         <v>0</v>
       </c>
-      <c r="AF126" t="inlineStr"/>
       <c r="AG126" t="b">
         <v>0</v>
       </c>
@@ -14499,55 +14495,60 @@
       <c r="AY126" t="inlineStr"/>
       <c r="AZ126" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136330063</t>
+          <t>https://artportalen.se/Sighting/136346721</t>
         </is>
       </c>
     </row>
     <row r="127">
       <c r="A127" t="n">
-        <v>109890506</v>
+        <v>136259916</v>
       </c>
       <c r="B127" t="n">
-        <v>99118</v>
+        <v>8463</v>
       </c>
       <c r="D127" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E127" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F127" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G127" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H127" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I127" t="inlineStr"/>
       <c r="J127" t="inlineStr"/>
       <c r="K127" t="inlineStr"/>
       <c r="L127" t="inlineStr"/>
+      <c r="M127" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N127" t="inlineStr"/>
       <c r="P127" t="inlineStr">
         <is>
-          <t>Ö Norrby Mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q127" t="n">
-        <v>686831</v>
+        <v>686457</v>
       </c>
       <c r="R127" t="n">
-        <v>6563216</v>
+        <v>6563062</v>
       </c>
       <c r="S127" t="n">
         <v>10</v>
@@ -14574,12 +14575,12 @@
       </c>
       <c r="Y127" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AA127" t="inlineStr">
         <is>
-          <t>2023-05-02</t>
+          <t>2026-08-31</t>
         </is>
       </c>
       <c r="AD127" t="b">
@@ -14606,55 +14607,60 @@
       <c r="AY127" t="inlineStr"/>
       <c r="AZ127" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/109890506</t>
+          <t>https://artportalen.se/Sighting/136259916</t>
         </is>
       </c>
     </row>
     <row r="128">
       <c r="A128" t="n">
-        <v>122781008</v>
+        <v>136330063</v>
       </c>
       <c r="B128" t="n">
-        <v>99118</v>
+        <v>8463</v>
       </c>
       <c r="D128" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E128" t="n">
-        <v>220787</v>
+        <v>106545</v>
       </c>
       <c r="F128" t="inlineStr">
         <is>
-          <t>Knärot</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G128" t="inlineStr">
         <is>
-          <t>Goodyera repens</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H128" t="inlineStr">
         <is>
-          <t>(L.) R. Br.</t>
+          <t>(Hartig, 1834)</t>
         </is>
       </c>
       <c r="I128" t="inlineStr"/>
       <c r="J128" t="inlineStr"/>
       <c r="K128" t="inlineStr"/>
       <c r="L128" t="inlineStr"/>
+      <c r="M128" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
       <c r="N128" t="inlineStr"/>
       <c r="P128" t="inlineStr">
         <is>
-          <t>Knärot, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q128" t="n">
-        <v>686833</v>
+        <v>686661</v>
       </c>
       <c r="R128" t="n">
-        <v>6563215</v>
+        <v>6563103</v>
       </c>
       <c r="S128" t="n">
         <v>10</v>
@@ -14681,17 +14687,12 @@
       </c>
       <c r="Y128" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AA128" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
-        </is>
-      </c>
-      <c r="AC128" t="inlineStr">
-        <is>
-          <t>Knärot</t>
+          <t>2026-09-03</t>
         </is>
       </c>
       <c r="AD128" t="b">
@@ -14707,24 +14708,24 @@
       <c r="AT128" t="inlineStr"/>
       <c r="AW128" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX128" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY128" t="inlineStr"/>
       <c r="AZ128" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122781008</t>
+          <t>https://artportalen.se/Sighting/136330063</t>
         </is>
       </c>
     </row>
     <row r="129">
       <c r="A129" t="n">
-        <v>126418709</v>
+        <v>109890506</v>
       </c>
       <c r="B129" t="n">
         <v>99118</v>
@@ -14752,29 +14753,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I129" t="inlineStr">
-        <is>
-          <t>15</t>
-        </is>
-      </c>
-      <c r="J129" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I129" t="inlineStr"/>
+      <c r="J129" t="inlineStr"/>
       <c r="K129" t="inlineStr"/>
       <c r="L129" t="inlineStr"/>
       <c r="N129" t="inlineStr"/>
       <c r="P129" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q129" t="n">
-        <v>686771</v>
+        <v>686831</v>
       </c>
       <c r="R129" t="n">
-        <v>6563297</v>
+        <v>6563216</v>
       </c>
       <c r="S129" t="n">
         <v>10</v>
@@ -14801,17 +14794,12 @@
       </c>
       <c r="Y129" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AA129" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
-        </is>
-      </c>
-      <c r="AC129" t="inlineStr">
-        <is>
-          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
+          <t>2023-05-02</t>
         </is>
       </c>
       <c r="AD129" t="b">
@@ -14838,13 +14826,13 @@
       <c r="AY129" t="inlineStr"/>
       <c r="AZ129" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418709</t>
+          <t>https://artportalen.se/Sighting/109890506</t>
         </is>
       </c>
     </row>
     <row r="130">
       <c r="A130" t="n">
-        <v>126418756</v>
+        <v>122781008</v>
       </c>
       <c r="B130" t="n">
         <v>99118</v>
@@ -14872,29 +14860,21 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I130" t="inlineStr">
-        <is>
-          <t>16</t>
-        </is>
-      </c>
-      <c r="J130" t="inlineStr">
-        <is>
-          <t>stjälkar/strån/skott</t>
-        </is>
-      </c>
+      <c r="I130" t="inlineStr"/>
+      <c r="J130" t="inlineStr"/>
       <c r="K130" t="inlineStr"/>
       <c r="L130" t="inlineStr"/>
       <c r="N130" t="inlineStr"/>
       <c r="P130" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Knärot, Srm</t>
         </is>
       </c>
       <c r="Q130" t="n">
-        <v>686781</v>
+        <v>686833</v>
       </c>
       <c r="R130" t="n">
-        <v>6563292</v>
+        <v>6563215</v>
       </c>
       <c r="S130" t="n">
         <v>10</v>
@@ -14921,17 +14901,17 @@
       </c>
       <c r="Y130" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA130" t="inlineStr">
         <is>
-          <t>2025-07-04</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC130" t="inlineStr">
         <is>
-          <t>En av dem i knopp.</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="AD130" t="b">
@@ -14947,24 +14927,24 @@
       <c r="AT130" t="inlineStr"/>
       <c r="AW130" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX130" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY130" t="inlineStr"/>
       <c r="AZ130" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126418756</t>
+          <t>https://artportalen.se/Sighting/122781008</t>
         </is>
       </c>
     </row>
     <row r="131">
       <c r="A131" t="n">
-        <v>129564285</v>
+        <v>126418709</v>
       </c>
       <c r="B131" t="n">
         <v>99118</v>
@@ -14992,8 +14972,16 @@
           <t>(L.) R. Br.</t>
         </is>
       </c>
-      <c r="I131" t="inlineStr"/>
-      <c r="J131" t="inlineStr"/>
+      <c r="I131" t="inlineStr">
+        <is>
+          <t>15</t>
+        </is>
+      </c>
+      <c r="J131" t="inlineStr">
+        <is>
+          <t>stjälkar/strån/skott</t>
+        </is>
+      </c>
       <c r="K131" t="inlineStr"/>
       <c r="L131" t="inlineStr"/>
       <c r="N131" t="inlineStr"/>
@@ -15003,10 +14991,10 @@
         </is>
       </c>
       <c r="Q131" t="n">
-        <v>686625</v>
+        <v>686771</v>
       </c>
       <c r="R131" t="n">
-        <v>6563000</v>
+        <v>6563297</v>
       </c>
       <c r="S131" t="n">
         <v>10</v>
@@ -15033,12 +15021,17 @@
       </c>
       <c r="Y131" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA131" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC131" t="inlineStr">
+        <is>
+          <t>Två av dem i knopp, ca 3 m väster om de andra.</t>
         </is>
       </c>
       <c r="AD131" t="b">
@@ -15065,48 +15058,48 @@
       <c r="AY131" t="inlineStr"/>
       <c r="AZ131" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129564285</t>
+          <t>https://artportalen.se/Sighting/126418709</t>
         </is>
       </c>
     </row>
     <row r="132">
       <c r="A132" t="n">
-        <v>126234373</v>
+        <v>126418756</v>
       </c>
       <c r="B132" t="n">
-        <v>106244</v>
+        <v>99118</v>
       </c>
       <c r="D132" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E132" t="n">
-        <v>221144</v>
+        <v>220787</v>
       </c>
       <c r="F132" t="inlineStr">
         <is>
-          <t>Grönpyrola</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G132" t="inlineStr">
         <is>
-          <t>Pyrola chlorantha</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H132" t="inlineStr">
         <is>
-          <t>Sw.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I132" t="inlineStr">
         <is>
-          <t>12</t>
+          <t>16</t>
         </is>
       </c>
       <c r="J132" t="inlineStr">
         <is>
-          <t>plantor/tuvor</t>
+          <t>stjälkar/strån/skott</t>
         </is>
       </c>
       <c r="K132" t="inlineStr"/>
@@ -15114,14 +15107,14 @@
       <c r="N132" t="inlineStr"/>
       <c r="P132" t="inlineStr">
         <is>
-          <t>Norrby mosse SO, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q132" t="n">
-        <v>686756</v>
+        <v>686781</v>
       </c>
       <c r="R132" t="n">
-        <v>6563092</v>
+        <v>6563292</v>
       </c>
       <c r="S132" t="n">
         <v>10</v>
@@ -15148,12 +15141,17 @@
       </c>
       <c r="Y132" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-04</t>
         </is>
       </c>
       <c r="AA132" t="inlineStr">
         <is>
-          <t>2025-06-26</t>
+          <t>2025-07-04</t>
+        </is>
+      </c>
+      <c r="AC132" t="inlineStr">
+        <is>
+          <t>En av dem i knopp.</t>
         </is>
       </c>
       <c r="AD132" t="b">
@@ -15169,49 +15167,49 @@
       <c r="AT132" t="inlineStr"/>
       <c r="AW132" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX132" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY132" t="inlineStr"/>
       <c r="AZ132" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126234373</t>
+          <t>https://artportalen.se/Sighting/126418756</t>
         </is>
       </c>
     </row>
     <row r="133">
       <c r="A133" t="n">
-        <v>122929342</v>
+        <v>129564285</v>
       </c>
       <c r="B133" t="n">
-        <v>97986</v>
+        <v>99118</v>
       </c>
       <c r="D133" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E133" t="n">
-        <v>221946</v>
+        <v>220787</v>
       </c>
       <c r="F133" t="inlineStr">
         <is>
-          <t>Mattlummer</t>
+          <t>Knärot</t>
         </is>
       </c>
       <c r="G133" t="inlineStr">
         <is>
-          <t>Lycopodium clavatum</t>
+          <t>Goodyera repens</t>
         </is>
       </c>
       <c r="H133" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>(L.) R. Br.</t>
         </is>
       </c>
       <c r="I133" t="inlineStr"/>
@@ -15221,17 +15219,17 @@
       <c r="N133" t="inlineStr"/>
       <c r="P133" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q133" t="n">
-        <v>686569</v>
+        <v>686625</v>
       </c>
       <c r="R133" t="n">
-        <v>6562949</v>
+        <v>6563000</v>
       </c>
       <c r="S133" t="n">
-        <v>12</v>
+        <v>10</v>
       </c>
       <c r="T133" t="inlineStr">
         <is>
@@ -15255,22 +15253,12 @@
       </c>
       <c r="Y133" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z133" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AA133" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB133" t="inlineStr">
-        <is>
-          <t>10:52</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="AD133" t="b">
@@ -15279,33 +15267,34 @@
       <c r="AE133" t="b">
         <v>0</v>
       </c>
+      <c r="AF133" t="inlineStr"/>
       <c r="AG133" t="b">
         <v>0</v>
       </c>
       <c r="AT133" t="inlineStr"/>
       <c r="AW133" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX133" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY133" t="inlineStr"/>
       <c r="AZ133" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929342</t>
+          <t>https://artportalen.se/Sighting/129564285</t>
         </is>
       </c>
     </row>
     <row r="134">
       <c r="A134" t="n">
-        <v>134487656</v>
+        <v>126234373</v>
       </c>
       <c r="B134" t="n">
-        <v>99217</v>
+        <v>106244</v>
       </c>
       <c r="D134" t="inlineStr">
         <is>
@@ -15313,42 +15302,46 @@
         </is>
       </c>
       <c r="E134" t="n">
-        <v>221952</v>
+        <v>221144</v>
       </c>
       <c r="F134" t="inlineStr">
         <is>
-          <t>Spindelblomster</t>
+          <t>Grönpyrola</t>
         </is>
       </c>
       <c r="G134" t="inlineStr">
         <is>
-          <t>Neottia cordata</t>
+          <t>Pyrola chlorantha</t>
         </is>
       </c>
       <c r="H134" t="inlineStr">
         <is>
-          <t>(L.) Rich.</t>
-        </is>
-      </c>
-      <c r="I134" t="inlineStr"/>
-      <c r="J134" t="inlineStr"/>
-      <c r="K134" t="inlineStr">
-        <is>
-          <t>blomning</t>
-        </is>
-      </c>
+          <t>Sw.</t>
+        </is>
+      </c>
+      <c r="I134" t="inlineStr">
+        <is>
+          <t>12</t>
+        </is>
+      </c>
+      <c r="J134" t="inlineStr">
+        <is>
+          <t>plantor/tuvor</t>
+        </is>
+      </c>
+      <c r="K134" t="inlineStr"/>
       <c r="L134" t="inlineStr"/>
       <c r="N134" t="inlineStr"/>
       <c r="P134" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby mosse SO, Srm</t>
         </is>
       </c>
       <c r="Q134" t="n">
-        <v>686835</v>
+        <v>686756</v>
       </c>
       <c r="R134" t="n">
-        <v>6563212</v>
+        <v>6563092</v>
       </c>
       <c r="S134" t="n">
         <v>10</v>
@@ -15375,17 +15368,12 @@
       </c>
       <c r="Y134" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AA134" t="inlineStr">
         <is>
-          <t>2026-06-18</t>
-        </is>
-      </c>
-      <c r="AC134" t="inlineStr">
-        <is>
-          <t>2 i blom samt några plantor med endast blad.</t>
+          <t>2025-06-26</t>
         </is>
       </c>
       <c r="AD134" t="b">
@@ -15401,68 +15389,69 @@
       <c r="AT134" t="inlineStr"/>
       <c r="AW134" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX134" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY134" t="inlineStr"/>
       <c r="AZ134" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/134487656</t>
+          <t>https://artportalen.se/Sighting/126234373</t>
         </is>
       </c>
     </row>
     <row r="135">
       <c r="A135" t="n">
-        <v>118843519</v>
+        <v>122929342</v>
       </c>
       <c r="B135" t="n">
-        <v>91431</v>
+        <v>97986</v>
       </c>
       <c r="D135" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E135" t="n">
-        <v>6039941</v>
+        <v>221946</v>
       </c>
       <c r="F135" t="inlineStr">
         <is>
-          <t>Gelatinfingersvamp</t>
+          <t>Mattlummer</t>
         </is>
       </c>
       <c r="G135" t="inlineStr">
         <is>
-          <t>Ramaria primulina</t>
+          <t>Lycopodium clavatum</t>
         </is>
       </c>
       <c r="H135" t="inlineStr">
         <is>
-          <t>R.H.Petersen</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I135" t="inlineStr"/>
       <c r="J135" t="inlineStr"/>
       <c r="K135" t="inlineStr"/>
+      <c r="L135" t="inlineStr"/>
       <c r="N135" t="inlineStr"/>
       <c r="P135" t="inlineStr">
         <is>
-          <t>Norrby Mosse, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q135" t="n">
-        <v>686668</v>
+        <v>686569</v>
       </c>
       <c r="R135" t="n">
-        <v>6563218</v>
+        <v>6562949</v>
       </c>
       <c r="S135" t="n">
-        <v>10</v>
+        <v>12</v>
       </c>
       <c r="T135" t="inlineStr">
         <is>
@@ -15486,17 +15475,22 @@
       </c>
       <c r="Y135" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="Z135" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AA135" t="inlineStr">
         <is>
-          <t>2023-09-26</t>
-        </is>
-      </c>
-      <c r="AC135" t="inlineStr">
-        <is>
-          <t>Kollekt BR55. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/112337794</t>
+          <t>2025-03-07</t>
+        </is>
+      </c>
+      <c r="AB135" t="inlineStr">
+        <is>
+          <t>10:52</t>
         </is>
       </c>
       <c r="AD135" t="b">
@@ -15505,38 +15499,33 @@
       <c r="AE135" t="b">
         <v>0</v>
       </c>
-      <c r="AF135" t="inlineStr"/>
       <c r="AG135" t="b">
         <v>0</v>
       </c>
       <c r="AT135" t="inlineStr"/>
       <c r="AW135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX135" t="inlineStr">
         <is>
-          <t>Martin Axegård</t>
-        </is>
-      </c>
-      <c r="AY135" t="inlineStr">
-        <is>
-          <t>Fynd med DNA-sekvens - extern</t>
-        </is>
-      </c>
+          <t>Emilia Blixt</t>
+        </is>
+      </c>
+      <c r="AY135" t="inlineStr"/>
       <c r="AZ135" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/118843519</t>
+          <t>https://artportalen.se/Sighting/122929342</t>
         </is>
       </c>
     </row>
     <row r="136">
       <c r="A136" t="n">
-        <v>122203249</v>
+        <v>134487656</v>
       </c>
       <c r="B136" t="n">
-        <v>96554</v>
+        <v>99217</v>
       </c>
       <c r="D136" t="inlineStr">
         <is>
@@ -15544,46 +15533,42 @@
         </is>
       </c>
       <c r="E136" t="n">
-        <v>210</v>
+        <v>221952</v>
       </c>
       <c r="F136" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Spindelblomster</t>
         </is>
       </c>
       <c r="G136" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Neottia cordata</t>
         </is>
       </c>
       <c r="H136" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
-        </is>
-      </c>
-      <c r="I136" t="inlineStr">
-        <is>
-          <t>22</t>
-        </is>
-      </c>
+          <t>(L.) Rich.</t>
+        </is>
+      </c>
+      <c r="I136" t="inlineStr"/>
       <c r="J136" t="inlineStr"/>
       <c r="K136" t="inlineStr">
         <is>
-          <t>med kapsel</t>
+          <t>blomning</t>
         </is>
       </c>
       <c r="L136" t="inlineStr"/>
       <c r="N136" t="inlineStr"/>
       <c r="P136" t="inlineStr">
         <is>
-          <t>Ö Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q136" t="n">
-        <v>687968</v>
+        <v>686835</v>
       </c>
       <c r="R136" t="n">
-        <v>6562733</v>
+        <v>6563212</v>
       </c>
       <c r="S136" t="n">
         <v>10</v>
@@ -15610,17 +15595,17 @@
       </c>
       <c r="Y136" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AA136" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2026-06-18</t>
         </is>
       </c>
       <c r="AC136" t="inlineStr">
         <is>
-          <t>På murken granlåga i äldre skog.</t>
+          <t>2 i blom samt några plantor med endast blad.</t>
         </is>
       </c>
       <c r="AD136" t="b">
@@ -15647,55 +15632,54 @@
       <c r="AY136" t="inlineStr"/>
       <c r="AZ136" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122203249</t>
+          <t>https://artportalen.se/Sighting/134487656</t>
         </is>
       </c>
     </row>
     <row r="137">
       <c r="A137" t="n">
-        <v>122780924</v>
+        <v>118843519</v>
       </c>
       <c r="B137" t="n">
-        <v>96554</v>
+        <v>91431</v>
       </c>
       <c r="D137" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E137" t="n">
-        <v>210</v>
+        <v>6039941</v>
       </c>
       <c r="F137" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Gelatinfingersvamp</t>
         </is>
       </c>
       <c r="G137" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Ramaria primulina</t>
         </is>
       </c>
       <c r="H137" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>R.H.Petersen</t>
         </is>
       </c>
       <c r="I137" t="inlineStr"/>
       <c r="J137" t="inlineStr"/>
       <c r="K137" t="inlineStr"/>
-      <c r="L137" t="inlineStr"/>
       <c r="N137" t="inlineStr"/>
       <c r="P137" t="inlineStr">
         <is>
-          <t>Grön sköldmossa, Srm</t>
+          <t>Norrby Mosse, Srm</t>
         </is>
       </c>
       <c r="Q137" t="n">
-        <v>687970</v>
+        <v>686668</v>
       </c>
       <c r="R137" t="n">
-        <v>6562732</v>
+        <v>6563218</v>
       </c>
       <c r="S137" t="n">
         <v>10</v>
@@ -15722,17 +15706,17 @@
       </c>
       <c r="Y137" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AA137" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2023-09-26</t>
         </is>
       </c>
       <c r="AC137" t="inlineStr">
         <is>
-          <t>Grön sköldmossa på rutten stam</t>
+          <t>Kollekt BR55. Dublett av tidigare fynd för att rapportera resultat av sekvensering. Ursprungligt fynd rapporterat av Bodil Ravn och finns här https://www.artportalen.se/Sighting/112337794</t>
         </is>
       </c>
       <c r="AD137" t="b">
@@ -15748,65 +15732,78 @@
       <c r="AT137" t="inlineStr"/>
       <c r="AW137" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Martin Axegård</t>
         </is>
       </c>
       <c r="AX137" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
-        </is>
-      </c>
-      <c r="AY137" t="inlineStr"/>
+          <t>Martin Axegård</t>
+        </is>
+      </c>
+      <c r="AY137" t="inlineStr">
+        <is>
+          <t>Fynd med DNA-sekvens - extern</t>
+        </is>
+      </c>
       <c r="AZ137" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122780924</t>
+          <t>https://artportalen.se/Sighting/118843519</t>
         </is>
       </c>
     </row>
     <row r="138">
       <c r="A138" t="n">
-        <v>129624531</v>
+        <v>122203249</v>
       </c>
       <c r="B138" t="n">
-        <v>90946</v>
+        <v>96554</v>
       </c>
       <c r="D138" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E138" t="n">
-        <v>889</v>
+        <v>210</v>
       </c>
       <c r="F138" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G138" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H138" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
-        </is>
-      </c>
-      <c r="I138" t="inlineStr"/>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I138" t="inlineStr">
+        <is>
+          <t>22</t>
+        </is>
+      </c>
       <c r="J138" t="inlineStr"/>
-      <c r="K138" t="inlineStr"/>
+      <c r="K138" t="inlineStr">
+        <is>
+          <t>med kapsel</t>
+        </is>
+      </c>
+      <c r="L138" t="inlineStr"/>
       <c r="N138" t="inlineStr"/>
       <c r="P138" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q138" t="n">
-        <v>687931</v>
+        <v>687968</v>
       </c>
       <c r="R138" t="n">
-        <v>6562811</v>
+        <v>6562733</v>
       </c>
       <c r="S138" t="n">
         <v>10</v>
@@ -15833,12 +15830,17 @@
       </c>
       <c r="Y138" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA138" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-01-18</t>
+        </is>
+      </c>
+      <c r="AC138" t="inlineStr">
+        <is>
+          <t>På murken granlåga i äldre skog.</t>
         </is>
       </c>
       <c r="AD138" t="b">
@@ -15865,54 +15867,55 @@
       <c r="AY138" t="inlineStr"/>
       <c r="AZ138" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129624531</t>
+          <t>https://artportalen.se/Sighting/122203249</t>
         </is>
       </c>
     </row>
     <row r="139">
       <c r="A139" t="n">
-        <v>129624696</v>
+        <v>122780924</v>
       </c>
       <c r="B139" t="n">
-        <v>90946</v>
+        <v>96554</v>
       </c>
       <c r="D139" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E139" t="n">
-        <v>889</v>
+        <v>210</v>
       </c>
       <c r="F139" t="inlineStr">
         <is>
-          <t>Vintertagging</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G139" t="inlineStr">
         <is>
-          <t>Plicatura pendula</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H139" t="inlineStr">
         <is>
-          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
         </is>
       </c>
       <c r="I139" t="inlineStr"/>
       <c r="J139" t="inlineStr"/>
       <c r="K139" t="inlineStr"/>
+      <c r="L139" t="inlineStr"/>
       <c r="N139" t="inlineStr"/>
       <c r="P139" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Grön sköldmossa, Srm</t>
         </is>
       </c>
       <c r="Q139" t="n">
-        <v>687973</v>
+        <v>687970</v>
       </c>
       <c r="R139" t="n">
-        <v>6562815</v>
+        <v>6562732</v>
       </c>
       <c r="S139" t="n">
         <v>10</v>
@@ -15939,17 +15942,17 @@
       </c>
       <c r="Y139" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA139" t="inlineStr">
         <is>
-          <t>2025-11-09</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AC139" t="inlineStr">
         <is>
-          <t>På död tall.</t>
+          <t>Grön sköldmossa på rutten stam</t>
         </is>
       </c>
       <c r="AD139" t="b">
@@ -15965,27 +15968,27 @@
       <c r="AT139" t="inlineStr"/>
       <c r="AW139" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX139" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY139" t="inlineStr"/>
       <c r="AZ139" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129624696</t>
+          <t>https://artportalen.se/Sighting/122780924</t>
         </is>
       </c>
     </row>
     <row r="140">
       <c r="A140" t="n">
-        <v>122203275</v>
+        <v>129624531</v>
       </c>
       <c r="B140" t="n">
-        <v>91909</v>
+        <v>90946</v>
       </c>
       <c r="D140" t="inlineStr">
         <is>
@@ -15993,21 +15996,21 @@
         </is>
       </c>
       <c r="E140" t="n">
-        <v>1202</v>
+        <v>889</v>
       </c>
       <c r="F140" t="inlineStr">
         <is>
-          <t>Ullticka</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G140" t="inlineStr">
         <is>
-          <t>Phellinidium ferrugineofuscum</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H140" t="inlineStr">
         <is>
-          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
         </is>
       </c>
       <c r="I140" t="inlineStr"/>
@@ -16016,14 +16019,14 @@
       <c r="N140" t="inlineStr"/>
       <c r="P140" t="inlineStr">
         <is>
-          <t>Ö Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q140" t="n">
-        <v>687981</v>
+        <v>687931</v>
       </c>
       <c r="R140" t="n">
-        <v>6562724</v>
+        <v>6562811</v>
       </c>
       <c r="S140" t="n">
         <v>10</v>
@@ -16050,12 +16053,12 @@
       </c>
       <c r="Y140" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA140" t="inlineStr">
         <is>
-          <t>2025-01-18</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AD140" t="b">
@@ -16082,45 +16085,41 @@
       <c r="AY140" t="inlineStr"/>
       <c r="AZ140" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122203275</t>
+          <t>https://artportalen.se/Sighting/129624531</t>
         </is>
       </c>
     </row>
     <row r="141">
       <c r="A141" t="n">
-        <v>135358856</v>
+        <v>129624696</v>
       </c>
       <c r="B141" t="n">
-        <v>91545</v>
+        <v>90946</v>
       </c>
       <c r="D141" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E141" t="n">
-        <v>2051</v>
+        <v>889</v>
       </c>
       <c r="F141" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Vintertagging</t>
         </is>
       </c>
       <c r="G141" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Plicatura pendula</t>
         </is>
       </c>
       <c r="H141" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
-        </is>
-      </c>
-      <c r="I141" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Alb. &amp; Schwein.) B.Palla &amp; al.</t>
+        </is>
+      </c>
+      <c r="I141" t="inlineStr"/>
       <c r="J141" t="inlineStr"/>
       <c r="K141" t="inlineStr"/>
       <c r="N141" t="inlineStr"/>
@@ -16130,10 +16129,10 @@
         </is>
       </c>
       <c r="Q141" t="n">
-        <v>688004</v>
+        <v>687973</v>
       </c>
       <c r="R141" t="n">
-        <v>6562799</v>
+        <v>6562815</v>
       </c>
       <c r="S141" t="n">
         <v>10</v>
@@ -16160,12 +16159,17 @@
       </c>
       <c r="Y141" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2025-11-09</t>
         </is>
       </c>
       <c r="AA141" t="inlineStr">
         <is>
-          <t>2026-07-23</t>
+          <t>2025-11-09</t>
+        </is>
+      </c>
+      <c r="AC141" t="inlineStr">
+        <is>
+          <t>På död tall.</t>
         </is>
       </c>
       <c r="AD141" t="b">
@@ -16192,58 +16196,57 @@
       <c r="AY141" t="inlineStr"/>
       <c r="AZ141" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/135358856</t>
+          <t>https://artportalen.se/Sighting/129624696</t>
         </is>
       </c>
     </row>
     <row r="142">
       <c r="A142" t="n">
-        <v>136241603</v>
+        <v>122203275</v>
       </c>
       <c r="B142" t="n">
-        <v>96888</v>
+        <v>91909</v>
       </c>
       <c r="D142" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E142" t="n">
-        <v>2180</v>
+        <v>1202</v>
       </c>
       <c r="F142" t="inlineStr">
         <is>
-          <t>Blåmossa</t>
+          <t>Ullticka</t>
         </is>
       </c>
       <c r="G142" t="inlineStr">
         <is>
-          <t>Leucobryum glaucum</t>
+          <t>Phellinidium ferrugineofuscum</t>
         </is>
       </c>
       <c r="H142" t="inlineStr">
         <is>
-          <t>(Hedw.) Ångstr.</t>
+          <t>(P.Karst.) Fiasson &amp; Niemelä</t>
         </is>
       </c>
       <c r="I142" t="inlineStr"/>
       <c r="J142" t="inlineStr"/>
       <c r="K142" t="inlineStr"/>
-      <c r="L142" t="inlineStr"/>
       <c r="N142" t="inlineStr"/>
       <c r="P142" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>Ö Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q142" t="n">
-        <v>688059</v>
+        <v>687981</v>
       </c>
       <c r="R142" t="n">
-        <v>6562773</v>
+        <v>6562724</v>
       </c>
       <c r="S142" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T142" t="inlineStr">
         <is>
@@ -16267,22 +16270,12 @@
       </c>
       <c r="Y142" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z142" t="inlineStr">
-        <is>
-          <t>13:09</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AA142" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB142" t="inlineStr">
-        <is>
-          <t>13:09</t>
+          <t>2025-01-18</t>
         </is>
       </c>
       <c r="AD142" t="b">
@@ -16298,62 +16291,69 @@
       <c r="AT142" t="inlineStr"/>
       <c r="AW142" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX142" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY142" t="inlineStr"/>
       <c r="AZ142" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241603</t>
+          <t>https://artportalen.se/Sighting/122203275</t>
         </is>
       </c>
     </row>
     <row r="143">
       <c r="A143" t="n">
-        <v>136231090</v>
+        <v>135358856</v>
       </c>
       <c r="B143" t="n">
-        <v>96606</v>
+        <v>91545</v>
       </c>
       <c r="D143" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E143" t="n">
-        <v>2671</v>
+        <v>2051</v>
       </c>
       <c r="F143" t="inlineStr">
         <is>
-          <t>Fällmossa</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G143" t="inlineStr">
         <is>
-          <t>Antitrichia curtipendula</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H143" t="inlineStr">
         <is>
-          <t>(Hedw.) Brid.</t>
-        </is>
-      </c>
-      <c r="I143" t="inlineStr"/>
+          <t>Kytöv. &amp; M.Toivonen</t>
+        </is>
+      </c>
+      <c r="I143" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J143" t="inlineStr"/>
+      <c r="K143" t="inlineStr"/>
+      <c r="N143" t="inlineStr"/>
       <c r="P143" t="inlineStr">
         <is>
-          <t>Norrby torp, Norrby torp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q143" t="n">
-        <v>688046</v>
+        <v>688004</v>
       </c>
       <c r="R143" t="n">
-        <v>6562700</v>
+        <v>6562799</v>
       </c>
       <c r="S143" t="n">
         <v>10</v>
@@ -16380,12 +16380,12 @@
       </c>
       <c r="Y143" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AA143" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-07-23</t>
         </is>
       </c>
       <c r="AD143" t="b">
@@ -16394,33 +16394,34 @@
       <c r="AE143" t="b">
         <v>0</v>
       </c>
+      <c r="AF143" t="inlineStr"/>
       <c r="AG143" t="b">
         <v>0</v>
       </c>
       <c r="AT143" t="inlineStr"/>
       <c r="AW143" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX143" t="inlineStr">
         <is>
-          <t>Måns Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY143" t="inlineStr"/>
       <c r="AZ143" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136231090</t>
+          <t>https://artportalen.se/Sighting/135358856</t>
         </is>
       </c>
     </row>
     <row r="144">
       <c r="A144" t="n">
-        <v>128314411</v>
+        <v>136241603</v>
       </c>
       <c r="B144" t="n">
-        <v>92348</v>
+        <v>96888</v>
       </c>
       <c r="D144" t="inlineStr">
         <is>
@@ -16428,48 +16429,41 @@
         </is>
       </c>
       <c r="E144" t="n">
-        <v>5420</v>
+        <v>2180</v>
       </c>
       <c r="F144" t="inlineStr">
         <is>
-          <t>Grovticka</t>
+          <t>Blåmossa</t>
         </is>
       </c>
       <c r="G144" t="inlineStr">
         <is>
-          <t>Phaeolus schweinitzii</t>
+          <t>Leucobryum glaucum</t>
         </is>
       </c>
       <c r="H144" t="inlineStr">
         <is>
-          <t>(Fr.) Pat.</t>
-        </is>
-      </c>
-      <c r="I144" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J144" t="inlineStr">
-        <is>
-          <t>fruktkroppar</t>
-        </is>
-      </c>
+          <t>(Hedw.) Ångstr.</t>
+        </is>
+      </c>
+      <c r="I144" t="inlineStr"/>
+      <c r="J144" t="inlineStr"/>
       <c r="K144" t="inlineStr"/>
+      <c r="L144" t="inlineStr"/>
       <c r="N144" t="inlineStr"/>
       <c r="P144" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q144" t="n">
-        <v>688088</v>
+        <v>688059</v>
       </c>
       <c r="R144" t="n">
-        <v>6562722</v>
+        <v>6562773</v>
       </c>
       <c r="S144" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T144" t="inlineStr">
         <is>
@@ -16493,12 +16487,22 @@
       </c>
       <c r="Y144" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z144" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AA144" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB144" t="inlineStr">
+        <is>
+          <t>13:09</t>
         </is>
       </c>
       <c r="AD144" t="b">
@@ -16514,27 +16518,27 @@
       <c r="AT144" t="inlineStr"/>
       <c r="AW144" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX144" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY144" t="inlineStr"/>
       <c r="AZ144" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128314411</t>
+          <t>https://artportalen.se/Sighting/136241603</t>
         </is>
       </c>
     </row>
     <row r="145">
       <c r="A145" t="n">
-        <v>136268106</v>
+        <v>136231090</v>
       </c>
       <c r="B145" t="n">
-        <v>92037</v>
+        <v>96606</v>
       </c>
       <c r="D145" t="inlineStr">
         <is>
@@ -16542,37 +16546,34 @@
         </is>
       </c>
       <c r="E145" t="n">
-        <v>5447</v>
+        <v>2671</v>
       </c>
       <c r="F145" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fällmossa</t>
         </is>
       </c>
       <c r="G145" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Antitrichia curtipendula</t>
         </is>
       </c>
       <c r="H145" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>(Hedw.) Brid.</t>
         </is>
       </c>
       <c r="I145" t="inlineStr"/>
-      <c r="J145" t="inlineStr"/>
-      <c r="K145" t="inlineStr"/>
-      <c r="N145" t="inlineStr"/>
       <c r="P145" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby torp, Norrby torp, Srm</t>
         </is>
       </c>
       <c r="Q145" t="n">
-        <v>687910</v>
+        <v>688046</v>
       </c>
       <c r="R145" t="n">
-        <v>6562787</v>
+        <v>6562700</v>
       </c>
       <c r="S145" t="n">
         <v>10</v>
@@ -16607,71 +16608,73 @@
           <t>2026-08-30</t>
         </is>
       </c>
-      <c r="AC145" t="inlineStr">
-        <is>
-          <t>På rätt klen, senvuxen?, lutande granlåga i ett kärr.</t>
-        </is>
-      </c>
       <c r="AD145" t="b">
         <v>0</v>
       </c>
       <c r="AE145" t="b">
         <v>0</v>
       </c>
-      <c r="AF145" t="inlineStr"/>
       <c r="AG145" t="b">
         <v>0</v>
       </c>
       <c r="AT145" t="inlineStr"/>
       <c r="AW145" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AX145" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Måns Persson</t>
         </is>
       </c>
       <c r="AY145" t="inlineStr"/>
       <c r="AZ145" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136268106</t>
+          <t>https://artportalen.se/Sighting/136231090</t>
         </is>
       </c>
     </row>
     <row r="146">
       <c r="A146" t="n">
-        <v>128314833</v>
+        <v>128314411</v>
       </c>
       <c r="B146" t="n">
-        <v>93235</v>
+        <v>92348</v>
       </c>
       <c r="D146" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E146" t="n">
-        <v>5966</v>
+        <v>5420</v>
       </c>
       <c r="F146" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Grovticka</t>
         </is>
       </c>
       <c r="G146" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Phaeolus schweinitzii</t>
         </is>
       </c>
       <c r="H146" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
-        </is>
-      </c>
-      <c r="I146" t="inlineStr"/>
-      <c r="J146" t="inlineStr"/>
+          <t>(Fr.) Pat.</t>
+        </is>
+      </c>
+      <c r="I146" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J146" t="inlineStr">
+        <is>
+          <t>fruktkroppar</t>
+        </is>
+      </c>
       <c r="K146" t="inlineStr"/>
       <c r="N146" t="inlineStr"/>
       <c r="P146" t="inlineStr">
@@ -16680,10 +16683,10 @@
         </is>
       </c>
       <c r="Q146" t="n">
-        <v>688073</v>
+        <v>688088</v>
       </c>
       <c r="R146" t="n">
-        <v>6562768</v>
+        <v>6562722</v>
       </c>
       <c r="S146" t="n">
         <v>10</v>
@@ -16742,38 +16745,38 @@
       <c r="AY146" t="inlineStr"/>
       <c r="AZ146" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128314833</t>
+          <t>https://artportalen.se/Sighting/128314411</t>
         </is>
       </c>
     </row>
     <row r="147">
       <c r="A147" t="n">
-        <v>128317789</v>
+        <v>136268106</v>
       </c>
       <c r="B147" t="n">
-        <v>93235</v>
+        <v>92037</v>
       </c>
       <c r="D147" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E147" t="n">
-        <v>5966</v>
+        <v>5447</v>
       </c>
       <c r="F147" t="inlineStr">
         <is>
-          <t>Motaggsvamp</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G147" t="inlineStr">
         <is>
-          <t>Sarcodon squamosus</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H147" t="inlineStr">
         <is>
-          <t>(Schaeff.) Quél.</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I147" t="inlineStr"/>
@@ -16786,10 +16789,10 @@
         </is>
       </c>
       <c r="Q147" t="n">
-        <v>688094</v>
+        <v>687910</v>
       </c>
       <c r="R147" t="n">
-        <v>6562777</v>
+        <v>6562787</v>
       </c>
       <c r="S147" t="n">
         <v>10</v>
@@ -16816,12 +16819,17 @@
       </c>
       <c r="Y147" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA147" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AC147" t="inlineStr">
+        <is>
+          <t>På rätt klen, senvuxen?, lutande granlåga i ett kärr.</t>
         </is>
       </c>
       <c r="AD147" t="b">
@@ -16848,13 +16856,13 @@
       <c r="AY147" t="inlineStr"/>
       <c r="AZ147" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317789</t>
+          <t>https://artportalen.se/Sighting/136268106</t>
         </is>
       </c>
     </row>
     <row r="148">
       <c r="A148" t="n">
-        <v>128526064</v>
+        <v>128314833</v>
       </c>
       <c r="B148" t="n">
         <v>93235</v>
@@ -16892,10 +16900,10 @@
         </is>
       </c>
       <c r="Q148" t="n">
-        <v>687952</v>
+        <v>688073</v>
       </c>
       <c r="R148" t="n">
-        <v>6562790</v>
+        <v>6562768</v>
       </c>
       <c r="S148" t="n">
         <v>10</v>
@@ -16922,12 +16930,12 @@
       </c>
       <c r="Y148" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA148" t="inlineStr">
         <is>
-          <t>2025-09-18</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD148" t="b">
@@ -16954,13 +16962,13 @@
       <c r="AY148" t="inlineStr"/>
       <c r="AZ148" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128526064</t>
+          <t>https://artportalen.se/Sighting/128314833</t>
         </is>
       </c>
     </row>
     <row r="149">
       <c r="A149" t="n">
-        <v>128646583</v>
+        <v>128317789</v>
       </c>
       <c r="B149" t="n">
         <v>93235</v>
@@ -16998,10 +17006,10 @@
         </is>
       </c>
       <c r="Q149" t="n">
-        <v>688067</v>
+        <v>688094</v>
       </c>
       <c r="R149" t="n">
-        <v>6562731</v>
+        <v>6562777</v>
       </c>
       <c r="S149" t="n">
         <v>10</v>
@@ -17028,12 +17036,12 @@
       </c>
       <c r="Y149" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA149" t="inlineStr">
         <is>
-          <t>2025-09-23</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD149" t="b">
@@ -17060,16 +17068,16 @@
       <c r="AY149" t="inlineStr"/>
       <c r="AZ149" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128646583</t>
+          <t>https://artportalen.se/Sighting/128317789</t>
         </is>
       </c>
     </row>
     <row r="150">
       <c r="A150" t="n">
-        <v>136241765</v>
+        <v>128526064</v>
       </c>
       <c r="B150" t="n">
-        <v>80069</v>
+        <v>93235</v>
       </c>
       <c r="D150" t="inlineStr">
         <is>
@@ -17077,44 +17085,40 @@
         </is>
       </c>
       <c r="E150" t="n">
-        <v>6453</v>
+        <v>5966</v>
       </c>
       <c r="F150" t="inlineStr">
         <is>
-          <t>Vedskivlav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G150" t="inlineStr">
         <is>
-          <t>Hertelidea botryosa</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H150" t="inlineStr">
         <is>
-          <t>(Fr.) Printzen &amp; Kantvilas</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I150" t="inlineStr"/>
       <c r="J150" t="inlineStr"/>
-      <c r="K150" t="inlineStr">
-        <is>
-          <t>med apothecier</t>
-        </is>
-      </c>
+      <c r="K150" t="inlineStr"/>
       <c r="N150" t="inlineStr"/>
       <c r="P150" t="inlineStr">
         <is>
-          <t>Norrbytorp, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q150" t="n">
-        <v>688014</v>
+        <v>687952</v>
       </c>
       <c r="R150" t="n">
-        <v>6562734</v>
+        <v>6562790</v>
       </c>
       <c r="S150" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T150" t="inlineStr">
         <is>
@@ -17138,22 +17142,12 @@
       </c>
       <c r="Y150" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="Z150" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AA150" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AB150" t="inlineStr">
-        <is>
-          <t>12:38</t>
+          <t>2025-09-18</t>
         </is>
       </c>
       <c r="AD150" t="b">
@@ -17169,27 +17163,27 @@
       <c r="AT150" t="inlineStr"/>
       <c r="AW150" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX150" t="inlineStr">
         <is>
-          <t>Björn Persson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY150" t="inlineStr"/>
       <c r="AZ150" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241765</t>
+          <t>https://artportalen.se/Sighting/128526064</t>
         </is>
       </c>
     </row>
     <row r="151">
       <c r="A151" t="n">
-        <v>17285491</v>
+        <v>128646583</v>
       </c>
       <c r="B151" t="n">
-        <v>80432</v>
+        <v>93235</v>
       </c>
       <c r="D151" t="inlineStr">
         <is>
@@ -17197,36 +17191,37 @@
         </is>
       </c>
       <c r="E151" t="n">
-        <v>6458</v>
+        <v>5966</v>
       </c>
       <c r="F151" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Motaggsvamp</t>
         </is>
       </c>
       <c r="G151" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Sarcodon squamosus</t>
         </is>
       </c>
       <c r="H151" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Schaeff.) Quél.</t>
         </is>
       </c>
       <c r="I151" t="inlineStr"/>
       <c r="J151" t="inlineStr"/>
       <c r="K151" t="inlineStr"/>
+      <c r="N151" t="inlineStr"/>
       <c r="P151" t="inlineStr">
         <is>
-          <t>Norrby torp, 480 m Ö, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q151" t="n">
-        <v>688111</v>
+        <v>688067</v>
       </c>
       <c r="R151" t="n">
-        <v>6562706</v>
+        <v>6562731</v>
       </c>
       <c r="S151" t="n">
         <v>10</v>
@@ -17253,17 +17248,12 @@
       </c>
       <c r="Y151" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AA151" t="inlineStr">
         <is>
-          <t>2015-04-02</t>
-        </is>
-      </c>
-      <c r="AC151" t="inlineStr">
-        <is>
-          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
+          <t>2025-09-23</t>
         </is>
       </c>
       <c r="AD151" t="b">
@@ -17272,38 +17262,34 @@
       <c r="AE151" t="b">
         <v>0</v>
       </c>
+      <c r="AF151" t="inlineStr"/>
       <c r="AG151" t="b">
         <v>0</v>
-      </c>
-      <c r="AI151" t="inlineStr">
-        <is>
-          <t>Yngre gallrad blandskog</t>
-        </is>
       </c>
       <c r="AT151" t="inlineStr"/>
       <c r="AW151" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX151" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY151" t="inlineStr"/>
       <c r="AZ151" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/17285491</t>
+          <t>https://artportalen.se/Sighting/128646583</t>
         </is>
       </c>
     </row>
     <row r="152">
       <c r="A152" t="n">
-        <v>79273786</v>
+        <v>136241765</v>
       </c>
       <c r="B152" t="n">
-        <v>80432</v>
+        <v>80069</v>
       </c>
       <c r="D152" t="inlineStr">
         <is>
@@ -17311,37 +17297,44 @@
         </is>
       </c>
       <c r="E152" t="n">
-        <v>6458</v>
+        <v>6453</v>
       </c>
       <c r="F152" t="inlineStr">
         <is>
-          <t>Lunglav</t>
+          <t>Vedskivlav</t>
         </is>
       </c>
       <c r="G152" t="inlineStr">
         <is>
-          <t>Lobaria pulmonaria</t>
+          <t>Hertelidea botryosa</t>
         </is>
       </c>
       <c r="H152" t="inlineStr">
         <is>
-          <t>(L.) Hoffm.</t>
+          <t>(Fr.) Printzen &amp; Kantvilas</t>
         </is>
       </c>
       <c r="I152" t="inlineStr"/>
+      <c r="J152" t="inlineStr"/>
+      <c r="K152" t="inlineStr">
+        <is>
+          <t>med apothecier</t>
+        </is>
+      </c>
+      <c r="N152" t="inlineStr"/>
       <c r="P152" t="inlineStr">
         <is>
-          <t>Åvadal, Srm</t>
+          <t>Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q152" t="n">
-        <v>688109</v>
+        <v>688014</v>
       </c>
       <c r="R152" t="n">
-        <v>6562704</v>
+        <v>6562734</v>
       </c>
       <c r="S152" t="n">
-        <v>10</v>
+        <v>5</v>
       </c>
       <c r="T152" t="inlineStr">
         <is>
@@ -17365,12 +17358,22 @@
       </c>
       <c r="Y152" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="Z152" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AA152" t="inlineStr">
         <is>
-          <t>2019-08-01</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AB152" t="inlineStr">
+        <is>
+          <t>12:38</t>
         </is>
       </c>
       <c r="AD152" t="b">
@@ -17379,45 +17382,31 @@
       <c r="AE152" t="b">
         <v>0</v>
       </c>
+      <c r="AF152" t="inlineStr"/>
       <c r="AG152" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ152" t="inlineStr">
-        <is>
-          <t>skogsek</t>
-        </is>
-      </c>
-      <c r="AK152" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
-      </c>
-      <c r="AO152" t="inlineStr">
-        <is>
-          <t>Quercus robur</t>
-        </is>
       </c>
       <c r="AT152" t="inlineStr"/>
       <c r="AW152" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AX152" t="inlineStr">
         <is>
-          <t>Gustav Wikström</t>
+          <t>Björn Persson</t>
         </is>
       </c>
       <c r="AY152" t="inlineStr"/>
       <c r="AZ152" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/79273786</t>
+          <t>https://artportalen.se/Sighting/136241765</t>
         </is>
       </c>
     </row>
     <row r="153">
       <c r="A153" t="n">
-        <v>89840770</v>
+        <v>17285491</v>
       </c>
       <c r="B153" t="n">
         <v>80432</v>
@@ -17448,17 +17437,16 @@
       <c r="I153" t="inlineStr"/>
       <c r="J153" t="inlineStr"/>
       <c r="K153" t="inlineStr"/>
-      <c r="N153" t="inlineStr"/>
       <c r="P153" t="inlineStr">
         <is>
-          <t>Ö Norrby Torp, Srm</t>
+          <t>Norrby torp, 480 m Ö, Srm</t>
         </is>
       </c>
       <c r="Q153" t="n">
-        <v>688146</v>
+        <v>688111</v>
       </c>
       <c r="R153" t="n">
-        <v>6562738</v>
+        <v>6562706</v>
       </c>
       <c r="S153" t="n">
         <v>10</v>
@@ -17485,17 +17473,17 @@
       </c>
       <c r="Y153" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2015-04-02</t>
         </is>
       </c>
       <c r="AA153" t="inlineStr">
         <is>
-          <t>2020-12-30</t>
+          <t>2015-04-02</t>
         </is>
       </c>
       <c r="AC153" t="inlineStr">
         <is>
-          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
+          <t>På ek i bergskanten, ca 220 cm omkrets. Sparsamt vid 20 resp. 70 cm höjd.</t>
         </is>
       </c>
       <c r="AD153" t="b">
@@ -17504,31 +17492,35 @@
       <c r="AE153" t="b">
         <v>0</v>
       </c>
-      <c r="AF153" t="inlineStr"/>
       <c r="AG153" t="b">
         <v>0</v>
+      </c>
+      <c r="AI153" t="inlineStr">
+        <is>
+          <t>Yngre gallrad blandskog</t>
+        </is>
       </c>
       <c r="AT153" t="inlineStr"/>
       <c r="AW153" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX153" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AY153" t="inlineStr"/>
       <c r="AZ153" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/89840770</t>
+          <t>https://artportalen.se/Sighting/17285491</t>
         </is>
       </c>
     </row>
     <row r="154">
       <c r="A154" t="n">
-        <v>112384453</v>
+        <v>79273786</v>
       </c>
       <c r="B154" t="n">
         <v>80432</v>
@@ -17557,19 +17549,16 @@
         </is>
       </c>
       <c r="I154" t="inlineStr"/>
-      <c r="J154" t="inlineStr"/>
-      <c r="K154" t="inlineStr"/>
-      <c r="N154" t="inlineStr"/>
       <c r="P154" t="inlineStr">
         <is>
-          <t>Norrby torp Ö om, Srm</t>
+          <t>Åvadal, Srm</t>
         </is>
       </c>
       <c r="Q154" t="n">
-        <v>688145</v>
+        <v>688109</v>
       </c>
       <c r="R154" t="n">
-        <v>6562737</v>
+        <v>6562704</v>
       </c>
       <c r="S154" t="n">
         <v>10</v>
@@ -17596,17 +17585,12 @@
       </c>
       <c r="Y154" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AA154" t="inlineStr">
         <is>
-          <t>2023-09-28</t>
-        </is>
-      </c>
-      <c r="AC154" t="inlineStr">
-        <is>
-          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
+          <t>2019-08-01</t>
         </is>
       </c>
       <c r="AD154" t="b">
@@ -17615,31 +17599,45 @@
       <c r="AE154" t="b">
         <v>0</v>
       </c>
-      <c r="AF154" t="inlineStr"/>
       <c r="AG154" t="b">
         <v>0</v>
+      </c>
+      <c r="AJ154" t="inlineStr">
+        <is>
+          <t>skogsek</t>
+        </is>
+      </c>
+      <c r="AK154" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
+      </c>
+      <c r="AO154" t="inlineStr">
+        <is>
+          <t>Quercus robur</t>
+        </is>
       </c>
       <c r="AT154" t="inlineStr"/>
       <c r="AW154" t="inlineStr">
         <is>
-          <t>Ulf Johansson</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AX154" t="inlineStr">
         <is>
-          <t>Ulf Johansson, Bodil Ravn</t>
+          <t>Gustav Wikström</t>
         </is>
       </c>
       <c r="AY154" t="inlineStr"/>
       <c r="AZ154" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/112384453</t>
+          <t>https://artportalen.se/Sighting/79273786</t>
         </is>
       </c>
     </row>
     <row r="155">
       <c r="A155" t="n">
-        <v>122779297</v>
+        <v>89840770</v>
       </c>
       <c r="B155" t="n">
         <v>80432</v>
@@ -17673,14 +17671,14 @@
       <c r="N155" t="inlineStr"/>
       <c r="P155" t="inlineStr">
         <is>
-          <t>Lunglav, Srm</t>
+          <t>Ö Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q155" t="n">
-        <v>688116</v>
+        <v>688146</v>
       </c>
       <c r="R155" t="n">
-        <v>6562703</v>
+        <v>6562738</v>
       </c>
       <c r="S155" t="n">
         <v>10</v>
@@ -17707,17 +17705,17 @@
       </c>
       <c r="Y155" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AA155" t="inlineStr">
         <is>
-          <t>2025-02-26</t>
+          <t>2020-12-30</t>
         </is>
       </c>
       <c r="AC155" t="inlineStr">
         <is>
-          <t>Lunglav på gammal ek</t>
+          <t>Tre bålar på en ek som inte längre ser ut att vara så livskraftig. Finns en annan noterad ek med lavar en bit ifrån.</t>
         </is>
       </c>
       <c r="AD155" t="b">
@@ -17733,81 +17731,68 @@
       <c r="AT155" t="inlineStr"/>
       <c r="AW155" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX155" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY155" t="inlineStr"/>
       <c r="AZ155" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122779297</t>
+          <t>https://artportalen.se/Sighting/89840770</t>
         </is>
       </c>
     </row>
     <row r="156">
       <c r="A156" t="n">
-        <v>125923864</v>
+        <v>112384453</v>
       </c>
       <c r="B156" t="n">
-        <v>57754</v>
+        <v>80432</v>
       </c>
       <c r="D156" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E156" t="n">
-        <v>102118</v>
+        <v>6458</v>
       </c>
       <c r="F156" t="inlineStr">
         <is>
-          <t>Nattskärra</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G156" t="inlineStr">
         <is>
-          <t>Caprimulgus europaeus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H156" t="inlineStr">
         <is>
-          <t>Linnaeus, 1758</t>
-        </is>
-      </c>
-      <c r="I156" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(L.) Hoffm.</t>
+        </is>
+      </c>
+      <c r="I156" t="inlineStr"/>
+      <c r="J156" t="inlineStr"/>
       <c r="K156" t="inlineStr"/>
-      <c r="L156" t="inlineStr">
-        <is>
-          <t>hona</t>
-        </is>
-      </c>
-      <c r="M156" t="inlineStr">
-        <is>
-          <t>bo, ägg/ungar</t>
-        </is>
-      </c>
       <c r="N156" t="inlineStr"/>
       <c r="P156" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Norrby torp Ö om, Srm</t>
         </is>
       </c>
       <c r="Q156" t="n">
-        <v>687916</v>
+        <v>688145</v>
       </c>
       <c r="R156" t="n">
-        <v>6562815</v>
+        <v>6562737</v>
       </c>
       <c r="S156" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T156" t="inlineStr">
         <is>
@@ -17831,17 +17816,17 @@
       </c>
       <c r="Y156" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AA156" t="inlineStr">
         <is>
-          <t>2025-06-13</t>
+          <t>2023-09-28</t>
         </is>
       </c>
       <c r="AC156" t="inlineStr">
         <is>
-          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
+          <t>Återfynd. På halvdöd ek med blottad ved men några levande grenar i toppen, ca 120 cm omkrets. Två mindre blaffor i dåligt skick, hänger något löst, ca 40 resp. 130 cm höjd.</t>
         </is>
       </c>
       <c r="AD156" t="b">
@@ -17850,33 +17835,34 @@
       <c r="AE156" t="b">
         <v>0</v>
       </c>
+      <c r="AF156" t="inlineStr"/>
       <c r="AG156" t="b">
         <v>0</v>
       </c>
       <c r="AT156" t="inlineStr"/>
       <c r="AW156" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson</t>
         </is>
       </c>
       <c r="AX156" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Ulf Johansson, Bodil Ravn</t>
         </is>
       </c>
       <c r="AY156" t="inlineStr"/>
       <c r="AZ156" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125923864</t>
+          <t>https://artportalen.se/Sighting/112384453</t>
         </is>
       </c>
     </row>
     <row r="157">
       <c r="A157" t="n">
-        <v>128317861</v>
+        <v>122779297</v>
       </c>
       <c r="B157" t="n">
-        <v>58114</v>
+        <v>80432</v>
       </c>
       <c r="D157" t="inlineStr">
         <is>
@@ -17884,45 +17870,40 @@
         </is>
       </c>
       <c r="E157" t="n">
-        <v>103021</v>
+        <v>6458</v>
       </c>
       <c r="F157" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Lunglav</t>
         </is>
       </c>
       <c r="G157" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Lobaria pulmonaria</t>
         </is>
       </c>
       <c r="H157" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
+          <t>(L.) Hoffm.</t>
         </is>
       </c>
       <c r="I157" t="inlineStr"/>
+      <c r="J157" t="inlineStr"/>
       <c r="K157" t="inlineStr"/>
-      <c r="L157" t="inlineStr"/>
-      <c r="M157" t="inlineStr">
-        <is>
-          <t>lockläte, övriga läten</t>
-        </is>
-      </c>
       <c r="N157" t="inlineStr"/>
       <c r="P157" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Lunglav, Srm</t>
         </is>
       </c>
       <c r="Q157" t="n">
-        <v>688058</v>
+        <v>688116</v>
       </c>
       <c r="R157" t="n">
-        <v>6562805</v>
+        <v>6562703</v>
       </c>
       <c r="S157" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T157" t="inlineStr">
         <is>
@@ -17946,12 +17927,17 @@
       </c>
       <c r="Y157" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-02-26</t>
         </is>
       </c>
       <c r="AA157" t="inlineStr">
         <is>
-          <t>2025-09-08</t>
+          <t>2025-02-26</t>
+        </is>
+      </c>
+      <c r="AC157" t="inlineStr">
+        <is>
+          <t>Lunglav på gammal ek</t>
         </is>
       </c>
       <c r="AD157" t="b">
@@ -17960,63 +17946,72 @@
       <c r="AE157" t="b">
         <v>0</v>
       </c>
+      <c r="AF157" t="inlineStr"/>
       <c r="AG157" t="b">
         <v>0</v>
       </c>
       <c r="AT157" t="inlineStr"/>
       <c r="AW157" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX157" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY157" t="inlineStr"/>
       <c r="AZ157" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/128317861</t>
+          <t>https://artportalen.se/Sighting/122779297</t>
         </is>
       </c>
     </row>
     <row r="158">
       <c r="A158" t="n">
-        <v>136138855</v>
+        <v>125923864</v>
       </c>
       <c r="B158" t="n">
-        <v>58149</v>
+        <v>57754</v>
       </c>
       <c r="D158" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E158" t="n">
-        <v>103021</v>
+        <v>102118</v>
       </c>
       <c r="F158" t="inlineStr">
         <is>
-          <t>Talltita</t>
+          <t>Nattskärra</t>
         </is>
       </c>
       <c r="G158" t="inlineStr">
         <is>
-          <t>Poecile montanus</t>
+          <t>Caprimulgus europaeus</t>
         </is>
       </c>
       <c r="H158" t="inlineStr">
         <is>
-          <t>(Conrad von Baldenstein, 1827)</t>
-        </is>
-      </c>
-      <c r="I158" t="inlineStr"/>
+          <t>Linnaeus, 1758</t>
+        </is>
+      </c>
+      <c r="I158" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="K158" t="inlineStr"/>
-      <c r="L158" t="inlineStr"/>
+      <c r="L158" t="inlineStr">
+        <is>
+          <t>hona</t>
+        </is>
+      </c>
       <c r="M158" t="inlineStr">
         <is>
-          <t>lockläte, övriga läten</t>
+          <t>bo, ägg/ungar</t>
         </is>
       </c>
       <c r="N158" t="inlineStr"/>
@@ -18026,13 +18021,13 @@
         </is>
       </c>
       <c r="Q158" t="n">
-        <v>687836</v>
+        <v>687916</v>
       </c>
       <c r="R158" t="n">
-        <v>6562786</v>
+        <v>6562815</v>
       </c>
       <c r="S158" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T158" t="inlineStr">
         <is>
@@ -18056,12 +18051,17 @@
       </c>
       <c r="Y158" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-06-13</t>
         </is>
       </c>
       <c r="AA158" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-06-13</t>
+        </is>
+      </c>
+      <c r="AC158" t="inlineStr">
+        <is>
+          <t>Stöttes och stannade nära, det fanns ett ägg. Än så länge?</t>
         </is>
       </c>
       <c r="AD158" t="b">
@@ -18087,16 +18087,16 @@
       <c r="AY158" t="inlineStr"/>
       <c r="AZ158" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136138855</t>
+          <t>https://artportalen.se/Sighting/125923864</t>
         </is>
       </c>
     </row>
     <row r="159">
       <c r="A159" t="n">
-        <v>136138971</v>
+        <v>128317861</v>
       </c>
       <c r="B159" t="n">
-        <v>58149</v>
+        <v>58114</v>
       </c>
       <c r="D159" t="inlineStr">
         <is>
@@ -18136,10 +18136,10 @@
         </is>
       </c>
       <c r="Q159" t="n">
-        <v>687977</v>
+        <v>688058</v>
       </c>
       <c r="R159" t="n">
-        <v>6562735</v>
+        <v>6562805</v>
       </c>
       <c r="S159" t="n">
         <v>25</v>
@@ -18166,12 +18166,12 @@
       </c>
       <c r="Y159" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AA159" t="inlineStr">
         <is>
-          <t>2026-08-25</t>
+          <t>2025-09-08</t>
         </is>
       </c>
       <c r="AD159" t="b">
@@ -18197,68 +18197,59 @@
       <c r="AY159" t="inlineStr"/>
       <c r="AZ159" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136138971</t>
+          <t>https://artportalen.se/Sighting/128317861</t>
         </is>
       </c>
     </row>
     <row r="160">
       <c r="A160" t="n">
-        <v>122692266</v>
+        <v>136138855</v>
       </c>
       <c r="B160" t="n">
-        <v>58826</v>
+        <v>58149</v>
       </c>
       <c r="D160" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E160" t="n">
-        <v>208242</v>
+        <v>103021</v>
       </c>
       <c r="F160" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G160" t="inlineStr">
         <is>
-          <t>Lissotriton vulgaris</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H160" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
-        </is>
-      </c>
-      <c r="I160" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
-      <c r="J160" t="inlineStr"/>
+          <t>(Conrad von Baldenstein, 1827)</t>
+        </is>
+      </c>
+      <c r="I160" t="inlineStr"/>
       <c r="K160" t="inlineStr"/>
       <c r="L160" t="inlineStr"/>
       <c r="M160" t="inlineStr">
         <is>
-          <t>födosökande</t>
-        </is>
-      </c>
-      <c r="N160" t="inlineStr">
-        <is>
-          <t>observerad</t>
-        </is>
-      </c>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
+      <c r="N160" t="inlineStr"/>
       <c r="P160" t="inlineStr">
         <is>
-          <t>Mindre vattensalamander, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q160" t="n">
-        <v>687868</v>
+        <v>687836</v>
       </c>
       <c r="R160" t="n">
-        <v>6562755</v>
+        <v>6562786</v>
       </c>
       <c r="S160" t="n">
         <v>10</v>
@@ -18285,17 +18276,12 @@
       </c>
       <c r="Y160" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA160" t="inlineStr">
         <is>
-          <t>2024-09-16</t>
-        </is>
-      </c>
-      <c r="AC160" t="inlineStr">
-        <is>
-          <t>Mindre vattensalamander</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD160" t="b">
@@ -18304,63 +18290,65 @@
       <c r="AE160" t="b">
         <v>0</v>
       </c>
-      <c r="AF160" t="inlineStr"/>
       <c r="AG160" t="b">
         <v>0</v>
       </c>
       <c r="AT160" t="inlineStr"/>
       <c r="AW160" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX160" t="inlineStr">
         <is>
-          <t>Jenny Nyholm</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY160" t="inlineStr"/>
       <c r="AZ160" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122692266</t>
+          <t>https://artportalen.se/Sighting/136138855</t>
         </is>
       </c>
     </row>
     <row r="161">
       <c r="A161" t="n">
-        <v>136241491</v>
+        <v>136138971</v>
       </c>
       <c r="B161" t="n">
-        <v>58825</v>
+        <v>58149</v>
       </c>
       <c r="D161" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E161" t="n">
-        <v>208245</v>
+        <v>103021</v>
       </c>
       <c r="F161" t="inlineStr">
         <is>
-          <t>Vanlig padda</t>
+          <t>Talltita</t>
         </is>
       </c>
       <c r="G161" t="inlineStr">
         <is>
-          <t>Bufo bufo</t>
+          <t>Poecile montanus</t>
         </is>
       </c>
       <c r="H161" t="inlineStr">
         <is>
-          <t>(Linnaeus, 1758)</t>
+          <t>(Conrad von Baldenstein, 1827)</t>
         </is>
       </c>
       <c r="I161" t="inlineStr"/>
-      <c r="J161" t="inlineStr"/>
       <c r="K161" t="inlineStr"/>
       <c r="L161" t="inlineStr"/>
-      <c r="M161" t="inlineStr"/>
+      <c r="M161" t="inlineStr">
+        <is>
+          <t>lockläte, övriga läten</t>
+        </is>
+      </c>
       <c r="N161" t="inlineStr"/>
       <c r="P161" t="inlineStr">
         <is>
@@ -18368,13 +18356,13 @@
         </is>
       </c>
       <c r="Q161" t="n">
-        <v>687873</v>
+        <v>687977</v>
       </c>
       <c r="R161" t="n">
-        <v>6562755</v>
+        <v>6562735</v>
       </c>
       <c r="S161" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T161" t="inlineStr">
         <is>
@@ -18398,17 +18386,12 @@
       </c>
       <c r="Y161" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AA161" t="inlineStr">
         <is>
-          <t>2026-08-30</t>
-        </is>
-      </c>
-      <c r="AC161" t="inlineStr">
-        <is>
-          <t>Troligen årsunge.</t>
+          <t>2026-08-25</t>
         </is>
       </c>
       <c r="AD161" t="b">
@@ -18417,7 +18400,6 @@
       <c r="AE161" t="b">
         <v>0</v>
       </c>
-      <c r="AF161" t="inlineStr"/>
       <c r="AG161" t="b">
         <v>0</v>
       </c>
@@ -18435,16 +18417,16 @@
       <c r="AY161" t="inlineStr"/>
       <c r="AZ161" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/136241491</t>
+          <t>https://artportalen.se/Sighting/136138971</t>
         </is>
       </c>
     </row>
     <row r="162">
       <c r="A162" t="n">
-        <v>101544040</v>
+        <v>122692266</v>
       </c>
       <c r="B162" t="n">
-        <v>99035</v>
+        <v>58826</v>
       </c>
       <c r="D162" t="inlineStr">
         <is>
@@ -18452,41 +18434,54 @@
         </is>
       </c>
       <c r="E162" t="n">
-        <v>219790</v>
+        <v>208242</v>
       </c>
       <c r="F162" t="inlineStr">
         <is>
-          <t>Fläcknycklar</t>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="G162" t="inlineStr">
         <is>
-          <t>Dactylorhiza maculata</t>
+          <t>Lissotriton vulgaris</t>
         </is>
       </c>
       <c r="H162" t="inlineStr">
         <is>
-          <t>(L.) Soó</t>
-        </is>
-      </c>
-      <c r="I162" t="inlineStr"/>
+          <t>(Linnaeus, 1758)</t>
+        </is>
+      </c>
+      <c r="I162" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
       <c r="J162" t="inlineStr"/>
       <c r="K162" t="inlineStr"/>
       <c r="L162" t="inlineStr"/>
-      <c r="N162" t="inlineStr"/>
+      <c r="M162" t="inlineStr">
+        <is>
+          <t>födosökande</t>
+        </is>
+      </c>
+      <c r="N162" t="inlineStr">
+        <is>
+          <t>observerad</t>
+        </is>
+      </c>
       <c r="P162" t="inlineStr">
         <is>
-          <t>NO Norrby Torp, Srm</t>
+          <t>Mindre vattensalamander, Srm</t>
         </is>
       </c>
       <c r="Q162" t="n">
-        <v>687896</v>
+        <v>687868</v>
       </c>
       <c r="R162" t="n">
-        <v>6562764</v>
+        <v>6562755</v>
       </c>
       <c r="S162" t="n">
-        <v>25</v>
+        <v>10</v>
       </c>
       <c r="T162" t="inlineStr">
         <is>
@@ -18510,12 +18505,17 @@
       </c>
       <c r="Y162" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2024-09-16</t>
         </is>
       </c>
       <c r="AA162" t="inlineStr">
         <is>
-          <t>2022-06-09</t>
+          <t>2024-09-16</t>
+        </is>
+      </c>
+      <c r="AC162" t="inlineStr">
+        <is>
+          <t>Mindre vattensalamander</t>
         </is>
       </c>
       <c r="AD162" t="b">
@@ -18531,27 +18531,27 @@
       <c r="AT162" t="inlineStr"/>
       <c r="AW162" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AX162" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Jenny Nyholm</t>
         </is>
       </c>
       <c r="AY162" t="inlineStr"/>
       <c r="AZ162" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/101544040</t>
+          <t>https://artportalen.se/Sighting/122692266</t>
         </is>
       </c>
     </row>
     <row r="163">
       <c r="A163" t="n">
-        <v>122930166</v>
+        <v>136241491</v>
       </c>
       <c r="B163" t="n">
-        <v>96554</v>
+        <v>58825</v>
       </c>
       <c r="D163" t="inlineStr">
         <is>
@@ -18559,41 +18559,42 @@
         </is>
       </c>
       <c r="E163" t="n">
-        <v>210</v>
+        <v>208245</v>
       </c>
       <c r="F163" t="inlineStr">
         <is>
-          <t>Grön sköldmossa</t>
+          <t>Vanlig padda</t>
         </is>
       </c>
       <c r="G163" t="inlineStr">
         <is>
-          <t>Buxbaumia viridis</t>
+          <t>Bufo bufo</t>
         </is>
       </c>
       <c r="H163" t="inlineStr">
         <is>
-          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+          <t>(Linnaeus, 1758)</t>
         </is>
       </c>
       <c r="I163" t="inlineStr"/>
       <c r="J163" t="inlineStr"/>
       <c r="K163" t="inlineStr"/>
       <c r="L163" t="inlineStr"/>
+      <c r="M163" t="inlineStr"/>
       <c r="N163" t="inlineStr"/>
       <c r="P163" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q163" t="n">
-        <v>686762</v>
+        <v>687873</v>
       </c>
       <c r="R163" t="n">
-        <v>6562715</v>
+        <v>6562755</v>
       </c>
       <c r="S163" t="n">
-        <v>21</v>
+        <v>10</v>
       </c>
       <c r="T163" t="inlineStr">
         <is>
@@ -18617,22 +18618,17 @@
       </c>
       <c r="Y163" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z163" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2026-08-30</t>
         </is>
       </c>
       <c r="AA163" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB163" t="inlineStr">
-        <is>
-          <t>11:21</t>
+          <t>2026-08-30</t>
+        </is>
+      </c>
+      <c r="AC163" t="inlineStr">
+        <is>
+          <t>Troligen årsunge.</t>
         </is>
       </c>
       <c r="AD163" t="b">
@@ -18641,74 +18637,76 @@
       <c r="AE163" t="b">
         <v>0</v>
       </c>
+      <c r="AF163" t="inlineStr"/>
       <c r="AG163" t="b">
         <v>0</v>
       </c>
       <c r="AT163" t="inlineStr"/>
       <c r="AW163" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX163" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY163" t="inlineStr"/>
       <c r="AZ163" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122930166</t>
+          <t>https://artportalen.se/Sighting/136241491</t>
         </is>
       </c>
     </row>
     <row r="164">
       <c r="A164" t="n">
-        <v>119061006</v>
+        <v>101544040</v>
       </c>
       <c r="B164" t="n">
-        <v>91533</v>
+        <v>99035</v>
       </c>
       <c r="D164" t="inlineStr">
         <is>
-          <t>VU</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E164" t="n">
-        <v>2051</v>
+        <v>219790</v>
       </c>
       <c r="F164" t="inlineStr">
         <is>
-          <t>Rotfingersvamp</t>
+          <t>Fläcknycklar</t>
         </is>
       </c>
       <c r="G164" t="inlineStr">
         <is>
-          <t>Ramaria boreimaxima</t>
+          <t>Dactylorhiza maculata</t>
         </is>
       </c>
       <c r="H164" t="inlineStr">
         <is>
-          <t>Kytöv. &amp; M.Toivonen</t>
+          <t>(L.) Soó</t>
         </is>
       </c>
       <c r="I164" t="inlineStr"/>
       <c r="J164" t="inlineStr"/>
       <c r="K164" t="inlineStr"/>
+      <c r="L164" t="inlineStr"/>
       <c r="N164" t="inlineStr"/>
       <c r="P164" t="inlineStr">
         <is>
-          <t>S Norrby mosse, Srm</t>
+          <t>NO Norrby Torp, Srm</t>
         </is>
       </c>
       <c r="Q164" t="n">
-        <v>686477</v>
+        <v>687896</v>
       </c>
       <c r="R164" t="n">
-        <v>6562857</v>
+        <v>6562764</v>
       </c>
       <c r="S164" t="n">
-        <v>10</v>
+        <v>25</v>
       </c>
       <c r="T164" t="inlineStr">
         <is>
@@ -18732,17 +18730,12 @@
       </c>
       <c r="Y164" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AA164" t="inlineStr">
         <is>
-          <t>2024-07-29</t>
-        </is>
-      </c>
-      <c r="AC164" t="inlineStr">
-        <is>
-          <t>Brukad skog nära kant mot gammal.</t>
+          <t>2022-06-09</t>
         </is>
       </c>
       <c r="AD164" t="b">
@@ -18769,16 +18762,16 @@
       <c r="AY164" t="inlineStr"/>
       <c r="AZ164" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/119061006</t>
+          <t>https://artportalen.se/Sighting/101544040</t>
         </is>
       </c>
     </row>
     <row r="165">
       <c r="A165" t="n">
-        <v>122929535</v>
+        <v>122930166</v>
       </c>
       <c r="B165" t="n">
-        <v>8455</v>
+        <v>96554</v>
       </c>
       <c r="D165" t="inlineStr">
         <is>
@@ -18786,32 +18779,27 @@
         </is>
       </c>
       <c r="E165" t="n">
-        <v>106545</v>
+        <v>210</v>
       </c>
       <c r="F165" t="inlineStr">
         <is>
-          <t>Mindre märgborre</t>
+          <t>Grön sköldmossa</t>
         </is>
       </c>
       <c r="G165" t="inlineStr">
         <is>
-          <t>Tomicus minor</t>
+          <t>Buxbaumia viridis</t>
         </is>
       </c>
       <c r="H165" t="inlineStr">
         <is>
-          <t>(Hartig, 1834)</t>
-        </is>
-      </c>
-      <c r="I165" t="inlineStr">
-        <is>
-          <t>1</t>
-        </is>
-      </c>
+          <t>(Moug. ex Lam. &amp; DC.) Brid. ex Moug. &amp; Nestl.</t>
+        </is>
+      </c>
+      <c r="I165" t="inlineStr"/>
       <c r="J165" t="inlineStr"/>
       <c r="K165" t="inlineStr"/>
       <c r="L165" t="inlineStr"/>
-      <c r="M165" t="inlineStr"/>
       <c r="N165" t="inlineStr"/>
       <c r="P165" t="inlineStr">
         <is>
@@ -18819,13 +18807,13 @@
         </is>
       </c>
       <c r="Q165" t="n">
-        <v>686612</v>
+        <v>686762</v>
       </c>
       <c r="R165" t="n">
-        <v>6562882</v>
+        <v>6562715</v>
       </c>
       <c r="S165" t="n">
-        <v>9</v>
+        <v>21</v>
       </c>
       <c r="T165" t="inlineStr">
         <is>
@@ -18854,7 +18842,7 @@
       </c>
       <c r="Z165" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AA165" t="inlineStr">
@@ -18864,7 +18852,7 @@
       </c>
       <c r="AB165" t="inlineStr">
         <is>
-          <t>11:01</t>
+          <t>11:21</t>
         </is>
       </c>
       <c r="AD165" t="b">
@@ -18890,55 +18878,54 @@
       <c r="AY165" t="inlineStr"/>
       <c r="AZ165" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122929535</t>
+          <t>https://artportalen.se/Sighting/122930166</t>
         </is>
       </c>
     </row>
     <row r="166">
       <c r="A166" t="n">
-        <v>122928987</v>
+        <v>119061006</v>
       </c>
       <c r="B166" t="n">
-        <v>97983</v>
+        <v>91533</v>
       </c>
       <c r="D166" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>VU</t>
         </is>
       </c>
       <c r="E166" t="n">
-        <v>221945</v>
+        <v>2051</v>
       </c>
       <c r="F166" t="inlineStr">
         <is>
-          <t>Revlummer</t>
+          <t>Rotfingersvamp</t>
         </is>
       </c>
       <c r="G166" t="inlineStr">
         <is>
-          <t>Lycopodium annotinum</t>
+          <t>Ramaria boreimaxima</t>
         </is>
       </c>
       <c r="H166" t="inlineStr">
         <is>
-          <t>L.</t>
+          <t>Kytöv. &amp; M.Toivonen</t>
         </is>
       </c>
       <c r="I166" t="inlineStr"/>
       <c r="J166" t="inlineStr"/>
       <c r="K166" t="inlineStr"/>
-      <c r="L166" t="inlineStr"/>
       <c r="N166" t="inlineStr"/>
       <c r="P166" t="inlineStr">
         <is>
-          <t>Norrby mosse, Srm</t>
+          <t>S Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q166" t="n">
-        <v>686389</v>
+        <v>686477</v>
       </c>
       <c r="R166" t="n">
-        <v>6562967</v>
+        <v>6562857</v>
       </c>
       <c r="S166" t="n">
         <v>10</v>
@@ -18965,22 +18952,17 @@
       </c>
       <c r="Y166" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="Z166" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-07-29</t>
         </is>
       </c>
       <c r="AA166" t="inlineStr">
         <is>
-          <t>2025-03-07</t>
-        </is>
-      </c>
-      <c r="AB166" t="inlineStr">
-        <is>
-          <t>10:36</t>
+          <t>2024-07-29</t>
+        </is>
+      </c>
+      <c r="AC166" t="inlineStr">
+        <is>
+          <t>Brukad skog nära kant mot gammal.</t>
         </is>
       </c>
       <c r="AD166" t="b">
@@ -18989,71 +18971,81 @@
       <c r="AE166" t="b">
         <v>0</v>
       </c>
+      <c r="AF166" t="inlineStr"/>
       <c r="AG166" t="b">
         <v>0</v>
       </c>
       <c r="AT166" t="inlineStr"/>
       <c r="AW166" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX166" t="inlineStr">
         <is>
-          <t>Emilia Blixt</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY166" t="inlineStr"/>
       <c r="AZ166" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/122928987</t>
+          <t>https://artportalen.se/Sighting/119061006</t>
         </is>
       </c>
     </row>
     <row r="167">
       <c r="A167" t="n">
-        <v>126061106</v>
+        <v>122929535</v>
       </c>
       <c r="B167" t="n">
-        <v>91333</v>
+        <v>8455</v>
       </c>
       <c r="D167" t="inlineStr">
         <is>
-          <t>NT</t>
+          <t>LC</t>
         </is>
       </c>
       <c r="E167" t="n">
-        <v>2008</v>
+        <v>106545</v>
       </c>
       <c r="F167" t="inlineStr">
         <is>
-          <t>Fyrflikig jordstjärna</t>
+          <t>Mindre märgborre</t>
         </is>
       </c>
       <c r="G167" t="inlineStr">
         <is>
-          <t>Geastrum quadrifidum</t>
+          <t>Tomicus minor</t>
         </is>
       </c>
       <c r="H167" t="inlineStr">
         <is>
-          <t>Pers., nom.sanct.</t>
-        </is>
-      </c>
-      <c r="I167" t="inlineStr"/>
+          <t>(Hartig, 1834)</t>
+        </is>
+      </c>
+      <c r="I167" t="inlineStr">
+        <is>
+          <t>1</t>
+        </is>
+      </c>
+      <c r="J167" t="inlineStr"/>
+      <c r="K167" t="inlineStr"/>
+      <c r="L167" t="inlineStr"/>
+      <c r="M167" t="inlineStr"/>
+      <c r="N167" t="inlineStr"/>
       <c r="P167" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q167" t="n">
-        <v>686883</v>
+        <v>686612</v>
       </c>
       <c r="R167" t="n">
-        <v>6562742</v>
+        <v>6562882</v>
       </c>
       <c r="S167" t="n">
-        <v>10</v>
+        <v>9</v>
       </c>
       <c r="T167" t="inlineStr">
         <is>
@@ -19077,22 +19069,22 @@
       </c>
       <c r="Y167" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z167" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AA167" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB167" t="inlineStr">
         <is>
-          <t>13:23</t>
+          <t>11:01</t>
         </is>
       </c>
       <c r="AD167" t="b">
@@ -19107,27 +19099,27 @@
       <c r="AT167" t="inlineStr"/>
       <c r="AW167" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX167" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY167" t="inlineStr"/>
       <c r="AZ167" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061106</t>
+          <t>https://artportalen.se/Sighting/122929535</t>
         </is>
       </c>
     </row>
     <row r="168">
       <c r="A168" t="n">
-        <v>126061107</v>
+        <v>122928987</v>
       </c>
       <c r="B168" t="n">
-        <v>96458</v>
+        <v>97983</v>
       </c>
       <c r="D168" t="inlineStr">
         <is>
@@ -19135,34 +19127,38 @@
         </is>
       </c>
       <c r="E168" t="n">
-        <v>2818</v>
+        <v>221945</v>
       </c>
       <c r="F168" t="inlineStr">
         <is>
-          <t>Stubbspretmossa</t>
+          <t>Revlummer</t>
         </is>
       </c>
       <c r="G168" t="inlineStr">
         <is>
-          <t>Herzogiella seligeri</t>
+          <t>Lycopodium annotinum</t>
         </is>
       </c>
       <c r="H168" t="inlineStr">
         <is>
-          <t>(Brid.) Z.Iwats.</t>
+          <t>L.</t>
         </is>
       </c>
       <c r="I168" t="inlineStr"/>
+      <c r="J168" t="inlineStr"/>
+      <c r="K168" t="inlineStr"/>
+      <c r="L168" t="inlineStr"/>
+      <c r="N168" t="inlineStr"/>
       <c r="P168" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>Norrby mosse, Srm</t>
         </is>
       </c>
       <c r="Q168" t="n">
-        <v>686880</v>
+        <v>686389</v>
       </c>
       <c r="R168" t="n">
-        <v>6562745</v>
+        <v>6562967</v>
       </c>
       <c r="S168" t="n">
         <v>10</v>
@@ -19189,22 +19185,22 @@
       </c>
       <c r="Y168" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="Z168" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AA168" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
+          <t>2025-03-07</t>
         </is>
       </c>
       <c r="AB168" t="inlineStr">
         <is>
-          <t>13:19</t>
+          <t>10:36</t>
         </is>
       </c>
       <c r="AD168" t="b">
@@ -19219,65 +19215,62 @@
       <c r="AT168" t="inlineStr"/>
       <c r="AW168" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AX168" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Emilia Blixt</t>
         </is>
       </c>
       <c r="AY168" t="inlineStr"/>
       <c r="AZ168" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061107</t>
+          <t>https://artportalen.se/Sighting/122928987</t>
         </is>
       </c>
     </row>
     <row r="169">
       <c r="A169" t="n">
-        <v>129215187</v>
+        <v>126061106</v>
       </c>
       <c r="B169" t="n">
-        <v>91872</v>
+        <v>91333</v>
       </c>
       <c r="D169" t="inlineStr">
         <is>
-          <t>LC</t>
+          <t>NT</t>
         </is>
       </c>
       <c r="E169" t="n">
-        <v>5447</v>
+        <v>2008</v>
       </c>
       <c r="F169" t="inlineStr">
         <is>
-          <t>Vedticka</t>
+          <t>Fyrflikig jordstjärna</t>
         </is>
       </c>
       <c r="G169" t="inlineStr">
         <is>
-          <t>Fuscoporia viticola</t>
+          <t>Geastrum quadrifidum</t>
         </is>
       </c>
       <c r="H169" t="inlineStr">
         <is>
-          <t>(Schwein.) Murrill</t>
+          <t>Pers., nom.sanct.</t>
         </is>
       </c>
       <c r="I169" t="inlineStr"/>
-      <c r="J169" t="inlineStr"/>
-      <c r="K169" t="inlineStr"/>
-      <c r="N169" t="inlineStr"/>
       <c r="P169" t="inlineStr">
         <is>
-          <t>N Norrbytorp, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q169" t="n">
-        <v>686977</v>
+        <v>686883</v>
       </c>
       <c r="R169" t="n">
-        <v>6562706</v>
+        <v>6562742</v>
       </c>
       <c r="S169" t="n">
         <v>10</v>
@@ -19304,12 +19297,22 @@
       </c>
       <c r="Y169" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z169" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AA169" t="inlineStr">
         <is>
-          <t>2025-10-19</t>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB169" t="inlineStr">
+        <is>
+          <t>13:23</t>
         </is>
       </c>
       <c r="AD169" t="b">
@@ -19318,34 +19321,33 @@
       <c r="AE169" t="b">
         <v>0</v>
       </c>
-      <c r="AF169" t="inlineStr"/>
       <c r="AG169" t="b">
         <v>0</v>
       </c>
       <c r="AT169" t="inlineStr"/>
       <c r="AW169" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX169" t="inlineStr">
         <is>
-          <t>Bodil Ravn</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY169" t="inlineStr"/>
       <c r="AZ169" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/129215187</t>
+          <t>https://artportalen.se/Sighting/126061106</t>
         </is>
       </c>
     </row>
     <row r="170">
       <c r="A170" t="n">
-        <v>126061104</v>
+        <v>126061107</v>
       </c>
       <c r="B170" t="n">
-        <v>4775</v>
+        <v>96458</v>
       </c>
       <c r="D170" t="inlineStr">
         <is>
@@ -19353,21 +19355,21 @@
         </is>
       </c>
       <c r="E170" t="n">
-        <v>100299</v>
+        <v>2818</v>
       </c>
       <c r="F170" t="inlineStr">
         <is>
-          <t>Thomsons trägnagare</t>
+          <t>Stubbspretmossa</t>
         </is>
       </c>
       <c r="G170" t="inlineStr">
         <is>
-          <t>Cacotemnus thomsoni</t>
+          <t>Herzogiella seligeri</t>
         </is>
       </c>
       <c r="H170" t="inlineStr">
         <is>
-          <t>(Kraatz, 1881)</t>
+          <t>(Brid.) Z.Iwats.</t>
         </is>
       </c>
       <c r="I170" t="inlineStr"/>
@@ -19377,10 +19379,10 @@
         </is>
       </c>
       <c r="Q170" t="n">
-        <v>686868</v>
+        <v>686880</v>
       </c>
       <c r="R170" t="n">
-        <v>6562739</v>
+        <v>6562745</v>
       </c>
       <c r="S170" t="n">
         <v>10</v>
@@ -19412,7 +19414,7 @@
       </c>
       <c r="Z170" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AA170" t="inlineStr">
@@ -19422,7 +19424,7 @@
       </c>
       <c r="AB170" t="inlineStr">
         <is>
-          <t>13:41</t>
+          <t>13:19</t>
         </is>
       </c>
       <c r="AD170" t="b">
@@ -19433,26 +19435,6 @@
       </c>
       <c r="AG170" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ170" t="inlineStr">
-        <is>
-          <t>gran</t>
-        </is>
-      </c>
-      <c r="AK170" t="inlineStr">
-        <is>
-          <t>Picea abies</t>
-        </is>
-      </c>
-      <c r="AL170" t="inlineStr">
-        <is>
-          <t>Stående död gran.</t>
-        </is>
-      </c>
-      <c r="AO170" t="inlineStr">
-        <is>
-          <t>Picea abies # Stående död gran.</t>
-        </is>
       </c>
       <c r="AT170" t="inlineStr"/>
       <c r="AW170" t="inlineStr">
@@ -19468,16 +19450,16 @@
       <c r="AY170" t="inlineStr"/>
       <c r="AZ170" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061104</t>
+          <t>https://artportalen.se/Sighting/126061107</t>
         </is>
       </c>
     </row>
     <row r="171">
       <c r="A171" t="n">
-        <v>126061116</v>
+        <v>129215187</v>
       </c>
       <c r="B171" t="n">
-        <v>44177</v>
+        <v>91872</v>
       </c>
       <c r="D171" t="inlineStr">
         <is>
@@ -19485,34 +19467,37 @@
         </is>
       </c>
       <c r="E171" t="n">
-        <v>101735</v>
+        <v>5447</v>
       </c>
       <c r="F171" t="inlineStr">
         <is>
-          <t>Jättesvampmal</t>
+          <t>Vedticka</t>
         </is>
       </c>
       <c r="G171" t="inlineStr">
         <is>
-          <t>Scardia boletella</t>
+          <t>Fuscoporia viticola</t>
         </is>
       </c>
       <c r="H171" t="inlineStr">
         <is>
-          <t>(Fabricius, 1794)</t>
+          <t>(Schwein.) Murrill</t>
         </is>
       </c>
       <c r="I171" t="inlineStr"/>
+      <c r="J171" t="inlineStr"/>
+      <c r="K171" t="inlineStr"/>
+      <c r="N171" t="inlineStr"/>
       <c r="P171" t="inlineStr">
         <is>
-          <t>Ö Tyresta by, Srm</t>
+          <t>N Norrbytorp, Srm</t>
         </is>
       </c>
       <c r="Q171" t="n">
-        <v>686928</v>
+        <v>686977</v>
       </c>
       <c r="R171" t="n">
-        <v>6562716</v>
+        <v>6562706</v>
       </c>
       <c r="S171" t="n">
         <v>10</v>
@@ -19539,22 +19524,12 @@
       </c>
       <c r="Y171" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="Z171" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AA171" t="inlineStr">
         <is>
-          <t>2025-06-15</t>
-        </is>
-      </c>
-      <c r="AB171" t="inlineStr">
-        <is>
-          <t>11:58</t>
+          <t>2025-10-19</t>
         </is>
       </c>
       <c r="AD171" t="b">
@@ -19563,53 +19538,34 @@
       <c r="AE171" t="b">
         <v>0</v>
       </c>
+      <c r="AF171" t="inlineStr"/>
       <c r="AG171" t="b">
         <v>0</v>
-      </c>
-      <c r="AJ171" t="inlineStr">
-        <is>
-          <t>fnöskticka</t>
-        </is>
-      </c>
-      <c r="AK171" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius</t>
-        </is>
-      </c>
-      <c r="AL171" t="inlineStr">
-        <is>
-          <t>Fnöskticka på björk.</t>
-        </is>
-      </c>
-      <c r="AO171" t="inlineStr">
-        <is>
-          <t>Fomes fomentarius # Fnöskticka på björk.</t>
-        </is>
       </c>
       <c r="AT171" t="inlineStr"/>
       <c r="AW171" t="inlineStr">
         <is>
-          <t>Klas Magnusson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AX171" t="inlineStr">
         <is>
-          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+          <t>Bodil Ravn</t>
         </is>
       </c>
       <c r="AY171" t="inlineStr"/>
       <c r="AZ171" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/126061116</t>
+          <t>https://artportalen.se/Sighting/129215187</t>
         </is>
       </c>
     </row>
     <row r="172">
       <c r="A172" t="n">
-        <v>125974903</v>
+        <v>126061104</v>
       </c>
       <c r="B172" t="n">
-        <v>8444</v>
+        <v>4775</v>
       </c>
       <c r="D172" t="inlineStr">
         <is>
@@ -19617,50 +19573,37 @@
         </is>
       </c>
       <c r="E172" t="n">
-        <v>106554</v>
+        <v>100299</v>
       </c>
       <c r="F172" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Thomsons trägnagare</t>
         </is>
       </c>
       <c r="G172" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Cacotemnus thomsoni</t>
         </is>
       </c>
       <c r="H172" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
-        </is>
-      </c>
-      <c r="I172" t="inlineStr">
-        <is>
-          <t>10</t>
-        </is>
-      </c>
-      <c r="J172" t="inlineStr"/>
-      <c r="K172" t="inlineStr"/>
-      <c r="L172" t="inlineStr"/>
-      <c r="M172" t="inlineStr">
-        <is>
-          <t>äldre gnagspår</t>
-        </is>
-      </c>
-      <c r="N172" t="inlineStr"/>
+          <t>(Kraatz, 1881)</t>
+        </is>
+      </c>
+      <c r="I172" t="inlineStr"/>
       <c r="P172" t="inlineStr">
         <is>
-          <t>söder om Tyresta, Srm</t>
+          <t>Ö Tyresta by, Srm</t>
         </is>
       </c>
       <c r="Q172" t="n">
-        <v>686838</v>
+        <v>686868</v>
       </c>
       <c r="R172" t="n">
-        <v>6562733</v>
+        <v>6562739</v>
       </c>
       <c r="S172" t="n">
-        <v>5</v>
+        <v>10</v>
       </c>
       <c r="T172" t="inlineStr">
         <is>
@@ -19687,14 +19630,19 @@
           <t>2025-06-15</t>
         </is>
       </c>
+      <c r="Z172" t="inlineStr">
+        <is>
+          <t>13:41</t>
+        </is>
+      </c>
       <c r="AA172" t="inlineStr">
         <is>
           <t>2025-06-15</t>
         </is>
       </c>
-      <c r="AC172" t="inlineStr">
-        <is>
-          <t>gammal björklåga med spår längs hela stammen</t>
+      <c r="AB172" t="inlineStr">
+        <is>
+          <t>13:41</t>
         </is>
       </c>
       <c r="AD172" t="b">
@@ -19703,54 +19651,53 @@
       <c r="AE172" t="b">
         <v>0</v>
       </c>
-      <c r="AF172" t="inlineStr"/>
       <c r="AG172" t="b">
         <v>0</v>
       </c>
       <c r="AJ172" t="inlineStr">
         <is>
-          <t>vårtbjörk</t>
+          <t>gran</t>
         </is>
       </c>
       <c r="AK172" t="inlineStr">
         <is>
-          <t>Betula pendula</t>
-        </is>
-      </c>
-      <c r="AM172" t="inlineStr">
-        <is>
-          <t>Vedyta på död ved</t>
+          <t>Picea abies</t>
+        </is>
+      </c>
+      <c r="AL172" t="inlineStr">
+        <is>
+          <t>Stående död gran.</t>
         </is>
       </c>
       <c r="AO172" t="inlineStr">
         <is>
-          <t>Wood surface of dead wood # Betula pendula</t>
+          <t>Picea abies # Stående död gran.</t>
         </is>
       </c>
       <c r="AT172" t="inlineStr"/>
       <c r="AW172" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson</t>
         </is>
       </c>
       <c r="AX172" t="inlineStr">
         <is>
-          <t>Nette Bygren</t>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
         </is>
       </c>
       <c r="AY172" t="inlineStr"/>
       <c r="AZ172" t="inlineStr">
         <is>
-          <t>https://artportalen.se/Sighting/125974903</t>
+          <t>https://artportalen.se/Sighting/126061104</t>
         </is>
       </c>
     </row>
     <row r="173">
       <c r="A173" t="n">
-        <v>126061105</v>
+        <v>126061116</v>
       </c>
       <c r="B173" t="n">
-        <v>8444</v>
+        <v>44177</v>
       </c>
       <c r="D173" t="inlineStr">
         <is>
@@ -19758,21 +19705,21 @@
         </is>
       </c>
       <c r="E173" t="n">
-        <v>106554</v>
+        <v>101735</v>
       </c>
       <c r="F173" t="inlineStr">
         <is>
-          <t>Björksplintborre</t>
+          <t>Jättesvampmal</t>
         </is>
       </c>
       <c r="G173" t="inlineStr">
         <is>
-          <t>Scolytus ratzeburgii</t>
+          <t>Scardia boletella</t>
         </is>
       </c>
       <c r="H173" t="inlineStr">
         <is>
-          <t>Janson, 1856</t>
+          <t>(Fabricius, 1794)</t>
         </is>
       </c>
       <c r="I173" t="inlineStr"/>
@@ -19782,10 +19729,10 @@
         </is>
       </c>
       <c r="Q173" t="n">
-        <v>686860</v>
+        <v>686928</v>
       </c>
       <c r="R173" t="n">
-        <v>6562743</v>
+        <v>6562716</v>
       </c>
       <c r="S173" t="n">
         <v>10</v>
@@ -19817,7 +19764,7 @@
       </c>
       <c r="Z173" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AA173" t="inlineStr">
@@ -19827,7 +19774,7 @@
       </c>
       <c r="AB173" t="inlineStr">
         <is>
-          <t>13:36</t>
+          <t>11:58</t>
         </is>
       </c>
       <c r="AD173" t="b">
@@ -19841,17 +19788,22 @@
       </c>
       <c r="AJ173" t="inlineStr">
         <is>
-          <t>björkar</t>
+          <t>fnöskticka</t>
         </is>
       </c>
       <c r="AK173" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Fomes fomentarius</t>
+        </is>
+      </c>
+      <c r="AL173" t="inlineStr">
+        <is>
+          <t>Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AO173" t="inlineStr">
         <is>
-          <t>Betula</t>
+          <t>Fomes fomentarius # Fnöskticka på björk.</t>
         </is>
       </c>
       <c r="AT173" t="inlineStr"/>
@@ -19867,6 +19819,274 @@
       </c>
       <c r="AY173" t="inlineStr"/>
       <c r="AZ173" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/126061116</t>
+        </is>
+      </c>
+    </row>
+    <row r="174">
+      <c r="A174" t="n">
+        <v>125974903</v>
+      </c>
+      <c r="B174" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D174" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E174" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F174" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G174" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H174" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I174" t="inlineStr">
+        <is>
+          <t>10</t>
+        </is>
+      </c>
+      <c r="J174" t="inlineStr"/>
+      <c r="K174" t="inlineStr"/>
+      <c r="L174" t="inlineStr"/>
+      <c r="M174" t="inlineStr">
+        <is>
+          <t>äldre gnagspår</t>
+        </is>
+      </c>
+      <c r="N174" t="inlineStr"/>
+      <c r="P174" t="inlineStr">
+        <is>
+          <t>söder om Tyresta, Srm</t>
+        </is>
+      </c>
+      <c r="Q174" t="n">
+        <v>686838</v>
+      </c>
+      <c r="R174" t="n">
+        <v>6562733</v>
+      </c>
+      <c r="S174" t="n">
+        <v>5</v>
+      </c>
+      <c r="T174" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U174" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V174" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W174" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y174" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AA174" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AC174" t="inlineStr">
+        <is>
+          <t>gammal björklåga med spår längs hela stammen</t>
+        </is>
+      </c>
+      <c r="AD174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AF174" t="inlineStr"/>
+      <c r="AG174" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ174" t="inlineStr">
+        <is>
+          <t>vårtbjörk</t>
+        </is>
+      </c>
+      <c r="AK174" t="inlineStr">
+        <is>
+          <t>Betula pendula</t>
+        </is>
+      </c>
+      <c r="AM174" t="inlineStr">
+        <is>
+          <t>Vedyta på död ved</t>
+        </is>
+      </c>
+      <c r="AO174" t="inlineStr">
+        <is>
+          <t>Wood surface of dead wood # Betula pendula</t>
+        </is>
+      </c>
+      <c r="AT174" t="inlineStr"/>
+      <c r="AW174" t="inlineStr">
+        <is>
+          <t>Nette Bygren</t>
+        </is>
+      </c>
+      <c r="AX174" t="inlineStr">
+        <is>
+          <t>Nette Bygren</t>
+        </is>
+      </c>
+      <c r="AY174" t="inlineStr"/>
+      <c r="AZ174" t="inlineStr">
+        <is>
+          <t>https://artportalen.se/Sighting/125974903</t>
+        </is>
+      </c>
+    </row>
+    <row r="175">
+      <c r="A175" t="n">
+        <v>126061105</v>
+      </c>
+      <c r="B175" t="n">
+        <v>8444</v>
+      </c>
+      <c r="D175" t="inlineStr">
+        <is>
+          <t>LC</t>
+        </is>
+      </c>
+      <c r="E175" t="n">
+        <v>106554</v>
+      </c>
+      <c r="F175" t="inlineStr">
+        <is>
+          <t>Björksplintborre</t>
+        </is>
+      </c>
+      <c r="G175" t="inlineStr">
+        <is>
+          <t>Scolytus ratzeburgii</t>
+        </is>
+      </c>
+      <c r="H175" t="inlineStr">
+        <is>
+          <t>Janson, 1856</t>
+        </is>
+      </c>
+      <c r="I175" t="inlineStr"/>
+      <c r="P175" t="inlineStr">
+        <is>
+          <t>Ö Tyresta by, Srm</t>
+        </is>
+      </c>
+      <c r="Q175" t="n">
+        <v>686860</v>
+      </c>
+      <c r="R175" t="n">
+        <v>6562743</v>
+      </c>
+      <c r="S175" t="n">
+        <v>10</v>
+      </c>
+      <c r="T175" t="inlineStr">
+        <is>
+          <t>Stockholm</t>
+        </is>
+      </c>
+      <c r="U175" t="inlineStr">
+        <is>
+          <t>Haninge</t>
+        </is>
+      </c>
+      <c r="V175" t="inlineStr">
+        <is>
+          <t>Södermanland</t>
+        </is>
+      </c>
+      <c r="W175" t="inlineStr">
+        <is>
+          <t>Österhaninge</t>
+        </is>
+      </c>
+      <c r="Y175" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="Z175" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AA175" t="inlineStr">
+        <is>
+          <t>2025-06-15</t>
+        </is>
+      </c>
+      <c r="AB175" t="inlineStr">
+        <is>
+          <t>13:36</t>
+        </is>
+      </c>
+      <c r="AD175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AE175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AG175" t="b">
+        <v>0</v>
+      </c>
+      <c r="AJ175" t="inlineStr">
+        <is>
+          <t>björkar</t>
+        </is>
+      </c>
+      <c r="AK175" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AO175" t="inlineStr">
+        <is>
+          <t>Betula</t>
+        </is>
+      </c>
+      <c r="AT175" t="inlineStr"/>
+      <c r="AW175" t="inlineStr">
+        <is>
+          <t>Klas Magnusson</t>
+        </is>
+      </c>
+      <c r="AX175" t="inlineStr">
+        <is>
+          <t>Klas Magnusson, Måns Persson, Bodil Ravn, Isak Westerström, Birgitta Tulin, Johan Spaedtke, Viktor Munkhammar, Ulf Johansson</t>
+        </is>
+      </c>
+      <c r="AY175" t="inlineStr"/>
+      <c r="AZ175" t="inlineStr">
         <is>
           <t>https://artportalen.se/Sighting/126061105</t>
         </is>
@@ -20046,6 +20266,8 @@
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ171" r:id="rId170"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ172" r:id="rId171"/>
     <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ173" r:id="rId172"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ174" r:id="rId173"/>
+    <hyperlink xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" ref="AZ175" r:id="rId174"/>
   </hyperlinks>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
 </worksheet>
